--- a/Raw Data/Micro Plans/November 2025/Micro Plan - TA-421 Nov'25.xlsx
+++ b/Raw Data/Micro Plans/November 2025/Micro Plan - TA-421 Nov'25.xlsx
@@ -5,18 +5,19 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Eagle\Nov'25\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kaushikb\Documents\Work\Git\Office-work-\Raw Data\Micro Plans\November 2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12F3AC96-A78C-403F-901D-69CA934916BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ABE5E5B-1032-43D4-BF9B-84C78188882A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="757" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="757" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FDN-June25" sheetId="1" state="hidden" r:id="rId1"/>
     <sheet name="Stub dispatch" sheetId="4" state="hidden" r:id="rId2"/>
     <sheet name="Erection-Nov'25" sheetId="5" r:id="rId3"/>
-    <sheet name="STG-Sep25" sheetId="3" state="hidden" r:id="rId4"/>
+    <sheet name="Stringing Nov'25" sheetId="6" r:id="rId4"/>
+    <sheet name="STG-Sep25" sheetId="3" state="hidden" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Erection-Nov''25'!$A$1:$O$30</definedName>
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="215">
   <si>
     <t>Project Code</t>
   </si>
@@ -585,6 +586,111 @@
   </si>
   <si>
     <t xml:space="preserve">Subash Kumar </t>
+  </si>
+  <si>
+    <t>S. No.</t>
+  </si>
+  <si>
+    <t>From AP</t>
+  </si>
+  <si>
+    <t>To AP</t>
+  </si>
+  <si>
+    <t>Span (m)</t>
+  </si>
+  <si>
+    <t>Tower Erection Status</t>
+  </si>
+  <si>
+    <t>Towers in section</t>
+  </si>
+  <si>
+    <t>Insulator Hoisting</t>
+  </si>
+  <si>
+    <t>Paying Out Start</t>
+  </si>
+  <si>
+    <t>Paying Out Completed</t>
+  </si>
+  <si>
+    <t>Final Sag Complete</t>
+  </si>
+  <si>
+    <t>Method</t>
+  </si>
+  <si>
+    <t>Gang Strength</t>
+  </si>
+  <si>
+    <t>17/0</t>
+  </si>
+  <si>
+    <t>18/0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TSE 1 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">M R Constructions </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mr. Manoj Mahto/Mr.Chandrasekharan </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mr. Satyam Tiwari </t>
+  </si>
+  <si>
+    <t>16/0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16/11- TE Balance </t>
+  </si>
+  <si>
+    <t>15/0</t>
+  </si>
+  <si>
+    <t>34/0</t>
+  </si>
+  <si>
+    <t>34/1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manual </t>
+  </si>
+  <si>
+    <t>34/2</t>
+  </si>
+  <si>
+    <t>35/0</t>
+  </si>
+  <si>
+    <t>13/0</t>
+  </si>
+  <si>
+    <t>14/0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TSE 2 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nasiruddin </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mr.Susanth Pal </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mr. Godvin John </t>
+  </si>
+  <si>
+    <t>11/0</t>
+  </si>
+  <si>
+    <t>12/0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11/8 - TE Balance </t>
   </si>
 </sst>
 </file>
@@ -592,16 +698,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="8">
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="164" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
-    <numFmt numFmtId="166" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
-    <numFmt numFmtId="167" formatCode="[$-409]d/mmm/yy;@"/>
-    <numFmt numFmtId="168" formatCode="0.0"/>
-    <numFmt numFmtId="169" formatCode="#,##0.000"/>
-    <numFmt numFmtId="170" formatCode="0.000"/>
+    <numFmt numFmtId="164" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="165" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="166" formatCode="[$-409]d\-mmm\-yy;@"/>
+    <numFmt numFmtId="167" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
+    <numFmt numFmtId="168" formatCode="[$-409]d/mmm/yy;@"/>
+    <numFmt numFmtId="169" formatCode="0.0"/>
+    <numFmt numFmtId="170" formatCode="#,##0.000"/>
+    <numFmt numFmtId="171" formatCode="0.000"/>
   </numFmts>
-  <fonts count="32" x14ac:knownFonts="1">
+  <fonts count="34" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -830,6 +936,17 @@
       <name val="Aptos"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="11">
     <fill>
@@ -893,7 +1010,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -1081,17 +1198,89 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="27">
+  <cellStyleXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
-    <xf numFmtId="167" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="167" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="168" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="168" fontId="13" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
@@ -1110,8 +1299,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="191">
+  <cellXfs count="207">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1155,13 +1345,13 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1170,25 +1360,25 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1197,31 +1387,31 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1230,13 +1420,13 @@
     <xf numFmtId="17" fontId="3" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="10" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1251,7 +1441,7 @@
     <xf numFmtId="9" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
@@ -1266,41 +1456,41 @@
     <xf numFmtId="2" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="15" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="17" fillId="6" borderId="14" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="17" fillId="6" borderId="14" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="17" fillId="6" borderId="14" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="166" fontId="17" fillId="6" borderId="14" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="1" fontId="17" fillId="6" borderId="14" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="17" fillId="6" borderId="14" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="17" fillId="6" borderId="14" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="18" fillId="0" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="18" fillId="0" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="19" fillId="0" borderId="1" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="19" fillId="0" borderId="1" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="18" fillId="0" borderId="1" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="18" fillId="0" borderId="1" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="18" fillId="0" borderId="1" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="18" fillId="0" borderId="1" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1328,7 +1518,7 @@
     <xf numFmtId="1" fontId="20" fillId="0" borderId="1" xfId="7" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="18" fillId="8" borderId="3" xfId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="18" fillId="8" borderId="3" xfId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1341,7 +1531,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1359,7 +1549,7 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1368,16 +1558,16 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
@@ -1389,16 +1579,16 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1410,7 +1600,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1449,19 +1639,19 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1470,7 +1660,7 @@
     <xf numFmtId="2" fontId="26" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="170" fontId="26" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="26" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1479,7 +1669,7 @@
     <xf numFmtId="2" fontId="26" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="170" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1488,21 +1678,153 @@
     <xf numFmtId="1" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="16" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="25" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="11" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="10" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="11" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="11" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="31" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="31" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1518,51 +1840,6 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1578,107 +1855,66 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="33" fillId="2" borderId="15" xfId="27" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="2" borderId="13" xfId="27" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="2" borderId="1" xfId="27" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="2" borderId="16" xfId="27" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="2" borderId="17" xfId="27" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="2" borderId="4" xfId="27" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="2" borderId="18" xfId="27" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="25" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="25" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="15" fontId="33" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="16" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="15" fontId="33" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="25" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="11" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="16" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="10" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="11" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="11" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="31" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="31" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="27">
+  <cellStyles count="28">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Comma 2" xfId="8" xr:uid="{2E20F6CD-B1A5-4CBE-90C6-C0D98A914F04}"/>
     <cellStyle name="Excel Built-in Normal" xfId="26" xr:uid="{4B0B78A8-24BE-4DE7-B5BF-D3DFA24ECD02}"/>
@@ -1702,12 +1938,13 @@
     <cellStyle name="Normal 219" xfId="18" xr:uid="{DFC60562-02A4-4EA4-8096-F18F39B0DE19}"/>
     <cellStyle name="Normal 222" xfId="16" xr:uid="{83AE90D7-9474-4B42-9990-710167A5A419}"/>
     <cellStyle name="Normal 3" xfId="25" xr:uid="{2DA1E557-7CA6-467D-8A70-659D8412FB6A}"/>
+    <cellStyle name="Normal 3 10" xfId="27" xr:uid="{CA7B12E2-DB4F-41A0-8414-726E8D4B45BC}"/>
     <cellStyle name="Normal 5" xfId="23" xr:uid="{3FC12385-9363-45A8-94D8-55F9303BEA9B}"/>
     <cellStyle name="Normal_Rev_IPP_ BUB_ 10.04.09 2" xfId="4" xr:uid="{526D1CE4-A6A3-4EA2-BCF4-E0959F12CAFC}"/>
     <cellStyle name="Percent" xfId="2" builtinId="5"/>
     <cellStyle name="Percent 2" xfId="7" xr:uid="{36A5E538-A591-4B85-8561-9BC706E69FE8}"/>
   </cellStyles>
-  <dxfs count="136">
+  <dxfs count="126">
     <dxf>
       <font>
         <color rgb="FFFF0000"/>
@@ -1725,6 +1962,36 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C5700"/>
       </font>
       <fill>
@@ -1755,6 +2022,46 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C5700"/>
       </font>
       <fill>
@@ -1765,6 +2072,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -1795,6 +2112,26 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -1805,6 +2142,26 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -1845,6 +2202,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -1885,6 +2252,46 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C5700"/>
       </font>
       <fill>
@@ -1905,6 +2312,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -1935,6 +2352,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -1955,6 +2382,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -1965,6 +2402,26 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C5700"/>
       </font>
       <fill>
@@ -2025,6 +2482,46 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C5700"/>
       </font>
       <fill>
@@ -2055,16 +2552,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -2075,16 +2562,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -2095,26 +2572,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -2125,26 +2582,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -2155,16 +2592,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -2175,16 +2602,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -2195,26 +2612,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -2225,16 +2622,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -2245,261 +2632,11 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2755,6 +2892,16 @@
     </dxf>
     <dxf>
       <font>
+        <color indexed="17"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color indexed="20"/>
       </font>
       <fill>
@@ -2777,16 +2924,6 @@
       <font>
         <color indexed="20"/>
       </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color indexed="17"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor indexed="42"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <font>
@@ -3333,38 +3470,38 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AG34"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="4.140625" style="4" customWidth="1"/>
+    <col min="1" max="1" width="4.1796875" style="4" customWidth="1"/>
     <col min="2" max="3" width="10" style="1" customWidth="1"/>
-    <col min="4" max="4" width="12.5703125" style="4" customWidth="1"/>
-    <col min="5" max="6" width="8.7109375" style="4" customWidth="1"/>
-    <col min="7" max="7" width="22.28515625" style="4" customWidth="1"/>
-    <col min="8" max="8" width="14.28515625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="11.5703125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="12.5703125" style="1" customWidth="1"/>
-    <col min="11" max="11" width="16.140625" style="1" customWidth="1"/>
-    <col min="12" max="12" width="12.140625" style="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" customWidth="1"/>
-    <col min="14" max="14" width="11.28515625" style="1" customWidth="1"/>
-    <col min="15" max="15" width="12.140625" style="1" customWidth="1"/>
-    <col min="16" max="16" width="17.7109375" style="1" customWidth="1"/>
-    <col min="17" max="17" width="3.140625" style="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" customWidth="1"/>
-    <col min="19" max="19" width="3.140625" style="1" customWidth="1"/>
-    <col min="20" max="25" width="8.7109375" style="1" customWidth="1"/>
-    <col min="26" max="26" width="3.140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="12.54296875" style="4" customWidth="1"/>
+    <col min="5" max="6" width="8.7265625" style="4" customWidth="1"/>
+    <col min="7" max="7" width="22.26953125" style="4" customWidth="1"/>
+    <col min="8" max="8" width="14.26953125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="11.54296875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="12.54296875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="16.1796875" style="1" customWidth="1"/>
+    <col min="12" max="12" width="12.1796875" style="1" customWidth="1"/>
+    <col min="13" max="13" width="14.81640625" style="1" customWidth="1"/>
+    <col min="14" max="14" width="11.26953125" style="1" customWidth="1"/>
+    <col min="15" max="15" width="12.1796875" style="1" customWidth="1"/>
+    <col min="16" max="16" width="17.7265625" style="1" customWidth="1"/>
+    <col min="17" max="17" width="3.1796875" style="1" customWidth="1"/>
+    <col min="18" max="18" width="14.54296875" style="1" customWidth="1"/>
+    <col min="19" max="19" width="3.1796875" style="1" customWidth="1"/>
+    <col min="20" max="25" width="8.7265625" style="1" customWidth="1"/>
+    <col min="26" max="26" width="3.1796875" style="1" customWidth="1"/>
     <col min="27" max="27" width="15" style="1" customWidth="1"/>
-    <col min="28" max="28" width="15.5703125" style="1" customWidth="1"/>
-    <col min="29" max="29" width="17.140625" style="1" customWidth="1"/>
-    <col min="30" max="30" width="13.85546875" style="1" customWidth="1"/>
-    <col min="31" max="31" width="10.7109375" style="1" customWidth="1"/>
-    <col min="32" max="32" width="15.5703125" style="1" customWidth="1"/>
-    <col min="33" max="33" width="17.140625" style="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="28" max="28" width="15.54296875" style="1" customWidth="1"/>
+    <col min="29" max="29" width="17.1796875" style="1" customWidth="1"/>
+    <col min="30" max="30" width="13.81640625" style="1" customWidth="1"/>
+    <col min="31" max="31" width="10.7265625" style="1" customWidth="1"/>
+    <col min="32" max="32" width="15.54296875" style="1" customWidth="1"/>
+    <col min="33" max="33" width="17.1796875" style="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.1796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
@@ -3372,7 +3509,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" s="13" t="s">
         <v>21</v>
       </c>
@@ -3380,11 +3517,11 @@
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" s="6"/>
       <c r="D3" s="1"/>
     </row>
-    <row r="4" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A4" s="13" t="s">
         <v>22</v>
       </c>
@@ -3400,7 +3537,7 @@
       <c r="L4" s="82"/>
       <c r="M4" s="83"/>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5" s="6"/>
       <c r="D5" s="2" t="s">
         <v>29</v>
@@ -3411,7 +3548,7 @@
       <c r="J5" s="4"/>
       <c r="K5" s="4"/>
     </row>
-    <row r="6" spans="1:13" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" ht="16" x14ac:dyDescent="0.35">
       <c r="A6" s="6"/>
       <c r="D6" s="2" t="s">
         <v>85</v>
@@ -3422,7 +3559,7 @@
       <c r="K6" s="3"/>
       <c r="M6" s="98"/>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7" s="6"/>
       <c r="D7" s="2" t="s">
         <v>2</v>
@@ -3434,11 +3571,11 @@
       <c r="K7" s="3"/>
       <c r="M7" s="98"/>
     </row>
-    <row r="8" spans="1:13" ht="5.0999999999999996" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" ht="5.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A8" s="6"/>
       <c r="D8" s="1"/>
     </row>
-    <row r="9" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A9" s="13" t="s">
         <v>23</v>
       </c>
@@ -3459,13 +3596,13 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" ht="5.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="13"/>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
       <c r="F10" s="13"/>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A11" s="13" t="s">
         <v>33</v>
       </c>
@@ -3489,7 +3626,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A12" s="5"/>
       <c r="D12" s="2" t="s">
         <v>25</v>
@@ -3511,7 +3648,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A13" s="5"/>
       <c r="D13" s="2" t="s">
         <v>26</v>
@@ -3533,7 +3670,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A14" s="5"/>
       <c r="D14" s="2" t="s">
         <v>27</v>
@@ -3555,7 +3692,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" ht="16" x14ac:dyDescent="0.35">
       <c r="A15" s="5"/>
       <c r="D15" s="28" t="s">
         <v>28</v>
@@ -3577,7 +3714,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A16" s="5" t="s">
         <v>51</v>
       </c>
@@ -3601,144 +3738,144 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A17" s="5"/>
       <c r="D17" s="6"/>
       <c r="E17" s="6"/>
       <c r="F17" s="6"/>
     </row>
-    <row r="18" spans="1:33" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="135" t="s">
+    <row r="18" spans="1:33" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="179" t="s">
         <v>4</v>
       </c>
-      <c r="B18" s="135" t="s">
+      <c r="B18" s="179" t="s">
         <v>5</v>
       </c>
-      <c r="C18" s="132" t="s">
+      <c r="C18" s="175" t="s">
         <v>6</v>
       </c>
-      <c r="D18" s="135" t="s">
+      <c r="D18" s="179" t="s">
         <v>7</v>
       </c>
-      <c r="E18" s="132" t="s">
+      <c r="E18" s="175" t="s">
         <v>16</v>
       </c>
-      <c r="F18" s="132" t="s">
+      <c r="F18" s="175" t="s">
         <v>17</v>
       </c>
-      <c r="G18" s="135" t="s">
+      <c r="G18" s="179" t="s">
         <v>8</v>
       </c>
-      <c r="H18" s="147" t="s">
+      <c r="H18" s="166" t="s">
         <v>18</v>
       </c>
-      <c r="I18" s="147"/>
-      <c r="J18" s="147"/>
-      <c r="K18" s="147"/>
-      <c r="L18" s="147"/>
-      <c r="M18" s="147"/>
-      <c r="N18" s="147"/>
-      <c r="O18" s="147"/>
-      <c r="P18" s="140" t="s">
+      <c r="I18" s="166"/>
+      <c r="J18" s="166"/>
+      <c r="K18" s="166"/>
+      <c r="L18" s="166"/>
+      <c r="M18" s="166"/>
+      <c r="N18" s="166"/>
+      <c r="O18" s="166"/>
+      <c r="P18" s="169" t="s">
         <v>19</v>
       </c>
-      <c r="R18" s="132" t="s">
+      <c r="R18" s="175" t="s">
         <v>36</v>
       </c>
-      <c r="T18" s="141" t="s">
+      <c r="T18" s="170" t="s">
         <v>31</v>
       </c>
-      <c r="U18" s="142"/>
-      <c r="V18" s="142"/>
-      <c r="W18" s="142"/>
-      <c r="X18" s="142"/>
-      <c r="Y18" s="143"/>
-      <c r="AA18" s="141" t="s">
+      <c r="U18" s="171"/>
+      <c r="V18" s="171"/>
+      <c r="W18" s="171"/>
+      <c r="X18" s="171"/>
+      <c r="Y18" s="172"/>
+      <c r="AA18" s="170" t="s">
         <v>30</v>
       </c>
-      <c r="AB18" s="142"/>
-      <c r="AC18" s="142"/>
-      <c r="AD18" s="142"/>
-      <c r="AE18" s="142"/>
-      <c r="AF18" s="143"/>
-      <c r="AG18" s="144" t="s">
+      <c r="AB18" s="171"/>
+      <c r="AC18" s="171"/>
+      <c r="AD18" s="171"/>
+      <c r="AE18" s="171"/>
+      <c r="AF18" s="172"/>
+      <c r="AG18" s="173" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="19" spans="1:33" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="136"/>
-      <c r="B19" s="136"/>
-      <c r="C19" s="133"/>
-      <c r="D19" s="136"/>
-      <c r="E19" s="133"/>
-      <c r="F19" s="133"/>
-      <c r="G19" s="136"/>
-      <c r="H19" s="152" t="s">
+    <row r="19" spans="1:33" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="180"/>
+      <c r="B19" s="180"/>
+      <c r="C19" s="177"/>
+      <c r="D19" s="180"/>
+      <c r="E19" s="177"/>
+      <c r="F19" s="177"/>
+      <c r="G19" s="180"/>
+      <c r="H19" s="165" t="s">
         <v>9</v>
       </c>
-      <c r="I19" s="152"/>
-      <c r="J19" s="152" t="s">
+      <c r="I19" s="165"/>
+      <c r="J19" s="165" t="s">
         <v>12</v>
       </c>
-      <c r="K19" s="152"/>
-      <c r="L19" s="152" t="s">
+      <c r="K19" s="165"/>
+      <c r="L19" s="165" t="s">
         <v>13</v>
       </c>
-      <c r="M19" s="152"/>
-      <c r="N19" s="148" t="s">
+      <c r="M19" s="165"/>
+      <c r="N19" s="163" t="s">
         <v>15</v>
       </c>
-      <c r="O19" s="148" t="s">
+      <c r="O19" s="163" t="s">
         <v>14</v>
       </c>
-      <c r="P19" s="140"/>
-      <c r="R19" s="146"/>
-      <c r="T19" s="138" t="s">
+      <c r="P19" s="169"/>
+      <c r="R19" s="176"/>
+      <c r="T19" s="167" t="s">
         <v>24</v>
       </c>
-      <c r="U19" s="138" t="s">
+      <c r="U19" s="167" t="s">
         <v>25</v>
       </c>
-      <c r="V19" s="138" t="s">
+      <c r="V19" s="167" t="s">
         <v>26</v>
       </c>
-      <c r="W19" s="138" t="s">
+      <c r="W19" s="167" t="s">
         <v>27</v>
       </c>
-      <c r="X19" s="138" t="s">
+      <c r="X19" s="167" t="s">
         <v>28</v>
       </c>
       <c r="Y19" s="43" t="s">
         <v>29</v>
       </c>
-      <c r="AA19" s="138" t="s">
+      <c r="AA19" s="167" t="s">
         <v>24</v>
       </c>
-      <c r="AB19" s="138" t="s">
+      <c r="AB19" s="167" t="s">
         <v>25</v>
       </c>
-      <c r="AC19" s="138" t="s">
+      <c r="AC19" s="167" t="s">
         <v>26</v>
       </c>
-      <c r="AD19" s="138" t="s">
+      <c r="AD19" s="167" t="s">
         <v>27</v>
       </c>
-      <c r="AE19" s="138" t="s">
+      <c r="AE19" s="167" t="s">
         <v>28</v>
       </c>
       <c r="AF19" s="43" t="s">
         <v>29</v>
       </c>
-      <c r="AG19" s="145"/>
-    </row>
-    <row r="20" spans="1:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="137"/>
-      <c r="B20" s="136"/>
-      <c r="C20" s="133"/>
-      <c r="D20" s="136"/>
-      <c r="E20" s="134"/>
-      <c r="F20" s="134"/>
-      <c r="G20" s="136"/>
+      <c r="AG19" s="174"/>
+    </row>
+    <row r="20" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="181"/>
+      <c r="B20" s="180"/>
+      <c r="C20" s="177"/>
+      <c r="D20" s="180"/>
+      <c r="E20" s="178"/>
+      <c r="F20" s="178"/>
+      <c r="G20" s="180"/>
       <c r="H20" s="94" t="s">
         <v>10</v>
       </c>
@@ -3757,25 +3894,25 @@
       <c r="M20" s="94" t="s">
         <v>11</v>
       </c>
-      <c r="N20" s="149"/>
-      <c r="O20" s="149"/>
+      <c r="N20" s="164"/>
+      <c r="O20" s="164"/>
       <c r="P20" s="44" t="s">
         <v>50</v>
       </c>
       <c r="R20" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="T20" s="139"/>
-      <c r="U20" s="139"/>
-      <c r="V20" s="139"/>
-      <c r="W20" s="139"/>
-      <c r="X20" s="139"/>
+      <c r="T20" s="168"/>
+      <c r="U20" s="168"/>
+      <c r="V20" s="168"/>
+      <c r="W20" s="168"/>
+      <c r="X20" s="168"/>
       <c r="Y20" s="19"/>
-      <c r="AA20" s="139"/>
-      <c r="AB20" s="139"/>
-      <c r="AC20" s="139"/>
-      <c r="AD20" s="139"/>
-      <c r="AE20" s="139"/>
+      <c r="AA20" s="168"/>
+      <c r="AB20" s="168"/>
+      <c r="AC20" s="168"/>
+      <c r="AD20" s="168"/>
+      <c r="AE20" s="168"/>
       <c r="AF20" s="19" t="s">
         <v>50</v>
       </c>
@@ -3783,7 +3920,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="21" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="97">
         <v>1</v>
       </c>
@@ -3875,7 +4012,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:33" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:33" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="97">
         <v>2</v>
       </c>
@@ -3921,7 +4058,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:33" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:33" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="97">
         <v>3</v>
       </c>
@@ -3979,7 +4116,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:33" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:33" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="97">
         <v>4</v>
       </c>
@@ -4037,7 +4174,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:33" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:33" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="97">
         <v>5</v>
       </c>
@@ -4046,7 +4183,7 @@
       <c r="D25" s="86"/>
       <c r="E25" s="101"/>
       <c r="F25" s="8"/>
-      <c r="G25" s="150"/>
+      <c r="G25" s="161"/>
       <c r="H25" s="99"/>
       <c r="I25" s="99"/>
       <c r="J25" s="99"/>
@@ -4095,7 +4232,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:33" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:33" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="97">
         <v>6</v>
       </c>
@@ -4104,7 +4241,7 @@
       <c r="D26" s="8"/>
       <c r="E26" s="102"/>
       <c r="F26" s="97"/>
-      <c r="G26" s="151"/>
+      <c r="G26" s="162"/>
       <c r="H26" s="99"/>
       <c r="I26" s="99"/>
       <c r="J26" s="99"/>
@@ -4153,7 +4290,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:33" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:33" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="97">
         <v>7</v>
       </c>
@@ -4211,7 +4348,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:33" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:33" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="97"/>
       <c r="B28" s="103"/>
       <c r="C28" s="103"/>
@@ -4267,7 +4404,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:33" ht="20.100000000000001" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:33" ht="20.149999999999999" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A29" s="11"/>
       <c r="B29" s="92"/>
       <c r="C29" s="93"/>
@@ -4323,7 +4460,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:33" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:33" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="9"/>
       <c r="B30" s="10"/>
       <c r="C30" s="10"/>
@@ -4403,7 +4540,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:33" x14ac:dyDescent="0.35">
       <c r="N32" s="55" t="s">
         <v>83</v>
       </c>
@@ -4412,7 +4549,7 @@
         <v>7224.33</v>
       </c>
     </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B33" s="76"/>
       <c r="C33" s="76"/>
       <c r="D33" s="77"/>
@@ -4430,7 +4567,7 @@
         <v>7782.57</v>
       </c>
     </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B34" s="78"/>
       <c r="C34" s="76"/>
       <c r="D34" s="77"/>
@@ -4459,16 +4596,13 @@
     <filterColumn colId="13" showButton="0"/>
   </autoFilter>
   <mergeCells count="29">
-    <mergeCell ref="G25:G26"/>
-    <mergeCell ref="O19:O20"/>
-    <mergeCell ref="H19:I19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="L19:M19"/>
-    <mergeCell ref="H18:O18"/>
-    <mergeCell ref="N19:N20"/>
-    <mergeCell ref="U19:U20"/>
-    <mergeCell ref="V19:V20"/>
-    <mergeCell ref="W19:W20"/>
+    <mergeCell ref="F18:F20"/>
+    <mergeCell ref="G18:G20"/>
+    <mergeCell ref="A18:A20"/>
+    <mergeCell ref="B18:B20"/>
+    <mergeCell ref="C18:C20"/>
+    <mergeCell ref="D18:D20"/>
+    <mergeCell ref="E18:E20"/>
     <mergeCell ref="X19:X20"/>
     <mergeCell ref="P18:P19"/>
     <mergeCell ref="AA18:AF18"/>
@@ -4481,163 +4615,166 @@
     <mergeCell ref="R18:R19"/>
     <mergeCell ref="T18:Y18"/>
     <mergeCell ref="T19:T20"/>
-    <mergeCell ref="F18:F20"/>
-    <mergeCell ref="G18:G20"/>
-    <mergeCell ref="A18:A20"/>
-    <mergeCell ref="B18:B20"/>
-    <mergeCell ref="C18:C20"/>
-    <mergeCell ref="D18:D20"/>
-    <mergeCell ref="E18:E20"/>
+    <mergeCell ref="H18:O18"/>
+    <mergeCell ref="N19:N20"/>
+    <mergeCell ref="U19:U20"/>
+    <mergeCell ref="V19:V20"/>
+    <mergeCell ref="W19:W20"/>
+    <mergeCell ref="G25:G26"/>
+    <mergeCell ref="O19:O20"/>
+    <mergeCell ref="H19:I19"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="L19:M19"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="B21">
-    <cfRule type="duplicateValues" dxfId="135" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="134" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="133" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="132" priority="4"/>
-    <cfRule type="expression" dxfId="131" priority="5" stopIfTrue="1">
+    <cfRule type="duplicateValues" dxfId="125" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="124" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="123" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="122" priority="4"/>
+    <cfRule type="expression" dxfId="121" priority="5" stopIfTrue="1">
       <formula>AND(COUNTIF($D$28:$D$37, B21)+COUNTIF($D$16:$D$16, B21)&gt;1,NOT(ISBLANK(B21)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="130" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="120" priority="6" stopIfTrue="1">
       <formula>AND(COUNTIF($D$28:$D$65380, B21)+COUNTIF($D$1:$D$16, B21)&gt;1,NOT(ISBLANK(B21)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="129" priority="7" stopIfTrue="1">
+    <cfRule type="expression" dxfId="119" priority="7" stopIfTrue="1">
       <formula>AND(COUNTIF($D$17:$D$65380, B21)+COUNTIF($D$1:$D$16, B21)&gt;1,NOT(ISBLANK(B21)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="128" priority="8" stopIfTrue="1">
+    <cfRule type="expression" dxfId="118" priority="8" stopIfTrue="1">
       <formula>AND(COUNTIF($D$1:$D$123, B21)+COUNTIF($D$142:$D$65380, B21)&gt;1,NOT(ISBLANK(B21)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="127" priority="9" stopIfTrue="1">
+    <cfRule type="expression" dxfId="117" priority="9" stopIfTrue="1">
       <formula>AND(COUNTIF($D$1:$D$191, B21)+COUNTIF($D$214:$D$65380, B21)&gt;1,NOT(ISBLANK(B21)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="126" priority="10" stopIfTrue="1">
+    <cfRule type="expression" dxfId="116" priority="10" stopIfTrue="1">
       <formula>AND(COUNTIF($D$1:$D$191, B21)+COUNTIF($D$214:$D$65380, B21)&gt;1,NOT(ISBLANK(B21)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="125" priority="11" stopIfTrue="1">
+    <cfRule type="expression" dxfId="115" priority="11" stopIfTrue="1">
       <formula>AND(COUNTIF($D$1:$D$191, B21)+COUNTIF($D$214:$D$65380, B21)&gt;1,NOT(ISBLANK(B21)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="124" priority="12" stopIfTrue="1">
+    <cfRule type="expression" dxfId="114" priority="12" stopIfTrue="1">
       <formula>AND(COUNTIF($D$474:$D$65380, B21)+COUNTIF($D$454:$D$455, B21)+COUNTIF($D$416:$D$417, B21)+COUNTIF($D$374:$D$377, B21)+COUNTIF($D$351:$D$352, B21)+COUNTIF($D$324:$D$325, B21)+COUNTIF($D$303:$D$303, B21)+COUNTIF($D$288:$D$289, B21)+COUNTIF($D$263:$D$263, B21)+COUNTIF($D$252:$D$253, B21)+COUNTIF($D$233:$D$234, B21)+COUNTIF($D$51:$D$218, B21)+COUNTIF($D$219:$D$220, B21)+COUNTIF($D$1:$D$50, B21)&gt;1,NOT(ISBLANK(B21)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B21:B27">
-    <cfRule type="duplicateValues" dxfId="123" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="113" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22">
-    <cfRule type="duplicateValues" dxfId="122" priority="14"/>
-    <cfRule type="duplicateValues" dxfId="121" priority="15"/>
-    <cfRule type="duplicateValues" dxfId="120" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="112" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="111" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="110" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B23">
-    <cfRule type="duplicateValues" dxfId="119" priority="19"/>
-    <cfRule type="duplicateValues" dxfId="118" priority="20"/>
-    <cfRule type="expression" dxfId="117" priority="1251" stopIfTrue="1">
+    <cfRule type="duplicateValues" dxfId="109" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="108" priority="20"/>
+    <cfRule type="expression" dxfId="107" priority="1251" stopIfTrue="1">
       <formula>AND(COUNTIF($C$2:$C$65291, B23)+COUNTIF(#REF!, B23)&gt;1,NOT(ISBLANK(B23)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="116" priority="1252" stopIfTrue="1">
+    <cfRule type="expression" dxfId="106" priority="1252" stopIfTrue="1">
       <formula>AND(COUNTIF($C$145:$C$65291, B23)+COUNTIF($C$125:$C$126, B23)+COUNTIF($C$87:$C$88, B23)+COUNTIF($C$45:$C$48, B23)+COUNTIF(#REF!, B23)+COUNTIF(#REF!, B23)+COUNTIF(#REF!, B23)+COUNTIF(#REF!, B23)+COUNTIF(#REF!, B23)+COUNTIF(#REF!, B23)+COUNTIF(#REF!, B23)+COUNTIF(#REF!, B23)+COUNTIF($B$9:$B$9, B23)+COUNTIF($C$2:$C$8, B23)&gt;1,NOT(ISBLANK(B23)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B26:B27 B21 B23">
-    <cfRule type="expression" dxfId="115" priority="1248" stopIfTrue="1">
+    <cfRule type="expression" dxfId="105" priority="1248" stopIfTrue="1">
       <formula>AND(COUNTIF($C$1:$C$65282, B21)+COUNTIF(#REF!, B21)&gt;1,NOT(ISBLANK(B21)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B26:B27 B23 B21">
-    <cfRule type="expression" dxfId="114" priority="1236" stopIfTrue="1">
+    <cfRule type="expression" dxfId="104" priority="1236" stopIfTrue="1">
       <formula>AND(COUNTIF($C$136:$C$65282, B21)+COUNTIF($C$116:$C$117, B21)+COUNTIF($C$78:$C$79, B21)+COUNTIF($C$36:$C$39, B21)+COUNTIF($C$23:$C$24, B21)+COUNTIF(#REF!, B21)+COUNTIF(#REF!, B21)+COUNTIF(#REF!, B21)+COUNTIF(#REF!, B21)+COUNTIF(#REF!, B21)+COUNTIF(#REF!, B21)+COUNTIF(#REF!, B21)+COUNTIF(#REF!, B21)+COUNTIF($C$1:$C$5, B21)&gt;1,NOT(ISBLANK(B21)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B26:B27">
-    <cfRule type="duplicateValues" dxfId="113" priority="1239"/>
-    <cfRule type="expression" dxfId="112" priority="1240" stopIfTrue="1">
+    <cfRule type="duplicateValues" dxfId="103" priority="1239"/>
+    <cfRule type="expression" dxfId="102" priority="1240" stopIfTrue="1">
       <formula>AND(COUNTIF($D$28:$D$37, B26)+COUNTIF($D$16:$D$16, B26)&gt;1,NOT(ISBLANK(B26)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="111" priority="1241" stopIfTrue="1">
+    <cfRule type="expression" dxfId="101" priority="1241" stopIfTrue="1">
       <formula>AND(COUNTIF($D$28:$D$65380, B26)+COUNTIF($D$1:$D$16, B26)&gt;1,NOT(ISBLANK(B26)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="110" priority="1242" stopIfTrue="1">
+    <cfRule type="expression" dxfId="100" priority="1242" stopIfTrue="1">
       <formula>AND(COUNTIF($D$17:$D$65380, B26)+COUNTIF($D$1:$D$16, B26)&gt;1,NOT(ISBLANK(B26)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="109" priority="1243" stopIfTrue="1">
+    <cfRule type="expression" dxfId="99" priority="1243" stopIfTrue="1">
       <formula>AND(COUNTIF($D$1:$D$123, B26)+COUNTIF($D$142:$D$65380, B26)&gt;1,NOT(ISBLANK(B26)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="108" priority="1244" stopIfTrue="1">
+    <cfRule type="expression" dxfId="98" priority="1245" stopIfTrue="1">
       <formula>AND(COUNTIF($D$1:$D$191, B26)+COUNTIF($D$214:$D$65380, B26)&gt;1,NOT(ISBLANK(B26)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="107" priority="1245" stopIfTrue="1">
+    <cfRule type="expression" dxfId="97" priority="1246" stopIfTrue="1">
       <formula>AND(COUNTIF($D$1:$D$191, B26)+COUNTIF($D$214:$D$65380, B26)&gt;1,NOT(ISBLANK(B26)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="106" priority="1246" stopIfTrue="1">
+    <cfRule type="expression" dxfId="96" priority="1247" stopIfTrue="1">
+      <formula>AND(COUNTIF($D$474:$D$65380, B26)+COUNTIF($D$454:$D$455, B26)+COUNTIF($D$416:$D$417, B26)+COUNTIF($D$374:$D$377, B26)+COUNTIF($D$351:$D$352, B26)+COUNTIF($D$324:$D$325, B26)+COUNTIF($D$303:$D$303, B26)+COUNTIF($D$288:$D$289, B26)+COUNTIF($D$263:$D$263, B26)+COUNTIF($D$252:$D$253, B26)+COUNTIF($D$233:$D$234, B26)+COUNTIF($D$51:$D$218, B26)+COUNTIF($D$219:$D$220, B26)+COUNTIF($D$1:$D$50, B26)&gt;1,NOT(ISBLANK(B26)))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="95" priority="1244" stopIfTrue="1">
       <formula>AND(COUNTIF($D$1:$D$191, B26)+COUNTIF($D$214:$D$65380, B26)&gt;1,NOT(ISBLANK(B26)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="105" priority="1247" stopIfTrue="1">
-      <formula>AND(COUNTIF($D$474:$D$65380, B26)+COUNTIF($D$454:$D$455, B26)+COUNTIF($D$416:$D$417, B26)+COUNTIF($D$374:$D$377, B26)+COUNTIF($D$351:$D$352, B26)+COUNTIF($D$324:$D$325, B26)+COUNTIF($D$303:$D$303, B26)+COUNTIF($D$288:$D$289, B26)+COUNTIF($D$263:$D$263, B26)+COUNTIF($D$252:$D$253, B26)+COUNTIF($D$233:$D$234, B26)+COUNTIF($D$51:$D$218, B26)+COUNTIF($D$219:$D$220, B26)+COUNTIF($D$1:$D$50, B26)&gt;1,NOT(ISBLANK(B26)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B27">
-    <cfRule type="duplicateValues" dxfId="104" priority="22"/>
-    <cfRule type="duplicateValues" dxfId="103" priority="23"/>
-    <cfRule type="duplicateValues" dxfId="102" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="94" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="93" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="92" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28">
-    <cfRule type="duplicateValues" dxfId="101" priority="1190"/>
-    <cfRule type="duplicateValues" dxfId="100" priority="1191"/>
-    <cfRule type="duplicateValues" dxfId="99" priority="1192"/>
+    <cfRule type="duplicateValues" dxfId="91" priority="1190"/>
+    <cfRule type="duplicateValues" dxfId="90" priority="1191"/>
+    <cfRule type="duplicateValues" dxfId="89" priority="1192"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B29:B1048576 B1:B20">
-    <cfRule type="duplicateValues" dxfId="98" priority="347"/>
+    <cfRule type="duplicateValues" dxfId="88" priority="347"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="L4">
-    <cfRule type="expression" dxfId="97" priority="1220" stopIfTrue="1">
+    <cfRule type="expression" dxfId="87" priority="1221" stopIfTrue="1">
+      <formula>AND(COUNTIF($C$1:$C$65460, L4)+COUNTIF(#REF!, L4)&gt;1,NOT(ISBLANK(L4)))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="86" priority="1220" stopIfTrue="1">
       <formula>AND(COUNTIF($C$314:$C$65460, L4)+COUNTIF($C$294:$C$295, L4)+COUNTIF($C$256:$C$257, L4)+COUNTIF($C$214:$C$217, L4)+COUNTIF($C$191:$C$192, L4)+COUNTIF($C$164:$C$165, L4)+COUNTIF($C$143:$C$143, L4)+COUNTIF($C$128:$C$129, L4)+COUNTIF($C$103:$C$103, L4)+COUNTIF($C$92:$C$93, L4)+COUNTIF($C$73:$C$74, L4)+COUNTIF($C$29:$C$56, L4)+COUNTIF($C$58:$C$60, L4)+COUNTIF($C$1:$C$27, L4)&gt;1,NOT(ISBLANK(L4)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="96" priority="1221" stopIfTrue="1">
-      <formula>AND(COUNTIF($C$1:$C$65460, L4)+COUNTIF(#REF!, L4)&gt;1,NOT(ISBLANK(L4)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M4">
-    <cfRule type="expression" dxfId="95" priority="1222" stopIfTrue="1">
+    <cfRule type="expression" dxfId="85" priority="1223" stopIfTrue="1">
+      <formula>AND(COUNTIF($D$314:$D$65460, M4)+COUNTIF(#REF!, M4)+COUNTIF($D$1:$D$27, M4)+COUNTIF($D$294:$D$295, M4)+COUNTIF($D$256:$D$257, M4)+COUNTIF($D$214:$D$217, M4)+COUNTIF($D$191:$D$192, M4)+COUNTIF($D$164:$D$165, M4)+COUNTIF($D$143:$D$143, M4)+COUNTIF($D$128:$D$129, M4)+COUNTIF($D$103:$D$103, M4)+COUNTIF($D$92:$D$93, M4)+COUNTIF($D$73:$D$74, M4)+COUNTIF($D$58:$D$60, M4)&gt;1,NOT(ISBLANK(M4)))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="84" priority="1224" stopIfTrue="1">
+      <formula>AND(COUNTIF($D$294:$D$65460, M4)+COUNTIF($D$1:$D$27, M4)+COUNTIF($D$256:$D$257, M4)+COUNTIF(#REF!, M4)+COUNTIF($D$214:$D$217, M4)+COUNTIF($D$191:$D$192, M4)+COUNTIF($D$164:$D$165, M4)+COUNTIF($D$143:$D$143, M4)+COUNTIF($D$128:$D$129, M4)+COUNTIF($D$103:$D$103, M4)+COUNTIF($D$92:$D$93, M4)+COUNTIF($D$73:$D$74, M4)+COUNTIF($D$58:$D$60, M4)&gt;1,NOT(ISBLANK(M4)))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="83" priority="1225" stopIfTrue="1">
+      <formula>AND(COUNTIF($D$256:$D$65460, M4)+COUNTIF($D$1:$D$27, M4)+COUNTIF(#REF!, M4)+COUNTIF($D$214:$D$217, M4)+COUNTIF($D$191:$D$192, M4)+COUNTIF($D$164:$D$165, M4)+COUNTIF($D$143:$D$143, M4)+COUNTIF($D$128:$D$129, M4)+COUNTIF($D$103:$D$103, M4)+COUNTIF($D$92:$D$93, M4)+COUNTIF($D$73:$D$74, M4)+COUNTIF($D$58:$D$60, M4)&gt;1,NOT(ISBLANK(M4)))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="82" priority="1226" stopIfTrue="1">
+      <formula>AND(COUNTIF($D$214:$D$65460, M4)+COUNTIF(#REF!, M4)+COUNTIF($D$1:$D$27, M4)+COUNTIF($D$191:$D$192, M4)+COUNTIF($D$164:$D$165, M4)+COUNTIF($D$143:$D$143, M4)+COUNTIF($D$128:$D$129, M4)+COUNTIF($D$103:$D$103, M4)+COUNTIF($D$92:$D$93, M4)+COUNTIF($D$73:$D$74, M4)+COUNTIF($D$58:$D$60, M4)&gt;1,NOT(ISBLANK(M4)))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="81" priority="1227" stopIfTrue="1">
+      <formula>AND(COUNTIF($D$214:$D$65460, M4)+COUNTIF($D$191:$D$192, M4)+COUNTIF($D$164:$D$165, M4)+COUNTIF($D$143:$D$143, M4)+COUNTIF($D$128:$D$129, M4)+COUNTIF($D$1:$D$27, M4)+COUNTIF(#REF!, M4)+COUNTIF($D$103:$D$103, M4)+COUNTIF($D$92:$D$93, M4)+COUNTIF(#REF!, M4)+COUNTIF($D$73:$D$74, M4)+COUNTIF($D$51:$D$51, M4)+COUNTIF($D$53:$D$60, M4)+COUNTIF(#REF!, M4)&gt;1,NOT(ISBLANK(M4)))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="80" priority="1228" stopIfTrue="1">
+      <formula>AND(COUNTIF($D$191:$D$65460, M4)+COUNTIF($D$164:$D$165, M4)+COUNTIF($D$143:$D$143, M4)+COUNTIF($D$128:$D$129, M4)+COUNTIF($D$1:$D$27, M4)+COUNTIF(#REF!, M4)+COUNTIF($D$103:$D$103, M4)+COUNTIF($D$92:$D$93, M4)+COUNTIF(#REF!, M4)+COUNTIF($D$73:$D$74, M4)+COUNTIF($D$51:$D$51, M4)+COUNTIF($D$53:$D$60, M4)+COUNTIF(#REF!, M4)&gt;1,NOT(ISBLANK(M4)))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="79" priority="1229" stopIfTrue="1">
+      <formula>AND(COUNTIF($F$369:$F$65454, M4)+COUNTIF($F$1:$F$27, M4)+COUNTIF(#REF!, M4)+COUNTIF($F$352:$F$353, M4)+COUNTIF($F$332:$F$333, M4)+COUNTIF($F$294:$F$295, M4)+COUNTIF($F$252:$F$255, M4)+COUNTIF($F$229:$F$230, M4)+COUNTIF($F$202:$F$203, M4)+COUNTIF($F$181:$F$181, M4)+COUNTIF($F$166:$F$167, M4)+COUNTIF($F$141:$F$141, M4)+COUNTIF($F$130:$F$131, M4)+COUNTIF($F$111:$F$112, M4)+COUNTIF($F$96:$F$98, M4)&gt;1,NOT(ISBLANK(M4)))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="78" priority="1230" stopIfTrue="1">
+      <formula>AND(COUNTIF($F$352:$F$65454, M4)+COUNTIF(#REF!, M4)+COUNTIF($F$1:$F$27, M4)+COUNTIF($F$332:$F$333, M4)+COUNTIF($F$294:$F$295, M4)+COUNTIF($F$252:$F$255, M4)+COUNTIF($F$229:$F$230, M4)+COUNTIF($F$202:$F$203, M4)+COUNTIF($F$181:$F$181, M4)+COUNTIF($F$166:$F$167, M4)+COUNTIF($F$141:$F$141, M4)+COUNTIF($F$130:$F$131, M4)+COUNTIF($F$111:$F$112, M4)+COUNTIF($F$96:$F$98, M4)&gt;1,NOT(ISBLANK(M4)))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="77" priority="1231" stopIfTrue="1">
+      <formula>AND(COUNTIF($F$332:$F$65454, M4)+COUNTIF($F$1:$F$27, M4)+COUNTIF($F$294:$F$295, M4)+COUNTIF(#REF!, M4)+COUNTIF($F$252:$F$255, M4)+COUNTIF($F$229:$F$230, M4)+COUNTIF($F$202:$F$203, M4)+COUNTIF($F$181:$F$181, M4)+COUNTIF($F$166:$F$167, M4)+COUNTIF($F$141:$F$141, M4)+COUNTIF($F$130:$F$131, M4)+COUNTIF($F$111:$F$112, M4)+COUNTIF($F$96:$F$98, M4)&gt;1,NOT(ISBLANK(M4)))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="76" priority="1232" stopIfTrue="1">
+      <formula>AND(COUNTIF($F$294:$F$65454, M4)+COUNTIF($F$1:$F$27, M4)+COUNTIF(#REF!, M4)+COUNTIF($F$252:$F$255, M4)+COUNTIF($F$229:$F$230, M4)+COUNTIF($F$202:$F$203, M4)+COUNTIF($F$181:$F$181, M4)+COUNTIF($F$166:$F$167, M4)+COUNTIF($F$141:$F$141, M4)+COUNTIF($F$130:$F$131, M4)+COUNTIF($F$111:$F$112, M4)+COUNTIF($F$96:$F$98, M4)&gt;1,NOT(ISBLANK(M4)))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="75" priority="1233" stopIfTrue="1">
+      <formula>AND(COUNTIF($F$252:$F$65454, M4)+COUNTIF(#REF!, M4)+COUNTIF($F$1:$F$27, M4)+COUNTIF($F$229:$F$230, M4)+COUNTIF($F$202:$F$203, M4)+COUNTIF($F$181:$F$181, M4)+COUNTIF($F$166:$F$167, M4)+COUNTIF($F$141:$F$141, M4)+COUNTIF($F$130:$F$131, M4)+COUNTIF($F$111:$F$112, M4)+COUNTIF($F$96:$F$98, M4)&gt;1,NOT(ISBLANK(M4)))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="74" priority="1234" stopIfTrue="1">
+      <formula>AND(COUNTIF($F$252:$F$65454, M4)+COUNTIF($F$229:$F$230, M4)+COUNTIF($F$202:$F$203, M4)+COUNTIF($F$181:$F$181, M4)+COUNTIF($F$166:$F$167, M4)+COUNTIF($F$1:$F$27, M4)+COUNTIF(#REF!, M4)+COUNTIF($F$141:$F$141, M4)+COUNTIF($F$130:$F$131, M4)+COUNTIF(#REF!, M4)+COUNTIF($F$111:$F$112, M4)+COUNTIF($F$89:$F$89, M4)+COUNTIF($F$91:$F$98, M4)+COUNTIF(#REF!, M4)&gt;1,NOT(ISBLANK(M4)))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="73" priority="1235" stopIfTrue="1">
+      <formula>AND(COUNTIF($F$229:$F$65454, M4)+COUNTIF($F$202:$F$203, M4)+COUNTIF($F$181:$F$181, M4)+COUNTIF($F$166:$F$167, M4)+COUNTIF($F$1:$F$27, M4)+COUNTIF(#REF!, M4)+COUNTIF($F$141:$F$141, M4)+COUNTIF($F$130:$F$131, M4)+COUNTIF(#REF!, M4)+COUNTIF($F$111:$F$112, M4)+COUNTIF($F$89:$F$89, M4)+COUNTIF($F$91:$F$98, M4)+COUNTIF(#REF!, M4)&gt;1,NOT(ISBLANK(M4)))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="72" priority="1222" stopIfTrue="1">
       <formula>AND(COUNTIF($D$331:$D$65460, M4)+COUNTIF($D$1:$D$27, M4)+COUNTIF(#REF!, M4)+COUNTIF($D$314:$D$315, M4)+COUNTIF($D$294:$D$295, M4)+COUNTIF($D$256:$D$257, M4)+COUNTIF($D$214:$D$217, M4)+COUNTIF($D$191:$D$192, M4)+COUNTIF($D$164:$D$165, M4)+COUNTIF($D$143:$D$143, M4)+COUNTIF($D$128:$D$129, M4)+COUNTIF($D$103:$D$103, M4)+COUNTIF($D$92:$D$93, M4)+COUNTIF($D$73:$D$74, M4)+COUNTIF($D$58:$D$60, M4)&gt;1,NOT(ISBLANK(M4)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="94" priority="1223" stopIfTrue="1">
-      <formula>AND(COUNTIF($D$314:$D$65460, M4)+COUNTIF(#REF!, M4)+COUNTIF($D$1:$D$27, M4)+COUNTIF($D$294:$D$295, M4)+COUNTIF($D$256:$D$257, M4)+COUNTIF($D$214:$D$217, M4)+COUNTIF($D$191:$D$192, M4)+COUNTIF($D$164:$D$165, M4)+COUNTIF($D$143:$D$143, M4)+COUNTIF($D$128:$D$129, M4)+COUNTIF($D$103:$D$103, M4)+COUNTIF($D$92:$D$93, M4)+COUNTIF($D$73:$D$74, M4)+COUNTIF($D$58:$D$60, M4)&gt;1,NOT(ISBLANK(M4)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="93" priority="1224" stopIfTrue="1">
-      <formula>AND(COUNTIF($D$294:$D$65460, M4)+COUNTIF($D$1:$D$27, M4)+COUNTIF($D$256:$D$257, M4)+COUNTIF(#REF!, M4)+COUNTIF($D$214:$D$217, M4)+COUNTIF($D$191:$D$192, M4)+COUNTIF($D$164:$D$165, M4)+COUNTIF($D$143:$D$143, M4)+COUNTIF($D$128:$D$129, M4)+COUNTIF($D$103:$D$103, M4)+COUNTIF($D$92:$D$93, M4)+COUNTIF($D$73:$D$74, M4)+COUNTIF($D$58:$D$60, M4)&gt;1,NOT(ISBLANK(M4)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="92" priority="1225" stopIfTrue="1">
-      <formula>AND(COUNTIF($D$256:$D$65460, M4)+COUNTIF($D$1:$D$27, M4)+COUNTIF(#REF!, M4)+COUNTIF($D$214:$D$217, M4)+COUNTIF($D$191:$D$192, M4)+COUNTIF($D$164:$D$165, M4)+COUNTIF($D$143:$D$143, M4)+COUNTIF($D$128:$D$129, M4)+COUNTIF($D$103:$D$103, M4)+COUNTIF($D$92:$D$93, M4)+COUNTIF($D$73:$D$74, M4)+COUNTIF($D$58:$D$60, M4)&gt;1,NOT(ISBLANK(M4)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="91" priority="1226" stopIfTrue="1">
-      <formula>AND(COUNTIF($D$214:$D$65460, M4)+COUNTIF(#REF!, M4)+COUNTIF($D$1:$D$27, M4)+COUNTIF($D$191:$D$192, M4)+COUNTIF($D$164:$D$165, M4)+COUNTIF($D$143:$D$143, M4)+COUNTIF($D$128:$D$129, M4)+COUNTIF($D$103:$D$103, M4)+COUNTIF($D$92:$D$93, M4)+COUNTIF($D$73:$D$74, M4)+COUNTIF($D$58:$D$60, M4)&gt;1,NOT(ISBLANK(M4)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="90" priority="1227" stopIfTrue="1">
-      <formula>AND(COUNTIF($D$214:$D$65460, M4)+COUNTIF($D$191:$D$192, M4)+COUNTIF($D$164:$D$165, M4)+COUNTIF($D$143:$D$143, M4)+COUNTIF($D$128:$D$129, M4)+COUNTIF($D$1:$D$27, M4)+COUNTIF(#REF!, M4)+COUNTIF($D$103:$D$103, M4)+COUNTIF($D$92:$D$93, M4)+COUNTIF(#REF!, M4)+COUNTIF($D$73:$D$74, M4)+COUNTIF($D$51:$D$51, M4)+COUNTIF($D$53:$D$60, M4)+COUNTIF(#REF!, M4)&gt;1,NOT(ISBLANK(M4)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="89" priority="1228" stopIfTrue="1">
-      <formula>AND(COUNTIF($D$191:$D$65460, M4)+COUNTIF($D$164:$D$165, M4)+COUNTIF($D$143:$D$143, M4)+COUNTIF($D$128:$D$129, M4)+COUNTIF($D$1:$D$27, M4)+COUNTIF(#REF!, M4)+COUNTIF($D$103:$D$103, M4)+COUNTIF($D$92:$D$93, M4)+COUNTIF(#REF!, M4)+COUNTIF($D$73:$D$74, M4)+COUNTIF($D$51:$D$51, M4)+COUNTIF($D$53:$D$60, M4)+COUNTIF(#REF!, M4)&gt;1,NOT(ISBLANK(M4)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="88" priority="1229" stopIfTrue="1">
-      <formula>AND(COUNTIF($F$369:$F$65454, M4)+COUNTIF($F$1:$F$27, M4)+COUNTIF(#REF!, M4)+COUNTIF($F$352:$F$353, M4)+COUNTIF($F$332:$F$333, M4)+COUNTIF($F$294:$F$295, M4)+COUNTIF($F$252:$F$255, M4)+COUNTIF($F$229:$F$230, M4)+COUNTIF($F$202:$F$203, M4)+COUNTIF($F$181:$F$181, M4)+COUNTIF($F$166:$F$167, M4)+COUNTIF($F$141:$F$141, M4)+COUNTIF($F$130:$F$131, M4)+COUNTIF($F$111:$F$112, M4)+COUNTIF($F$96:$F$98, M4)&gt;1,NOT(ISBLANK(M4)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="87" priority="1230" stopIfTrue="1">
-      <formula>AND(COUNTIF($F$352:$F$65454, M4)+COUNTIF(#REF!, M4)+COUNTIF($F$1:$F$27, M4)+COUNTIF($F$332:$F$333, M4)+COUNTIF($F$294:$F$295, M4)+COUNTIF($F$252:$F$255, M4)+COUNTIF($F$229:$F$230, M4)+COUNTIF($F$202:$F$203, M4)+COUNTIF($F$181:$F$181, M4)+COUNTIF($F$166:$F$167, M4)+COUNTIF($F$141:$F$141, M4)+COUNTIF($F$130:$F$131, M4)+COUNTIF($F$111:$F$112, M4)+COUNTIF($F$96:$F$98, M4)&gt;1,NOT(ISBLANK(M4)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="86" priority="1231" stopIfTrue="1">
-      <formula>AND(COUNTIF($F$332:$F$65454, M4)+COUNTIF($F$1:$F$27, M4)+COUNTIF($F$294:$F$295, M4)+COUNTIF(#REF!, M4)+COUNTIF($F$252:$F$255, M4)+COUNTIF($F$229:$F$230, M4)+COUNTIF($F$202:$F$203, M4)+COUNTIF($F$181:$F$181, M4)+COUNTIF($F$166:$F$167, M4)+COUNTIF($F$141:$F$141, M4)+COUNTIF($F$130:$F$131, M4)+COUNTIF($F$111:$F$112, M4)+COUNTIF($F$96:$F$98, M4)&gt;1,NOT(ISBLANK(M4)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="85" priority="1232" stopIfTrue="1">
-      <formula>AND(COUNTIF($F$294:$F$65454, M4)+COUNTIF($F$1:$F$27, M4)+COUNTIF(#REF!, M4)+COUNTIF($F$252:$F$255, M4)+COUNTIF($F$229:$F$230, M4)+COUNTIF($F$202:$F$203, M4)+COUNTIF($F$181:$F$181, M4)+COUNTIF($F$166:$F$167, M4)+COUNTIF($F$141:$F$141, M4)+COUNTIF($F$130:$F$131, M4)+COUNTIF($F$111:$F$112, M4)+COUNTIF($F$96:$F$98, M4)&gt;1,NOT(ISBLANK(M4)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="84" priority="1233" stopIfTrue="1">
-      <formula>AND(COUNTIF($F$252:$F$65454, M4)+COUNTIF(#REF!, M4)+COUNTIF($F$1:$F$27, M4)+COUNTIF($F$229:$F$230, M4)+COUNTIF($F$202:$F$203, M4)+COUNTIF($F$181:$F$181, M4)+COUNTIF($F$166:$F$167, M4)+COUNTIF($F$141:$F$141, M4)+COUNTIF($F$130:$F$131, M4)+COUNTIF($F$111:$F$112, M4)+COUNTIF($F$96:$F$98, M4)&gt;1,NOT(ISBLANK(M4)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="83" priority="1234" stopIfTrue="1">
-      <formula>AND(COUNTIF($F$252:$F$65454, M4)+COUNTIF($F$229:$F$230, M4)+COUNTIF($F$202:$F$203, M4)+COUNTIF($F$181:$F$181, M4)+COUNTIF($F$166:$F$167, M4)+COUNTIF($F$1:$F$27, M4)+COUNTIF(#REF!, M4)+COUNTIF($F$141:$F$141, M4)+COUNTIF($F$130:$F$131, M4)+COUNTIF(#REF!, M4)+COUNTIF($F$111:$F$112, M4)+COUNTIF($F$89:$F$89, M4)+COUNTIF($F$91:$F$98, M4)+COUNTIF(#REF!, M4)&gt;1,NOT(ISBLANK(M4)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="82" priority="1235" stopIfTrue="1">
-      <formula>AND(COUNTIF($F$229:$F$65454, M4)+COUNTIF($F$202:$F$203, M4)+COUNTIF($F$181:$F$181, M4)+COUNTIF($F$166:$F$167, M4)+COUNTIF($F$1:$F$27, M4)+COUNTIF(#REF!, M4)+COUNTIF($F$141:$F$141, M4)+COUNTIF($F$130:$F$131, M4)+COUNTIF(#REF!, M4)+COUNTIF($F$111:$F$112, M4)+COUNTIF($F$89:$F$89, M4)+COUNTIF($F$91:$F$98, M4)+COUNTIF(#REF!, M4)&gt;1,NOT(ISBLANK(M4)))</formula>
     </cfRule>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
@@ -4649,20 +4786,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{240DD7AA-E2CC-4325-BB1A-65DAE33EC798}">
   <dimension ref="B2:R6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="12.7109375" customWidth="1"/>
-    <col min="5" max="5" width="13.28515625" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" customWidth="1"/>
-    <col min="7" max="7" width="13.5703125" customWidth="1"/>
+    <col min="2" max="2" width="12.7265625" customWidth="1"/>
+    <col min="5" max="5" width="13.26953125" customWidth="1"/>
+    <col min="6" max="6" width="14.7265625" customWidth="1"/>
+    <col min="7" max="7" width="13.54296875" customWidth="1"/>
     <col min="8" max="15" width="0" hidden="1" customWidth="1"/>
-    <col min="16" max="16" width="16.140625" customWidth="1"/>
+    <col min="16" max="16" width="16.1796875" customWidth="1"/>
     <col min="17" max="17" width="0" hidden="1" customWidth="1"/>
     <col min="18" max="18" width="27" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="2:18" ht="57" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="3" spans="2:18" ht="56" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B3" s="56" t="s">
         <v>52</v>
       </c>
@@ -4715,7 +4852,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="4" spans="2:18" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:18" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B4" s="60" t="s">
         <v>68</v>
       </c>
@@ -4758,11 +4895,11 @@
       <c r="Q4" s="70">
         <v>0</v>
       </c>
-      <c r="R4" s="153" t="s">
+      <c r="R4" s="182" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="5" spans="2:18" ht="30" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:18" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B5" s="60" t="s">
         <v>68</v>
       </c>
@@ -4801,14 +4938,14 @@
       <c r="Q5" s="70">
         <v>0</v>
       </c>
-      <c r="R5" s="154"/>
-    </row>
-    <row r="6" spans="2:18" s="75" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="155" t="s">
+      <c r="R5" s="183"/>
+    </row>
+    <row r="6" spans="2:18" s="75" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B6" s="184" t="s">
         <v>29</v>
       </c>
-      <c r="C6" s="156"/>
-      <c r="D6" s="157"/>
+      <c r="C6" s="185"/>
+      <c r="D6" s="186"/>
       <c r="E6" s="73">
         <v>160</v>
       </c>
@@ -4835,7 +4972,7 @@
     <mergeCell ref="B6:D6"/>
   </mergeCells>
   <conditionalFormatting sqref="E4:E5">
-    <cfRule type="containsText" dxfId="81" priority="1" operator="containsText" text="proto">
+    <cfRule type="containsText" dxfId="71" priority="1" operator="containsText" text="proto">
       <formula>NOT(ISERROR(SEARCH("proto",E4)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4849,391 +4986,391 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AK31"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="13" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="3.42578125" style="170" customWidth="1"/>
-    <col min="2" max="2" width="13.42578125" style="131" customWidth="1"/>
-    <col min="3" max="3" width="11.28515625" style="131" customWidth="1"/>
-    <col min="4" max="4" width="12.5703125" style="170" customWidth="1"/>
-    <col min="5" max="5" width="23.28515625" style="170" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.7109375" style="170" customWidth="1"/>
-    <col min="7" max="7" width="16.85546875" style="170" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="21.140625" style="170" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.7109375" style="170" customWidth="1"/>
-    <col min="10" max="10" width="11.85546875" style="170" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="170" customWidth="1"/>
-    <col min="12" max="12" width="16.140625" style="131" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.7109375" style="131" customWidth="1"/>
-    <col min="14" max="14" width="13.140625" style="131" customWidth="1"/>
-    <col min="15" max="15" width="16.7109375" style="170" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="18.42578125" style="131" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="15.5703125" style="131" customWidth="1"/>
-    <col min="19" max="19" width="3.140625" style="131" customWidth="1"/>
-    <col min="20" max="20" width="28.140625" style="131" customWidth="1"/>
-    <col min="21" max="21" width="3.140625" style="131" customWidth="1"/>
-    <col min="22" max="27" width="8.7109375" style="131" customWidth="1"/>
-    <col min="28" max="28" width="3.140625" style="131" customWidth="1"/>
-    <col min="29" max="29" width="14.28515625" style="131" customWidth="1"/>
-    <col min="30" max="30" width="13.28515625" style="131" customWidth="1"/>
-    <col min="31" max="32" width="10.7109375" style="131" customWidth="1"/>
-    <col min="33" max="33" width="11.28515625" style="131" customWidth="1"/>
-    <col min="34" max="34" width="8.140625" style="131" customWidth="1"/>
-    <col min="35" max="35" width="38.140625" style="131" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="131"/>
+    <col min="1" max="1" width="3.453125" style="140" customWidth="1"/>
+    <col min="2" max="2" width="13.453125" style="131" customWidth="1"/>
+    <col min="3" max="3" width="11.26953125" style="131" customWidth="1"/>
+    <col min="4" max="4" width="12.54296875" style="140" customWidth="1"/>
+    <col min="5" max="5" width="23.26953125" style="140" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.7265625" style="140" customWidth="1"/>
+    <col min="7" max="7" width="16.81640625" style="140" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.1796875" style="140" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.7265625" style="140" customWidth="1"/>
+    <col min="10" max="10" width="11.81640625" style="140" customWidth="1"/>
+    <col min="11" max="11" width="14.7265625" style="140" customWidth="1"/>
+    <col min="12" max="12" width="16.1796875" style="131" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.7265625" style="131" customWidth="1"/>
+    <col min="14" max="14" width="13.1796875" style="131" customWidth="1"/>
+    <col min="15" max="15" width="16.7265625" style="140" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="18.453125" style="131" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="15.54296875" style="131" customWidth="1"/>
+    <col min="19" max="19" width="3.1796875" style="131" customWidth="1"/>
+    <col min="20" max="20" width="28.1796875" style="131" customWidth="1"/>
+    <col min="21" max="21" width="3.1796875" style="131" customWidth="1"/>
+    <col min="22" max="27" width="8.7265625" style="131" customWidth="1"/>
+    <col min="28" max="28" width="3.1796875" style="131" customWidth="1"/>
+    <col min="29" max="29" width="14.26953125" style="131" customWidth="1"/>
+    <col min="30" max="30" width="13.26953125" style="131" customWidth="1"/>
+    <col min="31" max="32" width="10.7265625" style="131" customWidth="1"/>
+    <col min="33" max="33" width="11.26953125" style="131" customWidth="1"/>
+    <col min="34" max="34" width="8.1796875" style="131" customWidth="1"/>
+    <col min="35" max="35" width="38.1796875" style="131" customWidth="1"/>
+    <col min="36" max="16384" width="9.1796875" style="131"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="188" t="s">
+    <row r="1" spans="1:37" ht="39" x14ac:dyDescent="0.35">
+      <c r="A1" s="158" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="188" t="s">
+      <c r="B1" s="158" t="s">
         <v>113</v>
       </c>
-      <c r="C1" s="188" t="s">
+      <c r="C1" s="158" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="188" t="s">
+      <c r="D1" s="158" t="s">
         <v>108</v>
       </c>
-      <c r="E1" s="188" t="s">
+      <c r="E1" s="158" t="s">
         <v>109</v>
       </c>
-      <c r="F1" s="188" t="s">
+      <c r="F1" s="158" t="s">
         <v>103</v>
       </c>
-      <c r="G1" s="188" t="s">
+      <c r="G1" s="158" t="s">
         <v>104</v>
       </c>
-      <c r="H1" s="188" t="s">
+      <c r="H1" s="158" t="s">
         <v>105</v>
       </c>
-      <c r="I1" s="188" t="s">
+      <c r="I1" s="158" t="s">
         <v>106</v>
       </c>
-      <c r="J1" s="189" t="s">
+      <c r="J1" s="159" t="s">
         <v>114</v>
       </c>
-      <c r="K1" s="189" t="s">
+      <c r="K1" s="159" t="s">
         <v>111</v>
       </c>
-      <c r="L1" s="189" t="s">
+      <c r="L1" s="159" t="s">
         <v>112</v>
       </c>
-      <c r="M1" s="189" t="s">
+      <c r="M1" s="159" t="s">
         <v>38</v>
       </c>
-      <c r="N1" s="189" t="s">
+      <c r="N1" s="159" t="s">
         <v>39</v>
       </c>
-      <c r="O1" s="188" t="s">
+      <c r="O1" s="158" t="s">
         <v>110</v>
       </c>
-      <c r="P1" s="180" t="s">
+      <c r="P1" s="150" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="2" spans="1:37" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="165">
+    <row r="2" spans="1:37" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="135">
         <v>1</v>
       </c>
-      <c r="B2" s="181" t="s">
+      <c r="B2" s="151" t="s">
         <v>116</v>
       </c>
-      <c r="C2" s="163" t="s">
+      <c r="C2" s="133" t="s">
         <v>117</v>
       </c>
-      <c r="D2" s="166">
+      <c r="D2" s="136">
         <v>31.99</v>
       </c>
-      <c r="E2" s="168" t="s">
+      <c r="E2" s="138" t="s">
         <v>179</v>
       </c>
-      <c r="F2" s="169">
+      <c r="F2" s="139">
         <v>27</v>
       </c>
-      <c r="G2" s="168" t="s">
+      <c r="G2" s="138" t="s">
         <v>167</v>
       </c>
-      <c r="H2" s="165" t="s">
+      <c r="H2" s="135" t="s">
         <v>169</v>
       </c>
-      <c r="I2" s="168" t="s">
+      <c r="I2" s="138" t="s">
         <v>107</v>
       </c>
       <c r="J2" s="85" t="s">
         <v>177</v>
       </c>
-      <c r="K2" s="165" t="s">
+      <c r="K2" s="135" t="s">
         <v>175</v>
       </c>
-      <c r="L2" s="185">
+      <c r="L2" s="155">
         <v>45966</v>
       </c>
-      <c r="M2" s="185">
+      <c r="M2" s="155">
         <f>L2+10</f>
         <v>45976</v>
       </c>
-      <c r="N2" s="185">
+      <c r="N2" s="155">
         <f>L2+5</f>
         <v>45971</v>
       </c>
-      <c r="O2" s="183">
+      <c r="O2" s="153">
         <v>292211</v>
       </c>
       <c r="P2" s="100"/>
     </row>
-    <row r="3" spans="1:37" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="165">
+    <row r="3" spans="1:37" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="135">
         <v>2</v>
       </c>
-      <c r="B3" s="162" t="s">
+      <c r="B3" s="132" t="s">
         <v>118</v>
       </c>
-      <c r="C3" s="163" t="s">
+      <c r="C3" s="133" t="s">
         <v>119</v>
       </c>
-      <c r="D3" s="164">
+      <c r="D3" s="134">
         <v>37.716900000000003</v>
       </c>
-      <c r="E3" s="168" t="s">
+      <c r="E3" s="138" t="s">
         <v>179</v>
       </c>
-      <c r="F3" s="171"/>
-      <c r="G3" s="168" t="s">
+      <c r="F3" s="141"/>
+      <c r="G3" s="138" t="s">
         <v>167</v>
       </c>
-      <c r="H3" s="165" t="s">
+      <c r="H3" s="135" t="s">
         <v>169</v>
       </c>
-      <c r="I3" s="168" t="s">
+      <c r="I3" s="138" t="s">
         <v>107</v>
       </c>
       <c r="J3" s="85" t="str">
         <f t="shared" ref="J3" si="0">I3</f>
         <v>No</v>
       </c>
-      <c r="K3" s="184">
+      <c r="K3" s="154">
         <v>45966</v>
       </c>
-      <c r="L3" s="184">
+      <c r="L3" s="154">
         <v>45968</v>
       </c>
-      <c r="M3" s="185">
+      <c r="M3" s="155">
         <f t="shared" ref="M3:M7" si="1">L3+10</f>
         <v>45978</v>
       </c>
-      <c r="N3" s="185">
+      <c r="N3" s="155">
         <f t="shared" ref="N3:N31" si="2">L3+5</f>
         <v>45973</v>
       </c>
-      <c r="O3" s="183">
+      <c r="O3" s="153">
         <v>347642</v>
       </c>
       <c r="P3" s="100"/>
-      <c r="Q3" s="172"/>
-      <c r="R3" s="172"/>
-      <c r="T3" s="173"/>
-      <c r="V3" s="172"/>
-      <c r="W3" s="172"/>
-      <c r="X3" s="172"/>
-      <c r="Y3" s="172"/>
-      <c r="Z3" s="172"/>
-      <c r="AA3" s="172"/>
-      <c r="AC3" s="172"/>
-      <c r="AD3" s="172"/>
-      <c r="AE3" s="172"/>
-      <c r="AF3" s="172"/>
-      <c r="AG3" s="172"/>
-      <c r="AH3" s="172"/>
-      <c r="AI3" s="174"/>
-    </row>
-    <row r="4" spans="1:37" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="165">
+      <c r="Q3" s="142"/>
+      <c r="R3" s="142"/>
+      <c r="T3" s="143"/>
+      <c r="V3" s="142"/>
+      <c r="W3" s="142"/>
+      <c r="X3" s="142"/>
+      <c r="Y3" s="142"/>
+      <c r="Z3" s="142"/>
+      <c r="AA3" s="142"/>
+      <c r="AC3" s="142"/>
+      <c r="AD3" s="142"/>
+      <c r="AE3" s="142"/>
+      <c r="AF3" s="142"/>
+      <c r="AG3" s="142"/>
+      <c r="AH3" s="142"/>
+      <c r="AI3" s="144"/>
+    </row>
+    <row r="4" spans="1:37" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="135">
         <v>3</v>
       </c>
-      <c r="B4" s="165" t="s">
+      <c r="B4" s="135" t="s">
         <v>120</v>
       </c>
-      <c r="C4" s="163" t="s">
+      <c r="C4" s="133" t="s">
         <v>121</v>
       </c>
-      <c r="D4" s="164">
+      <c r="D4" s="134">
         <v>77.319999999999993</v>
       </c>
-      <c r="E4" s="168" t="s">
+      <c r="E4" s="138" t="s">
         <v>179</v>
       </c>
-      <c r="F4" s="168"/>
-      <c r="G4" s="168" t="s">
+      <c r="F4" s="138"/>
+      <c r="G4" s="138" t="s">
         <v>167</v>
       </c>
-      <c r="H4" s="165" t="s">
+      <c r="H4" s="135" t="s">
         <v>169</v>
       </c>
-      <c r="I4" s="168" t="s">
+      <c r="I4" s="138" t="s">
         <v>107</v>
       </c>
       <c r="J4" s="85" t="str">
         <f t="shared" ref="J4:J31" si="3">I4</f>
         <v>No</v>
       </c>
-      <c r="K4" s="184">
+      <c r="K4" s="154">
         <v>45969</v>
       </c>
-      <c r="L4" s="184">
+      <c r="L4" s="154">
         <v>45972</v>
       </c>
-      <c r="M4" s="185">
+      <c r="M4" s="155">
         <f t="shared" si="1"/>
         <v>45982</v>
       </c>
-      <c r="N4" s="185">
+      <c r="N4" s="155">
         <f t="shared" si="2"/>
         <v>45977</v>
       </c>
-      <c r="O4" s="183">
+      <c r="O4" s="153">
         <v>708468.86</v>
       </c>
       <c r="P4" s="100"/>
-      <c r="Q4" s="175"/>
-      <c r="R4" s="174"/>
-      <c r="T4" s="173"/>
-      <c r="V4" s="172"/>
-      <c r="W4" s="172"/>
-      <c r="X4" s="172"/>
-      <c r="Y4" s="172"/>
-      <c r="Z4" s="172"/>
-      <c r="AA4" s="174"/>
-      <c r="AC4" s="172"/>
-      <c r="AD4" s="172"/>
-      <c r="AE4" s="172"/>
-      <c r="AF4" s="172"/>
-      <c r="AG4" s="172"/>
-      <c r="AH4" s="174"/>
-      <c r="AI4" s="174"/>
-    </row>
-    <row r="5" spans="1:37" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="165">
+      <c r="Q4" s="145"/>
+      <c r="R4" s="144"/>
+      <c r="T4" s="143"/>
+      <c r="V4" s="142"/>
+      <c r="W4" s="142"/>
+      <c r="X4" s="142"/>
+      <c r="Y4" s="142"/>
+      <c r="Z4" s="142"/>
+      <c r="AA4" s="144"/>
+      <c r="AC4" s="142"/>
+      <c r="AD4" s="142"/>
+      <c r="AE4" s="142"/>
+      <c r="AF4" s="142"/>
+      <c r="AG4" s="142"/>
+      <c r="AH4" s="144"/>
+      <c r="AI4" s="144"/>
+    </row>
+    <row r="5" spans="1:37" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="135">
         <v>4</v>
       </c>
-      <c r="B5" s="165" t="s">
+      <c r="B5" s="135" t="s">
         <v>122</v>
       </c>
-      <c r="C5" s="163" t="s">
+      <c r="C5" s="133" t="s">
         <v>123</v>
       </c>
-      <c r="D5" s="164">
+      <c r="D5" s="134">
         <v>33.380000000000003</v>
       </c>
-      <c r="E5" s="168" t="s">
+      <c r="E5" s="138" t="s">
         <v>179</v>
       </c>
-      <c r="F5" s="171"/>
-      <c r="G5" s="168" t="s">
+      <c r="F5" s="141"/>
+      <c r="G5" s="138" t="s">
         <v>167</v>
       </c>
-      <c r="H5" s="165" t="s">
+      <c r="H5" s="135" t="s">
         <v>169</v>
       </c>
-      <c r="I5" s="168" t="s">
+      <c r="I5" s="138" t="s">
         <v>107</v>
       </c>
       <c r="J5" s="85" t="str">
         <f t="shared" si="3"/>
         <v>No</v>
       </c>
-      <c r="K5" s="184">
+      <c r="K5" s="154">
         <v>45973</v>
       </c>
-      <c r="L5" s="184">
+      <c r="L5" s="154">
         <v>45975</v>
       </c>
-      <c r="M5" s="185">
+      <c r="M5" s="155">
         <f t="shared" si="1"/>
         <v>45985</v>
       </c>
-      <c r="N5" s="185">
+      <c r="N5" s="155">
         <f t="shared" si="2"/>
         <v>45980</v>
       </c>
-      <c r="O5" s="183">
+      <c r="O5" s="153">
         <v>307108</v>
       </c>
       <c r="P5" s="100"/>
-      <c r="Q5" s="176"/>
-      <c r="R5" s="176"/>
-      <c r="T5" s="177"/>
-      <c r="V5" s="172"/>
-      <c r="W5" s="172"/>
-      <c r="X5" s="172"/>
-      <c r="Y5" s="172"/>
-      <c r="Z5" s="172"/>
-      <c r="AA5" s="176"/>
-      <c r="AC5" s="172"/>
-      <c r="AD5" s="172"/>
-      <c r="AE5" s="172"/>
-      <c r="AF5" s="172"/>
-      <c r="AG5" s="172"/>
-      <c r="AH5" s="176"/>
-      <c r="AI5" s="176"/>
-    </row>
-    <row r="6" spans="1:37" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="165">
+      <c r="Q5" s="146"/>
+      <c r="R5" s="146"/>
+      <c r="T5" s="147"/>
+      <c r="V5" s="142"/>
+      <c r="W5" s="142"/>
+      <c r="X5" s="142"/>
+      <c r="Y5" s="142"/>
+      <c r="Z5" s="142"/>
+      <c r="AA5" s="146"/>
+      <c r="AC5" s="142"/>
+      <c r="AD5" s="142"/>
+      <c r="AE5" s="142"/>
+      <c r="AF5" s="142"/>
+      <c r="AG5" s="142"/>
+      <c r="AH5" s="146"/>
+      <c r="AI5" s="146"/>
+    </row>
+    <row r="6" spans="1:37" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="135">
         <v>5</v>
       </c>
-      <c r="B6" s="165" t="s">
+      <c r="B6" s="135" t="s">
         <v>124</v>
       </c>
-      <c r="C6" s="163" t="s">
+      <c r="C6" s="133" t="s">
         <v>125</v>
       </c>
-      <c r="D6" s="164">
+      <c r="D6" s="134">
         <v>58.93</v>
       </c>
-      <c r="E6" s="168" t="s">
+      <c r="E6" s="138" t="s">
         <v>179</v>
       </c>
-      <c r="F6" s="168"/>
-      <c r="G6" s="168" t="s">
+      <c r="F6" s="138"/>
+      <c r="G6" s="138" t="s">
         <v>167</v>
       </c>
-      <c r="H6" s="165" t="s">
+      <c r="H6" s="135" t="s">
         <v>169</v>
       </c>
-      <c r="I6" s="168" t="s">
+      <c r="I6" s="138" t="s">
         <v>107</v>
       </c>
       <c r="J6" s="85" t="str">
         <f t="shared" si="3"/>
         <v>No</v>
       </c>
-      <c r="K6" s="184">
+      <c r="K6" s="154">
         <v>45979</v>
       </c>
-      <c r="L6" s="184">
+      <c r="L6" s="154">
         <v>45985</v>
       </c>
-      <c r="M6" s="185">
+      <c r="M6" s="155">
         <f t="shared" si="1"/>
         <v>45995</v>
       </c>
-      <c r="N6" s="185">
+      <c r="N6" s="155">
         <f t="shared" si="2"/>
         <v>45990</v>
       </c>
-      <c r="O6" s="183">
+      <c r="O6" s="153">
         <v>530631.65</v>
       </c>
       <c r="P6" s="100"/>
       <c r="Q6" s="127"/>
       <c r="R6" s="127"/>
-      <c r="T6" s="178"/>
-      <c r="V6" s="179"/>
-      <c r="W6" s="179"/>
-      <c r="X6" s="179"/>
-      <c r="Y6" s="179"/>
-      <c r="Z6" s="179"/>
-      <c r="AA6" s="179"/>
+      <c r="T6" s="148"/>
+      <c r="V6" s="149"/>
+      <c r="W6" s="149"/>
+      <c r="X6" s="149"/>
+      <c r="Y6" s="149"/>
+      <c r="Z6" s="149"/>
+      <c r="AA6" s="149"/>
       <c r="AC6" s="128"/>
       <c r="AD6" s="128"/>
       <c r="AE6" s="128"/>
@@ -5242,63 +5379,63 @@
       <c r="AH6" s="129"/>
       <c r="AI6" s="130"/>
     </row>
-    <row r="7" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="165">
+    <row r="7" spans="1:37" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="135">
         <v>6</v>
       </c>
-      <c r="B7" s="165" t="s">
+      <c r="B7" s="135" t="s">
         <v>126</v>
       </c>
-      <c r="C7" s="163" t="s">
+      <c r="C7" s="133" t="s">
         <v>125</v>
       </c>
-      <c r="D7" s="164">
+      <c r="D7" s="134">
         <v>58.93</v>
       </c>
-      <c r="E7" s="168" t="s">
+      <c r="E7" s="138" t="s">
         <v>179</v>
       </c>
-      <c r="F7" s="171"/>
-      <c r="G7" s="168" t="s">
+      <c r="F7" s="141"/>
+      <c r="G7" s="138" t="s">
         <v>167</v>
       </c>
-      <c r="H7" s="165" t="s">
+      <c r="H7" s="135" t="s">
         <v>169</v>
       </c>
-      <c r="I7" s="168" t="s">
+      <c r="I7" s="138" t="s">
         <v>107</v>
       </c>
       <c r="J7" s="85" t="str">
         <f t="shared" si="3"/>
         <v>No</v>
       </c>
-      <c r="K7" s="184">
+      <c r="K7" s="154">
         <v>45986</v>
       </c>
-      <c r="L7" s="184">
+      <c r="L7" s="154">
         <v>45991</v>
       </c>
-      <c r="M7" s="185">
+      <c r="M7" s="155">
         <f t="shared" si="1"/>
         <v>46001</v>
       </c>
-      <c r="N7" s="185">
+      <c r="N7" s="155">
         <f t="shared" si="2"/>
         <v>45996</v>
       </c>
-      <c r="O7" s="183">
+      <c r="O7" s="153">
         <v>530631.65</v>
       </c>
       <c r="P7" s="100"/>
       <c r="Q7" s="127"/>
       <c r="R7" s="127"/>
-      <c r="T7" s="178"/>
-      <c r="V7" s="179"/>
-      <c r="W7" s="179"/>
-      <c r="X7" s="179"/>
-      <c r="Y7" s="179"/>
-      <c r="Z7" s="179"/>
-      <c r="AA7" s="179"/>
+      <c r="T7" s="148"/>
+      <c r="V7" s="149"/>
+      <c r="W7" s="149"/>
+      <c r="X7" s="149"/>
+      <c r="Y7" s="149"/>
+      <c r="Z7" s="149"/>
+      <c r="AA7" s="149"/>
       <c r="AC7" s="128"/>
       <c r="AD7" s="128"/>
       <c r="AE7" s="128"/>
@@ -5307,53 +5444,53 @@
       <c r="AH7" s="129"/>
       <c r="AI7" s="130"/>
     </row>
-    <row r="8" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="165">
+    <row r="8" spans="1:37" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="135">
         <v>7</v>
       </c>
-      <c r="B8" s="165" t="s">
+      <c r="B8" s="135" t="s">
         <v>127</v>
       </c>
-      <c r="C8" s="163" t="s">
+      <c r="C8" s="133" t="s">
         <v>128</v>
       </c>
-      <c r="D8" s="164">
+      <c r="D8" s="134">
         <v>36.372</v>
       </c>
-      <c r="E8" s="168" t="s">
+      <c r="E8" s="138" t="s">
         <v>161</v>
       </c>
-      <c r="F8" s="169">
+      <c r="F8" s="139">
         <v>35</v>
       </c>
-      <c r="G8" s="168" t="s">
+      <c r="G8" s="138" t="s">
         <v>167</v>
       </c>
-      <c r="H8" s="168" t="s">
+      <c r="H8" s="138" t="s">
         <v>170</v>
       </c>
-      <c r="I8" s="168" t="s">
+      <c r="I8" s="138" t="s">
         <v>107</v>
       </c>
       <c r="J8" s="85"/>
-      <c r="K8" s="186"/>
-      <c r="L8" s="185" t="s">
+      <c r="K8" s="156"/>
+      <c r="L8" s="155" t="s">
         <v>176</v>
       </c>
-      <c r="M8" s="185"/>
-      <c r="O8" s="183">
+      <c r="M8" s="155"/>
+      <c r="O8" s="153">
         <v>327992</v>
       </c>
       <c r="P8" s="100"/>
       <c r="Q8" s="127"/>
       <c r="R8" s="127"/>
-      <c r="T8" s="178"/>
-      <c r="V8" s="179"/>
-      <c r="W8" s="179"/>
-      <c r="X8" s="179"/>
-      <c r="Y8" s="179"/>
-      <c r="Z8" s="179"/>
-      <c r="AA8" s="179"/>
+      <c r="T8" s="148"/>
+      <c r="V8" s="149"/>
+      <c r="W8" s="149"/>
+      <c r="X8" s="149"/>
+      <c r="Y8" s="149"/>
+      <c r="Z8" s="149"/>
+      <c r="AA8" s="149"/>
       <c r="AC8" s="128"/>
       <c r="AD8" s="128"/>
       <c r="AE8" s="128"/>
@@ -5362,62 +5499,62 @@
       <c r="AH8" s="129"/>
       <c r="AI8" s="130"/>
     </row>
-    <row r="9" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="165">
+    <row r="9" spans="1:37" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="135">
         <v>8</v>
       </c>
-      <c r="B9" s="165" t="s">
+      <c r="B9" s="135" t="s">
         <v>134</v>
       </c>
-      <c r="C9" s="163" t="s">
+      <c r="C9" s="133" t="s">
         <v>135</v>
       </c>
-      <c r="D9" s="164">
+      <c r="D9" s="134">
         <v>61.15</v>
       </c>
-      <c r="E9" s="168" t="s">
+      <c r="E9" s="138" t="s">
         <v>161</v>
       </c>
-      <c r="F9" s="171"/>
-      <c r="G9" s="168" t="s">
+      <c r="F9" s="141"/>
+      <c r="G9" s="138" t="s">
         <v>167</v>
       </c>
-      <c r="H9" s="168" t="s">
+      <c r="H9" s="138" t="s">
         <v>170</v>
       </c>
-      <c r="I9" s="168" t="s">
+      <c r="I9" s="138" t="s">
         <v>107</v>
       </c>
       <c r="J9" s="85" t="s">
         <v>178</v>
       </c>
-      <c r="K9" s="186">
+      <c r="K9" s="156">
         <v>45964</v>
       </c>
-      <c r="L9" s="185">
+      <c r="L9" s="155">
         <v>45968</v>
       </c>
-      <c r="M9" s="185">
+      <c r="M9" s="155">
         <f t="shared" ref="M9:M31" si="4">L9+10</f>
         <v>45978</v>
       </c>
-      <c r="N9" s="185">
+      <c r="N9" s="155">
         <f t="shared" si="2"/>
         <v>45973</v>
       </c>
-      <c r="O9" s="183">
+      <c r="O9" s="153">
         <v>550294.30000000005</v>
       </c>
       <c r="P9" s="100"/>
       <c r="Q9" s="127"/>
       <c r="R9" s="127"/>
-      <c r="T9" s="178"/>
-      <c r="V9" s="179"/>
-      <c r="W9" s="179"/>
-      <c r="X9" s="179"/>
-      <c r="Y9" s="179"/>
-      <c r="Z9" s="179"/>
-      <c r="AA9" s="179"/>
+      <c r="T9" s="148"/>
+      <c r="V9" s="149"/>
+      <c r="W9" s="149"/>
+      <c r="X9" s="149"/>
+      <c r="Y9" s="149"/>
+      <c r="Z9" s="149"/>
+      <c r="AA9" s="149"/>
       <c r="AC9" s="128"/>
       <c r="AD9" s="128"/>
       <c r="AE9" s="128"/>
@@ -5426,63 +5563,63 @@
       <c r="AH9" s="129"/>
       <c r="AI9" s="130"/>
     </row>
-    <row r="10" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="165">
+    <row r="10" spans="1:37" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="135">
         <v>9</v>
       </c>
-      <c r="B10" s="165" t="s">
+      <c r="B10" s="135" t="s">
         <v>129</v>
       </c>
-      <c r="C10" s="163" t="s">
+      <c r="C10" s="133" t="s">
         <v>128</v>
       </c>
-      <c r="D10" s="164">
+      <c r="D10" s="134">
         <v>36.372</v>
       </c>
-      <c r="E10" s="168" t="s">
+      <c r="E10" s="138" t="s">
         <v>161</v>
       </c>
-      <c r="F10" s="171"/>
-      <c r="G10" s="168" t="s">
+      <c r="F10" s="141"/>
+      <c r="G10" s="138" t="s">
         <v>167</v>
       </c>
-      <c r="H10" s="168" t="s">
+      <c r="H10" s="138" t="s">
         <v>170</v>
       </c>
-      <c r="I10" s="168" t="s">
+      <c r="I10" s="138" t="s">
         <v>107</v>
       </c>
       <c r="J10" s="85" t="str">
         <f t="shared" si="3"/>
         <v>No</v>
       </c>
-      <c r="K10" s="186">
+      <c r="K10" s="156">
         <v>45969</v>
       </c>
-      <c r="L10" s="185">
+      <c r="L10" s="155">
         <v>45972</v>
       </c>
-      <c r="M10" s="185">
+      <c r="M10" s="155">
         <f t="shared" si="4"/>
         <v>45982</v>
       </c>
-      <c r="N10" s="185">
+      <c r="N10" s="155">
         <f t="shared" si="2"/>
         <v>45977</v>
       </c>
-      <c r="O10" s="183">
+      <c r="O10" s="153">
         <v>292211</v>
       </c>
       <c r="P10" s="100"/>
       <c r="Q10" s="127"/>
       <c r="R10" s="127"/>
-      <c r="T10" s="178"/>
-      <c r="V10" s="179"/>
-      <c r="W10" s="179"/>
-      <c r="X10" s="179"/>
-      <c r="Y10" s="179"/>
-      <c r="Z10" s="179"/>
-      <c r="AA10" s="179"/>
+      <c r="T10" s="148"/>
+      <c r="V10" s="149"/>
+      <c r="W10" s="149"/>
+      <c r="X10" s="149"/>
+      <c r="Y10" s="149"/>
+      <c r="Z10" s="149"/>
+      <c r="AA10" s="149"/>
       <c r="AC10" s="128"/>
       <c r="AD10" s="128"/>
       <c r="AE10" s="128"/>
@@ -5491,63 +5628,63 @@
       <c r="AH10" s="129"/>
       <c r="AI10" s="130"/>
     </row>
-    <row r="11" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="165">
+    <row r="11" spans="1:37" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="135">
         <v>10</v>
       </c>
-      <c r="B11" s="165" t="s">
+      <c r="B11" s="135" t="s">
         <v>130</v>
       </c>
-      <c r="C11" s="163" t="s">
+      <c r="C11" s="133" t="s">
         <v>117</v>
       </c>
-      <c r="D11" s="166">
+      <c r="D11" s="136">
         <v>31.99</v>
       </c>
-      <c r="E11" s="168" t="s">
+      <c r="E11" s="138" t="s">
         <v>161</v>
       </c>
-      <c r="F11" s="171"/>
-      <c r="G11" s="168" t="s">
+      <c r="F11" s="141"/>
+      <c r="G11" s="138" t="s">
         <v>167</v>
       </c>
-      <c r="H11" s="168" t="s">
+      <c r="H11" s="138" t="s">
         <v>170</v>
       </c>
-      <c r="I11" s="168" t="s">
+      <c r="I11" s="138" t="s">
         <v>107</v>
       </c>
       <c r="J11" s="85" t="str">
         <f t="shared" si="3"/>
         <v>No</v>
       </c>
-      <c r="K11" s="186">
+      <c r="K11" s="156">
         <v>45973</v>
       </c>
-      <c r="L11" s="185">
+      <c r="L11" s="155">
         <v>45975</v>
       </c>
-      <c r="M11" s="185">
+      <c r="M11" s="155">
         <f t="shared" si="4"/>
         <v>45985</v>
       </c>
-      <c r="N11" s="185">
+      <c r="N11" s="155">
         <f t="shared" si="2"/>
         <v>45980</v>
       </c>
-      <c r="O11" s="183">
+      <c r="O11" s="153">
         <v>292211</v>
       </c>
       <c r="P11" s="100"/>
       <c r="Q11" s="127"/>
       <c r="R11" s="127"/>
-      <c r="T11" s="178"/>
-      <c r="V11" s="179"/>
-      <c r="W11" s="179"/>
-      <c r="X11" s="179"/>
-      <c r="Y11" s="179"/>
-      <c r="Z11" s="179"/>
-      <c r="AA11" s="179"/>
+      <c r="T11" s="148"/>
+      <c r="V11" s="149"/>
+      <c r="W11" s="149"/>
+      <c r="X11" s="149"/>
+      <c r="Y11" s="149"/>
+      <c r="Z11" s="149"/>
+      <c r="AA11" s="149"/>
       <c r="AC11" s="128"/>
       <c r="AD11" s="128"/>
       <c r="AE11" s="128"/>
@@ -5556,63 +5693,63 @@
       <c r="AH11" s="129"/>
       <c r="AI11" s="130"/>
     </row>
-    <row r="12" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="165">
+    <row r="12" spans="1:37" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="135">
         <v>11</v>
       </c>
-      <c r="B12" s="165" t="s">
+      <c r="B12" s="135" t="s">
         <v>131</v>
       </c>
-      <c r="C12" s="163" t="s">
+      <c r="C12" s="133" t="s">
         <v>117</v>
       </c>
-      <c r="D12" s="166">
+      <c r="D12" s="136">
         <v>31.99</v>
       </c>
-      <c r="E12" s="168" t="s">
+      <c r="E12" s="138" t="s">
         <v>161</v>
       </c>
-      <c r="F12" s="165"/>
-      <c r="G12" s="168" t="s">
+      <c r="F12" s="135"/>
+      <c r="G12" s="138" t="s">
         <v>167</v>
       </c>
-      <c r="H12" s="168" t="s">
+      <c r="H12" s="138" t="s">
         <v>170</v>
       </c>
-      <c r="I12" s="168" t="s">
+      <c r="I12" s="138" t="s">
         <v>107</v>
       </c>
       <c r="J12" s="85" t="str">
         <f t="shared" si="3"/>
         <v>No</v>
       </c>
-      <c r="K12" s="186">
+      <c r="K12" s="156">
         <v>45976</v>
       </c>
-      <c r="L12" s="185">
+      <c r="L12" s="155">
         <v>45981</v>
       </c>
-      <c r="M12" s="185">
+      <c r="M12" s="155">
         <f t="shared" si="4"/>
         <v>45991</v>
       </c>
-      <c r="N12" s="185">
+      <c r="N12" s="155">
         <f t="shared" si="2"/>
         <v>45986</v>
       </c>
-      <c r="O12" s="183">
+      <c r="O12" s="153">
         <v>292211</v>
       </c>
       <c r="P12" s="100"/>
       <c r="Q12" s="127"/>
       <c r="R12" s="127"/>
-      <c r="T12" s="178"/>
-      <c r="V12" s="179"/>
-      <c r="W12" s="179"/>
-      <c r="X12" s="179"/>
-      <c r="Y12" s="179"/>
-      <c r="Z12" s="179"/>
-      <c r="AA12" s="179"/>
+      <c r="T12" s="148"/>
+      <c r="V12" s="149"/>
+      <c r="W12" s="149"/>
+      <c r="X12" s="149"/>
+      <c r="Y12" s="149"/>
+      <c r="Z12" s="149"/>
+      <c r="AA12" s="149"/>
       <c r="AC12" s="128"/>
       <c r="AD12" s="128"/>
       <c r="AE12" s="128"/>
@@ -5621,63 +5758,63 @@
       <c r="AH12" s="129"/>
       <c r="AI12" s="130"/>
     </row>
-    <row r="13" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="165">
+    <row r="13" spans="1:37" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="135">
         <v>12</v>
       </c>
-      <c r="B13" s="165" t="s">
+      <c r="B13" s="135" t="s">
         <v>132</v>
       </c>
-      <c r="C13" s="163" t="s">
+      <c r="C13" s="133" t="s">
         <v>117</v>
       </c>
-      <c r="D13" s="166">
+      <c r="D13" s="136">
         <v>31.99</v>
       </c>
-      <c r="E13" s="168" t="s">
+      <c r="E13" s="138" t="s">
         <v>161</v>
       </c>
-      <c r="F13" s="165"/>
-      <c r="G13" s="168" t="s">
+      <c r="F13" s="135"/>
+      <c r="G13" s="138" t="s">
         <v>167</v>
       </c>
-      <c r="H13" s="168" t="s">
+      <c r="H13" s="138" t="s">
         <v>170</v>
       </c>
-      <c r="I13" s="168" t="s">
+      <c r="I13" s="138" t="s">
         <v>107</v>
       </c>
       <c r="J13" s="85" t="str">
         <f t="shared" si="3"/>
         <v>No</v>
       </c>
-      <c r="K13" s="186">
+      <c r="K13" s="156">
         <v>45982</v>
       </c>
-      <c r="L13" s="185">
+      <c r="L13" s="155">
         <v>45986</v>
       </c>
-      <c r="M13" s="185">
+      <c r="M13" s="155">
         <f t="shared" si="4"/>
         <v>45996</v>
       </c>
-      <c r="N13" s="185">
+      <c r="N13" s="155">
         <f t="shared" si="2"/>
         <v>45991</v>
       </c>
-      <c r="O13" s="183">
+      <c r="O13" s="153">
         <v>292211</v>
       </c>
       <c r="P13" s="100"/>
       <c r="Q13" s="127"/>
       <c r="R13" s="127"/>
-      <c r="T13" s="178"/>
-      <c r="V13" s="179"/>
-      <c r="W13" s="179"/>
-      <c r="X13" s="179"/>
-      <c r="Y13" s="179"/>
-      <c r="Z13" s="179"/>
-      <c r="AA13" s="179"/>
+      <c r="T13" s="148"/>
+      <c r="V13" s="149"/>
+      <c r="W13" s="149"/>
+      <c r="X13" s="149"/>
+      <c r="Y13" s="149"/>
+      <c r="Z13" s="149"/>
+      <c r="AA13" s="149"/>
       <c r="AC13" s="128"/>
       <c r="AD13" s="128"/>
       <c r="AE13" s="128"/>
@@ -5686,63 +5823,63 @@
       <c r="AH13" s="129"/>
       <c r="AI13" s="130"/>
     </row>
-    <row r="14" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="165">
+    <row r="14" spans="1:37" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="135">
         <v>13</v>
       </c>
-      <c r="B14" s="165" t="s">
+      <c r="B14" s="135" t="s">
         <v>133</v>
       </c>
-      <c r="C14" s="163" t="s">
+      <c r="C14" s="133" t="s">
         <v>125</v>
       </c>
-      <c r="D14" s="164">
+      <c r="D14" s="134">
         <v>58.93</v>
       </c>
-      <c r="E14" s="168" t="s">
+      <c r="E14" s="138" t="s">
         <v>161</v>
       </c>
-      <c r="F14" s="171"/>
-      <c r="G14" s="168" t="s">
+      <c r="F14" s="141"/>
+      <c r="G14" s="138" t="s">
         <v>167</v>
       </c>
-      <c r="H14" s="168" t="s">
+      <c r="H14" s="138" t="s">
         <v>170</v>
       </c>
-      <c r="I14" s="168" t="s">
+      <c r="I14" s="138" t="s">
         <v>107</v>
       </c>
       <c r="J14" s="85" t="str">
         <f t="shared" si="3"/>
         <v>No</v>
       </c>
-      <c r="K14" s="186">
+      <c r="K14" s="156">
         <v>45987</v>
       </c>
-      <c r="L14" s="185">
+      <c r="L14" s="155">
         <v>45991</v>
       </c>
-      <c r="M14" s="185">
+      <c r="M14" s="155">
         <f t="shared" si="4"/>
         <v>46001</v>
       </c>
-      <c r="N14" s="185">
+      <c r="N14" s="155">
         <f t="shared" si="2"/>
         <v>45996</v>
       </c>
-      <c r="O14" s="183">
+      <c r="O14" s="153">
         <v>550294.30000000005</v>
       </c>
       <c r="P14" s="100"/>
       <c r="Q14" s="127"/>
       <c r="R14" s="127"/>
-      <c r="T14" s="178"/>
-      <c r="V14" s="179"/>
-      <c r="W14" s="179"/>
-      <c r="X14" s="179"/>
-      <c r="Y14" s="179"/>
-      <c r="Z14" s="179"/>
-      <c r="AA14" s="179"/>
+      <c r="T14" s="148"/>
+      <c r="V14" s="149"/>
+      <c r="W14" s="149"/>
+      <c r="X14" s="149"/>
+      <c r="Y14" s="149"/>
+      <c r="Z14" s="149"/>
+      <c r="AA14" s="149"/>
       <c r="AC14" s="128"/>
       <c r="AD14" s="128"/>
       <c r="AE14" s="128"/>
@@ -5752,53 +5889,53 @@
       <c r="AI14" s="130"/>
       <c r="AK14" s="100"/>
     </row>
-    <row r="15" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="165">
+    <row r="15" spans="1:37" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="135">
         <v>14</v>
       </c>
-      <c r="B15" s="165" t="s">
+      <c r="B15" s="135" t="s">
         <v>136</v>
       </c>
-      <c r="C15" s="163" t="s">
+      <c r="C15" s="133" t="s">
         <v>128</v>
       </c>
-      <c r="D15" s="166">
+      <c r="D15" s="136">
         <v>36.372</v>
       </c>
-      <c r="E15" s="168" t="s">
+      <c r="E15" s="138" t="s">
         <v>162</v>
       </c>
-      <c r="F15" s="169">
+      <c r="F15" s="139">
         <v>30</v>
       </c>
-      <c r="G15" s="168" t="s">
+      <c r="G15" s="138" t="s">
         <v>168</v>
       </c>
-      <c r="H15" s="168" t="s">
+      <c r="H15" s="138" t="s">
         <v>171</v>
       </c>
-      <c r="I15" s="168" t="s">
+      <c r="I15" s="138" t="s">
         <v>107</v>
       </c>
       <c r="J15" s="131"/>
       <c r="K15" s="131"/>
-      <c r="L15" s="185" t="s">
+      <c r="L15" s="155" t="s">
         <v>176</v>
       </c>
-      <c r="N15" s="185"/>
-      <c r="O15" s="183">
+      <c r="N15" s="155"/>
+      <c r="O15" s="153">
         <v>327992</v>
       </c>
       <c r="P15" s="100"/>
       <c r="Q15" s="127"/>
       <c r="R15" s="127"/>
-      <c r="T15" s="178"/>
-      <c r="V15" s="179"/>
-      <c r="W15" s="179"/>
-      <c r="X15" s="179"/>
-      <c r="Y15" s="179"/>
-      <c r="Z15" s="179"/>
-      <c r="AA15" s="179"/>
+      <c r="T15" s="148"/>
+      <c r="V15" s="149"/>
+      <c r="W15" s="149"/>
+      <c r="X15" s="149"/>
+      <c r="Y15" s="149"/>
+      <c r="Z15" s="149"/>
+      <c r="AA15" s="149"/>
       <c r="AC15" s="128"/>
       <c r="AD15" s="128"/>
       <c r="AE15" s="128"/>
@@ -5807,63 +5944,63 @@
       <c r="AH15" s="129"/>
       <c r="AI15" s="130"/>
     </row>
-    <row r="16" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="165">
+    <row r="16" spans="1:37" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="135">
         <v>15</v>
       </c>
-      <c r="B16" s="165" t="s">
+      <c r="B16" s="135" t="s">
         <v>141</v>
       </c>
-      <c r="C16" s="163" t="s">
+      <c r="C16" s="133" t="s">
         <v>142</v>
       </c>
-      <c r="D16" s="166">
+      <c r="D16" s="136">
         <v>83.81</v>
       </c>
-      <c r="E16" s="168" t="s">
+      <c r="E16" s="138" t="s">
         <v>162</v>
       </c>
-      <c r="F16" s="165"/>
-      <c r="G16" s="168" t="s">
+      <c r="F16" s="135"/>
+      <c r="G16" s="138" t="s">
         <v>168</v>
       </c>
-      <c r="H16" s="168" t="s">
+      <c r="H16" s="138" t="s">
         <v>171</v>
       </c>
-      <c r="I16" s="168" t="s">
+      <c r="I16" s="138" t="s">
         <v>107</v>
       </c>
       <c r="J16" s="85" t="s">
         <v>178</v>
       </c>
-      <c r="K16" s="185">
+      <c r="K16" s="155">
         <v>45967</v>
       </c>
-      <c r="L16" s="185">
+      <c r="L16" s="155">
         <f>K16+10</f>
         <v>45977</v>
       </c>
-      <c r="M16" s="185">
+      <c r="M16" s="155">
         <f>K16+5</f>
         <v>45972</v>
       </c>
-      <c r="N16" s="178">
+      <c r="N16" s="148">
         <f>M16+5</f>
         <v>45977</v>
       </c>
-      <c r="O16" s="183">
+      <c r="O16" s="153">
         <v>749941.09</v>
       </c>
       <c r="P16" s="100"/>
       <c r="Q16" s="127"/>
       <c r="R16" s="127"/>
-      <c r="T16" s="178"/>
-      <c r="V16" s="179"/>
-      <c r="W16" s="179"/>
-      <c r="X16" s="179"/>
-      <c r="Y16" s="179"/>
-      <c r="Z16" s="179"/>
-      <c r="AA16" s="179"/>
+      <c r="T16" s="148"/>
+      <c r="V16" s="149"/>
+      <c r="W16" s="149"/>
+      <c r="X16" s="149"/>
+      <c r="Y16" s="149"/>
+      <c r="Z16" s="149"/>
+      <c r="AA16" s="149"/>
       <c r="AC16" s="128"/>
       <c r="AD16" s="128"/>
       <c r="AE16" s="128"/>
@@ -5872,63 +6009,63 @@
       <c r="AH16" s="129"/>
       <c r="AI16" s="130"/>
     </row>
-    <row r="17" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="165">
+    <row r="17" spans="1:35" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="135">
         <v>16</v>
       </c>
-      <c r="B17" s="165" t="s">
+      <c r="B17" s="135" t="s">
         <v>137</v>
       </c>
-      <c r="C17" s="163" t="s">
+      <c r="C17" s="133" t="s">
         <v>138</v>
       </c>
-      <c r="D17" s="167">
+      <c r="D17" s="137">
         <v>37.930999999999997</v>
       </c>
-      <c r="E17" s="168" t="s">
+      <c r="E17" s="138" t="s">
         <v>162</v>
       </c>
-      <c r="F17" s="165"/>
-      <c r="G17" s="168" t="s">
+      <c r="F17" s="135"/>
+      <c r="G17" s="138" t="s">
         <v>168</v>
       </c>
-      <c r="H17" s="168" t="s">
+      <c r="H17" s="138" t="s">
         <v>171</v>
       </c>
-      <c r="I17" s="168" t="s">
+      <c r="I17" s="138" t="s">
         <v>107</v>
       </c>
       <c r="J17" s="85" t="str">
         <f t="shared" si="3"/>
         <v>No</v>
       </c>
-      <c r="K17" s="186">
+      <c r="K17" s="156">
         <v>45978</v>
       </c>
-      <c r="L17" s="185">
+      <c r="L17" s="155">
         <v>45982</v>
       </c>
-      <c r="M17" s="185">
+      <c r="M17" s="155">
         <f>L17+10</f>
         <v>45992</v>
       </c>
-      <c r="N17" s="185">
+      <c r="N17" s="155">
         <f>L17+5</f>
         <v>45987</v>
       </c>
-      <c r="O17" s="183">
+      <c r="O17" s="153">
         <v>342752</v>
       </c>
       <c r="P17" s="100"/>
       <c r="Q17" s="127"/>
       <c r="R17" s="127"/>
-      <c r="T17" s="178"/>
-      <c r="V17" s="179"/>
-      <c r="W17" s="179"/>
-      <c r="X17" s="179"/>
-      <c r="Y17" s="179"/>
-      <c r="Z17" s="179"/>
-      <c r="AA17" s="179"/>
+      <c r="T17" s="148"/>
+      <c r="V17" s="149"/>
+      <c r="W17" s="149"/>
+      <c r="X17" s="149"/>
+      <c r="Y17" s="149"/>
+      <c r="Z17" s="149"/>
+      <c r="AA17" s="149"/>
       <c r="AC17" s="128"/>
       <c r="AD17" s="128"/>
       <c r="AE17" s="128"/>
@@ -5937,63 +6074,63 @@
       <c r="AH17" s="129"/>
       <c r="AI17" s="130"/>
     </row>
-    <row r="18" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="165">
+    <row r="18" spans="1:35" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="135">
         <v>17</v>
       </c>
-      <c r="B18" s="165" t="s">
+      <c r="B18" s="135" t="s">
         <v>139</v>
       </c>
-      <c r="C18" s="163" t="s">
+      <c r="C18" s="133" t="s">
         <v>140</v>
       </c>
-      <c r="D18" s="166">
+      <c r="D18" s="136">
         <v>54.66</v>
       </c>
-      <c r="E18" s="168" t="s">
+      <c r="E18" s="138" t="s">
         <v>162</v>
       </c>
-      <c r="F18" s="171"/>
-      <c r="G18" s="168" t="s">
+      <c r="F18" s="141"/>
+      <c r="G18" s="138" t="s">
         <v>168</v>
       </c>
-      <c r="H18" s="168" t="s">
+      <c r="H18" s="138" t="s">
         <v>171</v>
       </c>
-      <c r="I18" s="168" t="s">
+      <c r="I18" s="138" t="s">
         <v>107</v>
       </c>
       <c r="J18" s="85" t="str">
         <f t="shared" si="3"/>
         <v>No</v>
       </c>
-      <c r="K18" s="186">
+      <c r="K18" s="156">
         <v>45984</v>
       </c>
-      <c r="L18" s="185">
+      <c r="L18" s="155">
         <v>45990</v>
       </c>
-      <c r="M18" s="185">
+      <c r="M18" s="155">
         <f t="shared" si="4"/>
         <v>46000</v>
       </c>
-      <c r="N18" s="185">
+      <c r="N18" s="155">
         <f t="shared" si="2"/>
         <v>45995</v>
       </c>
-      <c r="O18" s="183">
+      <c r="O18" s="153">
         <v>478941</v>
       </c>
       <c r="P18" s="100"/>
       <c r="Q18" s="127"/>
       <c r="R18" s="127"/>
-      <c r="T18" s="178"/>
-      <c r="V18" s="179"/>
-      <c r="W18" s="179"/>
-      <c r="X18" s="179"/>
-      <c r="Y18" s="179"/>
-      <c r="Z18" s="179"/>
-      <c r="AA18" s="179"/>
+      <c r="T18" s="148"/>
+      <c r="V18" s="149"/>
+      <c r="W18" s="149"/>
+      <c r="X18" s="149"/>
+      <c r="Y18" s="149"/>
+      <c r="Z18" s="149"/>
+      <c r="AA18" s="149"/>
       <c r="AC18" s="128"/>
       <c r="AD18" s="128"/>
       <c r="AE18" s="128"/>
@@ -6002,32 +6139,32 @@
       <c r="AH18" s="129"/>
       <c r="AI18" s="130"/>
     </row>
-    <row r="19" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="165">
+    <row r="19" spans="1:35" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="135">
         <v>18</v>
       </c>
-      <c r="B19" s="165" t="s">
+      <c r="B19" s="135" t="s">
         <v>143</v>
       </c>
-      <c r="C19" s="163" t="s">
+      <c r="C19" s="133" t="s">
         <v>138</v>
       </c>
-      <c r="D19" s="167">
+      <c r="D19" s="137">
         <v>37.930999999999997</v>
       </c>
-      <c r="E19" s="168" t="s">
+      <c r="E19" s="138" t="s">
         <v>163</v>
       </c>
-      <c r="F19" s="169">
+      <c r="F19" s="139">
         <v>20</v>
       </c>
-      <c r="G19" s="168" t="s">
+      <c r="G19" s="138" t="s">
         <v>168</v>
       </c>
-      <c r="H19" s="168" t="s">
+      <c r="H19" s="138" t="s">
         <v>172</v>
       </c>
-      <c r="I19" s="168" t="s">
+      <c r="I19" s="138" t="s">
         <v>107</v>
       </c>
       <c r="J19" s="85" t="s">
@@ -6036,30 +6173,30 @@
       <c r="K19" s="114" t="s">
         <v>175</v>
       </c>
-      <c r="L19" s="185">
+      <c r="L19" s="155">
         <v>45968</v>
       </c>
-      <c r="M19" s="185">
+      <c r="M19" s="155">
         <f t="shared" si="4"/>
         <v>45978</v>
       </c>
-      <c r="N19" s="185">
+      <c r="N19" s="155">
         <f t="shared" si="2"/>
         <v>45973</v>
       </c>
-      <c r="O19" s="183">
+      <c r="O19" s="153">
         <v>342752</v>
       </c>
       <c r="P19" s="100"/>
       <c r="Q19" s="127"/>
       <c r="R19" s="127"/>
-      <c r="T19" s="178"/>
-      <c r="V19" s="179"/>
-      <c r="W19" s="179"/>
-      <c r="X19" s="179"/>
-      <c r="Y19" s="179"/>
-      <c r="Z19" s="179"/>
-      <c r="AA19" s="179"/>
+      <c r="T19" s="148"/>
+      <c r="V19" s="149"/>
+      <c r="W19" s="149"/>
+      <c r="X19" s="149"/>
+      <c r="Y19" s="149"/>
+      <c r="Z19" s="149"/>
+      <c r="AA19" s="149"/>
       <c r="AC19" s="128"/>
       <c r="AD19" s="128"/>
       <c r="AE19" s="128"/>
@@ -6068,30 +6205,30 @@
       <c r="AH19" s="129"/>
       <c r="AI19" s="130"/>
     </row>
-    <row r="20" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="165">
+    <row r="20" spans="1:35" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="135">
         <v>19</v>
       </c>
-      <c r="B20" s="165" t="s">
+      <c r="B20" s="135" t="s">
         <v>144</v>
       </c>
-      <c r="C20" s="163" t="s">
+      <c r="C20" s="133" t="s">
         <v>145</v>
       </c>
-      <c r="D20" s="167">
+      <c r="D20" s="137">
         <v>44.85</v>
       </c>
-      <c r="E20" s="168" t="s">
+      <c r="E20" s="138" t="s">
         <v>163</v>
       </c>
-      <c r="F20" s="168"/>
-      <c r="G20" s="168" t="s">
+      <c r="F20" s="138"/>
+      <c r="G20" s="138" t="s">
         <v>168</v>
       </c>
-      <c r="H20" s="168" t="s">
+      <c r="H20" s="138" t="s">
         <v>172</v>
       </c>
-      <c r="I20" s="168" t="s">
+      <c r="I20" s="138" t="s">
         <v>107</v>
       </c>
       <c r="J20" s="85" t="str">
@@ -6101,30 +6238,30 @@
       <c r="K20" s="114">
         <v>45969</v>
       </c>
-      <c r="L20" s="185">
+      <c r="L20" s="155">
         <v>45975</v>
       </c>
-      <c r="M20" s="185">
+      <c r="M20" s="155">
         <f t="shared" si="4"/>
         <v>45985</v>
       </c>
-      <c r="N20" s="185">
+      <c r="N20" s="155">
         <f t="shared" si="2"/>
         <v>45980</v>
       </c>
-      <c r="O20" s="183">
+      <c r="O20" s="153">
         <v>406294</v>
       </c>
       <c r="P20" s="100"/>
       <c r="Q20" s="127"/>
       <c r="R20" s="127"/>
-      <c r="T20" s="178"/>
-      <c r="V20" s="179"/>
-      <c r="W20" s="179"/>
-      <c r="X20" s="179"/>
-      <c r="Y20" s="179"/>
-      <c r="Z20" s="179"/>
-      <c r="AA20" s="179"/>
+      <c r="T20" s="148"/>
+      <c r="V20" s="149"/>
+      <c r="W20" s="149"/>
+      <c r="X20" s="149"/>
+      <c r="Y20" s="149"/>
+      <c r="Z20" s="149"/>
+      <c r="AA20" s="149"/>
       <c r="AC20" s="128"/>
       <c r="AD20" s="128"/>
       <c r="AE20" s="128"/>
@@ -6133,30 +6270,30 @@
       <c r="AH20" s="129"/>
       <c r="AI20" s="130"/>
     </row>
-    <row r="21" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="165">
+    <row r="21" spans="1:35" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="135">
         <v>20</v>
       </c>
-      <c r="B21" s="165" t="s">
+      <c r="B21" s="135" t="s">
         <v>146</v>
       </c>
-      <c r="C21" s="163" t="s">
+      <c r="C21" s="133" t="s">
         <v>128</v>
       </c>
-      <c r="D21" s="167">
+      <c r="D21" s="137">
         <v>36.372</v>
       </c>
-      <c r="E21" s="168" t="s">
+      <c r="E21" s="138" t="s">
         <v>163</v>
       </c>
-      <c r="F21" s="168"/>
-      <c r="G21" s="168" t="s">
+      <c r="F21" s="138"/>
+      <c r="G21" s="138" t="s">
         <v>168</v>
       </c>
-      <c r="H21" s="168" t="s">
+      <c r="H21" s="138" t="s">
         <v>172</v>
       </c>
-      <c r="I21" s="168" t="s">
+      <c r="I21" s="138" t="s">
         <v>107</v>
       </c>
       <c r="J21" s="85" t="str">
@@ -6166,30 +6303,30 @@
       <c r="K21" s="114">
         <v>45976</v>
       </c>
-      <c r="L21" s="185">
+      <c r="L21" s="155">
         <v>45983</v>
       </c>
-      <c r="M21" s="185">
+      <c r="M21" s="155">
         <f t="shared" si="4"/>
         <v>45993</v>
       </c>
-      <c r="N21" s="185">
+      <c r="N21" s="155">
         <f t="shared" si="2"/>
         <v>45988</v>
       </c>
-      <c r="O21" s="183">
+      <c r="O21" s="153">
         <v>327992</v>
       </c>
       <c r="P21" s="100"/>
       <c r="Q21" s="127"/>
       <c r="R21" s="127"/>
-      <c r="T21" s="178"/>
-      <c r="V21" s="179"/>
-      <c r="W21" s="179"/>
-      <c r="X21" s="179"/>
-      <c r="Y21" s="179"/>
-      <c r="Z21" s="179"/>
-      <c r="AA21" s="179"/>
+      <c r="T21" s="148"/>
+      <c r="V21" s="149"/>
+      <c r="W21" s="149"/>
+      <c r="X21" s="149"/>
+      <c r="Y21" s="149"/>
+      <c r="Z21" s="149"/>
+      <c r="AA21" s="149"/>
       <c r="AC21" s="128"/>
       <c r="AD21" s="128"/>
       <c r="AE21" s="128"/>
@@ -6198,30 +6335,30 @@
       <c r="AH21" s="129"/>
       <c r="AI21" s="130"/>
     </row>
-    <row r="22" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="165">
+    <row r="22" spans="1:35" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="135">
         <v>21</v>
       </c>
-      <c r="B22" s="165" t="s">
+      <c r="B22" s="135" t="s">
         <v>147</v>
       </c>
-      <c r="C22" s="163" t="s">
+      <c r="C22" s="133" t="s">
         <v>128</v>
       </c>
-      <c r="D22" s="167">
+      <c r="D22" s="137">
         <v>36.372</v>
       </c>
-      <c r="E22" s="168" t="s">
+      <c r="E22" s="138" t="s">
         <v>163</v>
       </c>
-      <c r="F22" s="171"/>
-      <c r="G22" s="168" t="s">
+      <c r="F22" s="141"/>
+      <c r="G22" s="138" t="s">
         <v>168</v>
       </c>
-      <c r="H22" s="168" t="s">
+      <c r="H22" s="138" t="s">
         <v>172</v>
       </c>
-      <c r="I22" s="168" t="s">
+      <c r="I22" s="138" t="s">
         <v>107</v>
       </c>
       <c r="J22" s="85" t="str">
@@ -6231,30 +6368,30 @@
       <c r="K22" s="114">
         <v>45984</v>
       </c>
-      <c r="L22" s="185">
+      <c r="L22" s="155">
         <v>45991</v>
       </c>
-      <c r="M22" s="185">
+      <c r="M22" s="155">
         <f t="shared" si="4"/>
         <v>46001</v>
       </c>
-      <c r="N22" s="185">
+      <c r="N22" s="155">
         <f t="shared" si="2"/>
         <v>45996</v>
       </c>
-      <c r="O22" s="183">
+      <c r="O22" s="153">
         <v>327992</v>
       </c>
       <c r="P22" s="100"/>
       <c r="Q22" s="127"/>
       <c r="R22" s="127"/>
-      <c r="T22" s="178"/>
-      <c r="V22" s="179"/>
-      <c r="W22" s="179"/>
-      <c r="X22" s="179"/>
-      <c r="Y22" s="179"/>
-      <c r="Z22" s="179"/>
-      <c r="AA22" s="179"/>
+      <c r="T22" s="148"/>
+      <c r="V22" s="149"/>
+      <c r="W22" s="149"/>
+      <c r="X22" s="149"/>
+      <c r="Y22" s="149"/>
+      <c r="Z22" s="149"/>
+      <c r="AA22" s="149"/>
       <c r="AC22" s="128"/>
       <c r="AD22" s="128"/>
       <c r="AE22" s="128"/>
@@ -6263,32 +6400,32 @@
       <c r="AH22" s="129"/>
       <c r="AI22" s="130"/>
     </row>
-    <row r="23" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="165">
+    <row r="23" spans="1:35" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="135">
         <v>22</v>
       </c>
-      <c r="B23" s="165" t="s">
+      <c r="B23" s="135" t="s">
         <v>148</v>
       </c>
-      <c r="C23" s="163" t="s">
+      <c r="C23" s="133" t="s">
         <v>138</v>
       </c>
-      <c r="D23" s="167">
+      <c r="D23" s="137">
         <v>37.930999999999997</v>
       </c>
-      <c r="E23" s="168" t="s">
+      <c r="E23" s="138" t="s">
         <v>164</v>
       </c>
-      <c r="F23" s="169">
+      <c r="F23" s="139">
         <v>20</v>
       </c>
-      <c r="G23" s="168" t="s">
+      <c r="G23" s="138" t="s">
         <v>168</v>
       </c>
-      <c r="H23" s="168" t="s">
+      <c r="H23" s="138" t="s">
         <v>173</v>
       </c>
-      <c r="I23" s="168" t="s">
+      <c r="I23" s="138" t="s">
         <v>177</v>
       </c>
       <c r="J23" s="85" t="str">
@@ -6296,24 +6433,24 @@
         <v xml:space="preserve">YES </v>
       </c>
       <c r="K23" s="114"/>
-      <c r="L23" s="185" t="s">
+      <c r="L23" s="155" t="s">
         <v>176</v>
       </c>
-      <c r="M23" s="185"/>
-      <c r="N23" s="185"/>
-      <c r="O23" s="183">
+      <c r="M23" s="155"/>
+      <c r="N23" s="155"/>
+      <c r="O23" s="153">
         <v>342752</v>
       </c>
       <c r="P23" s="100"/>
       <c r="Q23" s="127"/>
       <c r="R23" s="127"/>
-      <c r="T23" s="178"/>
-      <c r="V23" s="179"/>
-      <c r="W23" s="179"/>
-      <c r="X23" s="179"/>
-      <c r="Y23" s="179"/>
-      <c r="Z23" s="179"/>
-      <c r="AA23" s="179"/>
+      <c r="T23" s="148"/>
+      <c r="V23" s="149"/>
+      <c r="W23" s="149"/>
+      <c r="X23" s="149"/>
+      <c r="Y23" s="149"/>
+      <c r="Z23" s="149"/>
+      <c r="AA23" s="149"/>
       <c r="AC23" s="128"/>
       <c r="AD23" s="128"/>
       <c r="AE23" s="128"/>
@@ -6322,62 +6459,62 @@
       <c r="AH23" s="129"/>
       <c r="AI23" s="130"/>
     </row>
-    <row r="24" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="165">
+    <row r="24" spans="1:35" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="135">
         <v>26</v>
       </c>
-      <c r="B24" s="165" t="s">
+      <c r="B24" s="135" t="s">
         <v>152</v>
       </c>
-      <c r="C24" s="163" t="s">
+      <c r="C24" s="133" t="s">
         <v>153</v>
       </c>
-      <c r="D24" s="166">
+      <c r="D24" s="136">
         <v>64.89</v>
       </c>
-      <c r="E24" s="168" t="s">
+      <c r="E24" s="138" t="s">
         <v>164</v>
       </c>
-      <c r="F24" s="171"/>
-      <c r="G24" s="168" t="s">
+      <c r="F24" s="141"/>
+      <c r="G24" s="138" t="s">
         <v>168</v>
       </c>
-      <c r="H24" s="168" t="s">
+      <c r="H24" s="138" t="s">
         <v>173</v>
       </c>
-      <c r="I24" s="168" t="s">
+      <c r="I24" s="138" t="s">
         <v>177</v>
       </c>
       <c r="J24" s="85" t="s">
         <v>178</v>
       </c>
-      <c r="K24" s="187">
+      <c r="K24" s="157">
         <v>45965</v>
       </c>
-      <c r="L24" s="185">
+      <c r="L24" s="155">
         <v>45971</v>
       </c>
-      <c r="M24" s="185">
+      <c r="M24" s="155">
         <f>L24+10</f>
         <v>45981</v>
       </c>
-      <c r="N24" s="185">
+      <c r="N24" s="155">
         <f>L24+5</f>
         <v>45976</v>
       </c>
-      <c r="O24" s="183">
+      <c r="O24" s="153">
         <v>586943</v>
       </c>
       <c r="P24" s="100"/>
       <c r="Q24" s="127"/>
       <c r="R24" s="127"/>
-      <c r="T24" s="178"/>
-      <c r="V24" s="179"/>
-      <c r="W24" s="179"/>
-      <c r="X24" s="179"/>
-      <c r="Y24" s="179"/>
-      <c r="Z24" s="179"/>
-      <c r="AA24" s="179"/>
+      <c r="T24" s="148"/>
+      <c r="V24" s="149"/>
+      <c r="W24" s="149"/>
+      <c r="X24" s="149"/>
+      <c r="Y24" s="149"/>
+      <c r="Z24" s="149"/>
+      <c r="AA24" s="149"/>
       <c r="AC24" s="128"/>
       <c r="AD24" s="128"/>
       <c r="AE24" s="128"/>
@@ -6386,62 +6523,62 @@
       <c r="AH24" s="129"/>
       <c r="AI24" s="130"/>
     </row>
-    <row r="25" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="165">
+    <row r="25" spans="1:35" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="135">
         <v>23</v>
       </c>
-      <c r="B25" s="165" t="s">
+      <c r="B25" s="135" t="s">
         <v>149</v>
       </c>
-      <c r="C25" s="163" t="s">
+      <c r="C25" s="133" t="s">
         <v>140</v>
       </c>
-      <c r="D25" s="167">
+      <c r="D25" s="137">
         <v>54.66</v>
       </c>
-      <c r="E25" s="168" t="s">
+      <c r="E25" s="138" t="s">
         <v>164</v>
       </c>
-      <c r="F25" s="171"/>
-      <c r="G25" s="168" t="s">
+      <c r="F25" s="141"/>
+      <c r="G25" s="138" t="s">
         <v>168</v>
       </c>
-      <c r="H25" s="168" t="s">
+      <c r="H25" s="138" t="s">
         <v>173</v>
       </c>
-      <c r="I25" s="168" t="s">
+      <c r="I25" s="138" t="s">
         <v>177</v>
       </c>
       <c r="J25" s="85" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve">YES </v>
       </c>
-      <c r="K25" s="187">
+      <c r="K25" s="157">
         <v>45972</v>
       </c>
-      <c r="L25" s="185">
+      <c r="L25" s="155">
         <v>45976</v>
       </c>
-      <c r="M25" s="185">
+      <c r="M25" s="155">
         <f>L25+10</f>
         <v>45986</v>
       </c>
-      <c r="N25" s="185">
+      <c r="N25" s="155">
         <f>L25+5</f>
         <v>45981</v>
       </c>
-      <c r="O25" s="183">
+      <c r="O25" s="153">
         <v>478941</v>
       </c>
       <c r="P25" s="100"/>
       <c r="Q25" s="127"/>
       <c r="R25" s="127"/>
-      <c r="V25" s="179"/>
-      <c r="W25" s="179"/>
-      <c r="X25" s="179"/>
-      <c r="Y25" s="179"/>
-      <c r="Z25" s="179"/>
-      <c r="AA25" s="179"/>
+      <c r="V25" s="149"/>
+      <c r="W25" s="149"/>
+      <c r="X25" s="149"/>
+      <c r="Y25" s="149"/>
+      <c r="Z25" s="149"/>
+      <c r="AA25" s="149"/>
       <c r="AC25" s="128"/>
       <c r="AD25" s="128"/>
       <c r="AE25" s="128"/>
@@ -6450,63 +6587,63 @@
       <c r="AH25" s="129"/>
       <c r="AI25" s="130"/>
     </row>
-    <row r="26" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="165">
+    <row r="26" spans="1:35" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="135">
         <v>24</v>
       </c>
-      <c r="B26" s="165" t="s">
+      <c r="B26" s="135" t="s">
         <v>150</v>
       </c>
-      <c r="C26" s="163" t="s">
+      <c r="C26" s="133" t="s">
         <v>128</v>
       </c>
-      <c r="D26" s="167">
+      <c r="D26" s="137">
         <v>36.372</v>
       </c>
-      <c r="E26" s="168" t="s">
+      <c r="E26" s="138" t="s">
         <v>164</v>
       </c>
-      <c r="F26" s="171"/>
-      <c r="G26" s="168" t="s">
+      <c r="F26" s="141"/>
+      <c r="G26" s="138" t="s">
         <v>168</v>
       </c>
-      <c r="H26" s="168" t="s">
+      <c r="H26" s="138" t="s">
         <v>173</v>
       </c>
-      <c r="I26" s="168" t="s">
+      <c r="I26" s="138" t="s">
         <v>177</v>
       </c>
       <c r="J26" s="85" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve">YES </v>
       </c>
-      <c r="K26" s="187">
+      <c r="K26" s="157">
         <v>45977</v>
       </c>
-      <c r="L26" s="185">
+      <c r="L26" s="155">
         <v>45982</v>
       </c>
-      <c r="M26" s="185">
+      <c r="M26" s="155">
         <f>L26+10</f>
         <v>45992</v>
       </c>
-      <c r="N26" s="185">
+      <c r="N26" s="155">
         <f>L26+5</f>
         <v>45987</v>
       </c>
-      <c r="O26" s="183">
+      <c r="O26" s="153">
         <v>327992</v>
       </c>
       <c r="P26" s="100"/>
       <c r="Q26" s="127"/>
       <c r="R26" s="127"/>
-      <c r="T26" s="178"/>
-      <c r="V26" s="179"/>
-      <c r="W26" s="179"/>
-      <c r="X26" s="179"/>
-      <c r="Y26" s="179"/>
-      <c r="Z26" s="179"/>
-      <c r="AA26" s="179"/>
+      <c r="T26" s="148"/>
+      <c r="V26" s="149"/>
+      <c r="W26" s="149"/>
+      <c r="X26" s="149"/>
+      <c r="Y26" s="149"/>
+      <c r="Z26" s="149"/>
+      <c r="AA26" s="149"/>
       <c r="AC26" s="128"/>
       <c r="AD26" s="128"/>
       <c r="AE26" s="128"/>
@@ -6515,63 +6652,63 @@
       <c r="AH26" s="129"/>
       <c r="AI26" s="130"/>
     </row>
-    <row r="27" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="165">
+    <row r="27" spans="1:35" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="135">
         <v>25</v>
       </c>
-      <c r="B27" s="165" t="s">
+      <c r="B27" s="135" t="s">
         <v>151</v>
       </c>
-      <c r="C27" s="163" t="s">
+      <c r="C27" s="133" t="s">
         <v>138</v>
       </c>
-      <c r="D27" s="166">
+      <c r="D27" s="136">
         <v>37.930999999999997</v>
       </c>
-      <c r="E27" s="168" t="s">
+      <c r="E27" s="138" t="s">
         <v>164</v>
       </c>
-      <c r="F27" s="171"/>
-      <c r="G27" s="168" t="s">
+      <c r="F27" s="141"/>
+      <c r="G27" s="138" t="s">
         <v>168</v>
       </c>
-      <c r="H27" s="168" t="s">
+      <c r="H27" s="138" t="s">
         <v>173</v>
       </c>
-      <c r="I27" s="168" t="s">
+      <c r="I27" s="138" t="s">
         <v>177</v>
       </c>
       <c r="J27" s="85" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve">YES </v>
       </c>
-      <c r="K27" s="187">
+      <c r="K27" s="157">
         <v>45983</v>
       </c>
-      <c r="L27" s="185">
+      <c r="L27" s="155">
         <v>45991</v>
       </c>
-      <c r="M27" s="185">
+      <c r="M27" s="155">
         <f>L27+10</f>
         <v>46001</v>
       </c>
-      <c r="N27" s="185">
+      <c r="N27" s="155">
         <f>L27+5</f>
         <v>45996</v>
       </c>
-      <c r="O27" s="183">
+      <c r="O27" s="153">
         <v>342752</v>
       </c>
       <c r="P27" s="100"/>
       <c r="Q27" s="127"/>
       <c r="R27" s="127"/>
-      <c r="T27" s="178"/>
-      <c r="V27" s="179"/>
-      <c r="W27" s="179"/>
-      <c r="X27" s="179"/>
-      <c r="Y27" s="179"/>
-      <c r="Z27" s="179"/>
-      <c r="AA27" s="179"/>
+      <c r="T27" s="148"/>
+      <c r="V27" s="149"/>
+      <c r="W27" s="149"/>
+      <c r="X27" s="149"/>
+      <c r="Y27" s="149"/>
+      <c r="Z27" s="149"/>
+      <c r="AA27" s="149"/>
       <c r="AC27" s="128"/>
       <c r="AD27" s="128"/>
       <c r="AE27" s="128"/>
@@ -6580,63 +6717,63 @@
       <c r="AH27" s="129"/>
       <c r="AI27" s="130"/>
     </row>
-    <row r="28" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="165">
+    <row r="28" spans="1:35" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="135">
         <v>27</v>
       </c>
-      <c r="B28" s="165" t="s">
+      <c r="B28" s="135" t="s">
         <v>154</v>
       </c>
-      <c r="C28" s="163" t="s">
+      <c r="C28" s="133" t="s">
         <v>155</v>
       </c>
-      <c r="D28" s="164">
+      <c r="D28" s="134">
         <v>90.24</v>
       </c>
-      <c r="E28" s="168" t="s">
+      <c r="E28" s="138" t="s">
         <v>165</v>
       </c>
-      <c r="F28" s="171"/>
-      <c r="G28" s="168" t="s">
+      <c r="F28" s="141"/>
+      <c r="G28" s="138" t="s">
         <v>168</v>
       </c>
-      <c r="H28" s="168" t="s">
+      <c r="H28" s="138" t="s">
         <v>174</v>
       </c>
-      <c r="I28" s="168" t="s">
+      <c r="I28" s="138" t="s">
         <v>107</v>
       </c>
       <c r="J28" s="85" t="str">
         <f t="shared" si="3"/>
         <v>No</v>
       </c>
-      <c r="K28" s="187">
+      <c r="K28" s="157">
         <v>45976</v>
       </c>
-      <c r="L28" s="185">
+      <c r="L28" s="155">
         <v>45982</v>
       </c>
-      <c r="M28" s="185">
+      <c r="M28" s="155">
         <f t="shared" si="4"/>
         <v>45992</v>
       </c>
-      <c r="N28" s="185">
+      <c r="N28" s="155">
         <f t="shared" si="2"/>
         <v>45987</v>
       </c>
-      <c r="O28" s="183">
+      <c r="O28" s="153">
         <v>796222</v>
       </c>
       <c r="P28" s="100"/>
       <c r="Q28" s="127"/>
       <c r="R28" s="127"/>
-      <c r="T28" s="178"/>
-      <c r="V28" s="179"/>
-      <c r="W28" s="179"/>
-      <c r="X28" s="179"/>
-      <c r="Y28" s="179"/>
-      <c r="Z28" s="179"/>
-      <c r="AA28" s="179"/>
+      <c r="T28" s="148"/>
+      <c r="V28" s="149"/>
+      <c r="W28" s="149"/>
+      <c r="X28" s="149"/>
+      <c r="Y28" s="149"/>
+      <c r="Z28" s="149"/>
+      <c r="AA28" s="149"/>
       <c r="AC28" s="128"/>
       <c r="AD28" s="128"/>
       <c r="AE28" s="128"/>
@@ -6645,63 +6782,63 @@
       <c r="AH28" s="129"/>
       <c r="AI28" s="130"/>
     </row>
-    <row r="29" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="165">
+    <row r="29" spans="1:35" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="135">
         <v>28</v>
       </c>
-      <c r="B29" s="165" t="s">
+      <c r="B29" s="135" t="s">
         <v>156</v>
       </c>
-      <c r="C29" s="163" t="s">
+      <c r="C29" s="133" t="s">
         <v>157</v>
       </c>
-      <c r="D29" s="164">
+      <c r="D29" s="134">
         <v>57.14</v>
       </c>
-      <c r="E29" s="168" t="s">
+      <c r="E29" s="138" t="s">
         <v>165</v>
       </c>
-      <c r="F29" s="171"/>
-      <c r="G29" s="168" t="s">
+      <c r="F29" s="141"/>
+      <c r="G29" s="138" t="s">
         <v>168</v>
       </c>
-      <c r="H29" s="168" t="s">
+      <c r="H29" s="138" t="s">
         <v>174</v>
       </c>
-      <c r="I29" s="168" t="s">
+      <c r="I29" s="138" t="s">
         <v>107</v>
       </c>
       <c r="J29" s="85" t="str">
         <f t="shared" si="3"/>
         <v>No</v>
       </c>
-      <c r="K29" s="187">
+      <c r="K29" s="157">
         <v>45983</v>
       </c>
-      <c r="L29" s="185">
+      <c r="L29" s="155">
         <v>45991</v>
       </c>
-      <c r="M29" s="185">
+      <c r="M29" s="155">
         <f t="shared" si="4"/>
         <v>46001</v>
       </c>
-      <c r="N29" s="185">
+      <c r="N29" s="155">
         <f t="shared" si="2"/>
         <v>45996</v>
       </c>
-      <c r="O29" s="183">
+      <c r="O29" s="153">
         <v>500493</v>
       </c>
       <c r="P29" s="100"/>
       <c r="Q29" s="127"/>
       <c r="R29" s="127"/>
-      <c r="T29" s="178"/>
-      <c r="V29" s="179"/>
-      <c r="W29" s="179"/>
-      <c r="X29" s="179"/>
-      <c r="Y29" s="179"/>
-      <c r="Z29" s="179"/>
-      <c r="AA29" s="179"/>
+      <c r="T29" s="148"/>
+      <c r="V29" s="149"/>
+      <c r="W29" s="149"/>
+      <c r="X29" s="149"/>
+      <c r="Y29" s="149"/>
+      <c r="Z29" s="149"/>
+      <c r="AA29" s="149"/>
       <c r="AC29" s="128"/>
       <c r="AD29" s="128"/>
       <c r="AE29" s="128"/>
@@ -6710,63 +6847,63 @@
       <c r="AH29" s="129"/>
       <c r="AI29" s="130"/>
     </row>
-    <row r="30" spans="1:35" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="165">
+    <row r="30" spans="1:35" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="135">
         <v>29</v>
       </c>
-      <c r="B30" s="182" t="s">
+      <c r="B30" s="152" t="s">
         <v>158</v>
       </c>
-      <c r="C30" s="163" t="s">
+      <c r="C30" s="133" t="s">
         <v>138</v>
       </c>
-      <c r="D30" s="164">
+      <c r="D30" s="134">
         <v>37.930999999999997</v>
       </c>
-      <c r="E30" s="168" t="s">
+      <c r="E30" s="138" t="s">
         <v>166</v>
       </c>
-      <c r="F30" s="171"/>
-      <c r="G30" s="168" t="s">
+      <c r="F30" s="141"/>
+      <c r="G30" s="138" t="s">
         <v>168</v>
       </c>
-      <c r="H30" s="168" t="s">
+      <c r="H30" s="138" t="s">
         <v>168</v>
       </c>
-      <c r="I30" s="168" t="s">
+      <c r="I30" s="138" t="s">
         <v>107</v>
       </c>
       <c r="J30" s="85" t="str">
         <f t="shared" si="3"/>
         <v>No</v>
       </c>
-      <c r="K30" s="190">
+      <c r="K30" s="160">
         <v>45964</v>
       </c>
-      <c r="L30" s="185">
+      <c r="L30" s="155">
         <v>45966</v>
       </c>
-      <c r="M30" s="185">
+      <c r="M30" s="155">
         <f t="shared" si="4"/>
         <v>45976</v>
       </c>
-      <c r="N30" s="185">
+      <c r="N30" s="155">
         <f t="shared" si="2"/>
         <v>45971</v>
       </c>
-      <c r="O30" s="183">
+      <c r="O30" s="153">
         <v>342752</v>
       </c>
       <c r="P30" s="100"/>
       <c r="Q30" s="127"/>
       <c r="R30" s="127"/>
-      <c r="T30" s="178"/>
-      <c r="V30" s="179"/>
-      <c r="W30" s="179"/>
-      <c r="X30" s="179"/>
-      <c r="Y30" s="179"/>
-      <c r="Z30" s="179"/>
-      <c r="AA30" s="179"/>
+      <c r="T30" s="148"/>
+      <c r="V30" s="149"/>
+      <c r="W30" s="149"/>
+      <c r="X30" s="149"/>
+      <c r="Y30" s="149"/>
+      <c r="Z30" s="149"/>
+      <c r="AA30" s="149"/>
       <c r="AC30" s="128"/>
       <c r="AD30" s="128"/>
       <c r="AE30" s="128"/>
@@ -6775,63 +6912,63 @@
       <c r="AH30" s="129"/>
       <c r="AI30" s="130"/>
     </row>
-    <row r="31" spans="1:35" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="165">
+    <row r="31" spans="1:35" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="135">
         <v>30</v>
       </c>
-      <c r="B31" s="182" t="s">
+      <c r="B31" s="152" t="s">
         <v>159</v>
       </c>
-      <c r="C31" s="163" t="s">
+      <c r="C31" s="133" t="s">
         <v>160</v>
       </c>
-      <c r="D31" s="164">
+      <c r="D31" s="134">
         <v>101.9</v>
       </c>
-      <c r="E31" s="168" t="s">
+      <c r="E31" s="138" t="s">
         <v>166</v>
       </c>
-      <c r="F31" s="171"/>
-      <c r="G31" s="168" t="s">
+      <c r="F31" s="141"/>
+      <c r="G31" s="138" t="s">
         <v>168</v>
       </c>
-      <c r="H31" s="168" t="s">
+      <c r="H31" s="138" t="s">
         <v>168</v>
       </c>
-      <c r="I31" s="168" t="s">
+      <c r="I31" s="138" t="s">
         <v>107</v>
       </c>
       <c r="J31" s="85" t="str">
         <f t="shared" si="3"/>
         <v>No</v>
       </c>
-      <c r="K31" s="190">
+      <c r="K31" s="160">
         <v>45969</v>
       </c>
-      <c r="L31" s="185">
+      <c r="L31" s="155">
         <v>45991</v>
       </c>
-      <c r="M31" s="185">
+      <c r="M31" s="155">
         <f t="shared" si="4"/>
         <v>46001</v>
       </c>
-      <c r="N31" s="185">
+      <c r="N31" s="155">
         <f t="shared" si="2"/>
         <v>45996</v>
       </c>
-      <c r="O31" s="183">
+      <c r="O31" s="153">
         <v>550754</v>
       </c>
       <c r="P31" s="100"/>
       <c r="Q31" s="127"/>
       <c r="R31" s="127"/>
-      <c r="T31" s="178"/>
-      <c r="V31" s="179"/>
-      <c r="W31" s="179"/>
-      <c r="X31" s="179"/>
-      <c r="Y31" s="179"/>
-      <c r="Z31" s="179"/>
-      <c r="AA31" s="179"/>
+      <c r="T31" s="148"/>
+      <c r="V31" s="149"/>
+      <c r="W31" s="149"/>
+      <c r="X31" s="149"/>
+      <c r="Y31" s="149"/>
+      <c r="Z31" s="149"/>
+      <c r="AA31" s="149"/>
       <c r="AC31" s="128"/>
       <c r="AD31" s="128"/>
       <c r="AE31" s="128"/>
@@ -6841,317 +6978,271 @@
       <c r="AI31" s="130"/>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="B2:B3 B5:B7">
+    <cfRule type="duplicateValues" dxfId="70" priority="127"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2:B3 B5:B8 B10:B14">
+    <cfRule type="duplicateValues" dxfId="69" priority="1375"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B3 B5:B8 B10:B14">
+    <cfRule type="duplicateValues" dxfId="68" priority="1379"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B17">
+    <cfRule type="duplicateValues" dxfId="67" priority="123"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="124"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B18">
+    <cfRule type="duplicateValues" dxfId="65" priority="125"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="126"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B26:B27 B2:B3 B21:B23 B5:B19">
+    <cfRule type="duplicateValues" dxfId="63" priority="1367"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B28:B31 B24:B25">
+    <cfRule type="duplicateValues" dxfId="62" priority="1396"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="B32:B1048576 B1">
-    <cfRule type="duplicateValues" dxfId="80" priority="160"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="160"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J14 K16 J16:J31">
-    <cfRule type="containsText" dxfId="79" priority="179" operator="containsText" text="WIP">
+    <cfRule type="containsText" dxfId="60" priority="197" operator="containsText" text="Complete">
+      <formula>NOT(ISERROR(SEARCH("Complete",J2)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="59" priority="198" operator="containsText" text="ROW">
+      <formula>NOT(ISERROR(SEARCH("ROW",J2)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="58" priority="179" operator="containsText" text="WIP">
       <formula>NOT(ISERROR(SEARCH("WIP",J2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="78" priority="182" operator="containsText" text="Complete">
+    <cfRule type="containsText" dxfId="57" priority="182" operator="containsText" text="Complete">
       <formula>NOT(ISERROR(SEARCH("Complete",J2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="77" priority="183" operator="containsText" text="ROW">
+    <cfRule type="containsText" dxfId="56" priority="183" operator="containsText" text="ROW">
       <formula>NOT(ISERROR(SEARCH("ROW",J2)))</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L2:N7 L9:N14 L8:M8 J2:J14 N15 K17:N18 K16:M16 O17 K25:K26 J28:N31 O26:O30 J16:J27 O24 L23:N26 K27:N27">
-    <cfRule type="containsText" dxfId="76" priority="185" operator="containsText" text="Complete">
-      <formula>NOT(ISERROR(SEARCH("Complete",J2)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="75" priority="186" operator="containsText" text="ROW">
-      <formula>NOT(ISERROR(SEARCH("ROW",J2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L2:N7 L9:N14 L8:M8 N15 K17:N18 K16:M16 O17 K25:K26 O26:O30 O24 L23:N26 K27:N31">
-    <cfRule type="containsText" dxfId="74" priority="184" operator="containsText" text="WIP">
-      <formula>NOT(ISERROR(SEARCH("WIP",K2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J14 K16 J16:J31">
-    <cfRule type="containsText" dxfId="73" priority="198" operator="containsText" text="ROW">
-      <formula>NOT(ISERROR(SEARCH("ROW",J2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J14 K16 J16:J31">
-    <cfRule type="containsText" dxfId="72" priority="197" operator="containsText" text="Complete">
-      <formula>NOT(ISERROR(SEARCH("Complete",J2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B3 B5:B7">
-    <cfRule type="duplicateValues" dxfId="71" priority="127"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B17">
-    <cfRule type="duplicateValues" dxfId="70" priority="123"/>
-    <cfRule type="duplicateValues" dxfId="69" priority="124"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B18">
-    <cfRule type="duplicateValues" dxfId="68" priority="125"/>
-    <cfRule type="duplicateValues" dxfId="67" priority="126"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B26:B27 B2:B3 B21:B23 B5:B19">
-    <cfRule type="duplicateValues" dxfId="66" priority="1367"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B3 B5:B8 B10:B14">
-    <cfRule type="duplicateValues" dxfId="65" priority="1375"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B3 B5:B8 B10:B14">
-    <cfRule type="duplicateValues" dxfId="64" priority="1379"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K3:K7 K9:K13 K20:K22">
-    <cfRule type="containsText" dxfId="63" priority="111" operator="containsText" text="Complete">
+    <cfRule type="containsText" dxfId="55" priority="112" operator="containsText" text="ROW">
+      <formula>NOT(ISERROR(SEARCH("ROW",K3)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="54" priority="111" operator="containsText" text="Complete">
       <formula>NOT(ISERROR(SEARCH("Complete",K3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="62" priority="112" operator="containsText" text="ROW">
-      <formula>NOT(ISERROR(SEARCH("ROW",K3)))</formula>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K3:K7 K9:K13 K20:N22">
+    <cfRule type="containsText" dxfId="53" priority="110" operator="containsText" text="WIP">
+      <formula>NOT(ISERROR(SEARCH("WIP",K3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K3:K7 L4:L5 K9:K13">
-    <cfRule type="containsText" dxfId="61" priority="109" operator="containsText" text="ROW">
+    <cfRule type="containsText" dxfId="52" priority="108" operator="containsText" text="Complete">
+      <formula>NOT(ISERROR(SEARCH("Complete",K3)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="51" priority="109" operator="containsText" text="ROW">
       <formula>NOT(ISERROR(SEARCH("ROW",K3)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K3:K7 K9:K13 K20:N22">
-    <cfRule type="containsText" dxfId="60" priority="110" operator="containsText" text="WIP">
-      <formula>NOT(ISERROR(SEARCH("WIP",K3)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K20:K22">
-    <cfRule type="containsText" dxfId="59" priority="66" operator="containsText" text="Complete">
-      <formula>NOT(ISERROR(SEARCH("Complete",K20)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="58" priority="67" operator="containsText" text="ROW">
-      <formula>NOT(ISERROR(SEARCH("ROW",K20)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K3:K7">
-    <cfRule type="containsText" dxfId="57" priority="70" operator="containsText" text="Complete">
+    <cfRule type="containsText" dxfId="50" priority="70" operator="containsText" text="Complete">
       <formula>NOT(ISERROR(SEARCH("Complete",K3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="56" priority="71" operator="containsText" text="ROW">
+    <cfRule type="containsText" dxfId="49" priority="71" operator="containsText" text="ROW">
       <formula>NOT(ISERROR(SEARCH("ROW",K3)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L4:L5 K3:K7 K9:K13">
-    <cfRule type="containsText" dxfId="55" priority="108" operator="containsText" text="Complete">
-      <formula>NOT(ISERROR(SEARCH("Complete",K3)))</formula>
+  <conditionalFormatting sqref="K16:M16 L2:N7 L9:N14 O24 O26:O30 L8:M8 N15 K17:N18 L23:N26 K25:K26 K27:N31">
+    <cfRule type="containsText" dxfId="48" priority="184" operator="containsText" text="WIP">
+      <formula>NOT(ISERROR(SEARCH("WIP",K2)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K20:N22">
+    <cfRule type="containsText" dxfId="47" priority="66" operator="containsText" text="Complete">
+      <formula>NOT(ISERROR(SEARCH("Complete",K20)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="46" priority="67" operator="containsText" text="ROW">
+      <formula>NOT(ISERROR(SEARCH("ROW",K20)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L10:L11">
-    <cfRule type="containsText" dxfId="54" priority="72" operator="containsText" text="Complete">
+    <cfRule type="containsText" dxfId="45" priority="72" operator="containsText" text="Complete">
       <formula>NOT(ISERROR(SEARCH("Complete",L10)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="53" priority="73" operator="containsText" text="ROW">
+    <cfRule type="containsText" dxfId="44" priority="73" operator="containsText" text="ROW">
       <formula>NOT(ISERROR(SEARCH("ROW",L10)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L20:N22">
-    <cfRule type="containsText" dxfId="52" priority="74" operator="containsText" text="Complete">
-      <formula>NOT(ISERROR(SEARCH("Complete",L20)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="51" priority="75" operator="containsText" text="ROW">
-      <formula>NOT(ISERROR(SEARCH("ROW",L20)))</formula>
+  <conditionalFormatting sqref="L15">
+    <cfRule type="containsText" dxfId="43" priority="3" operator="containsText" text="ROW">
+      <formula>NOT(ISERROR(SEARCH("ROW",L15)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="42" priority="2" operator="containsText" text="Complete">
+      <formula>NOT(ISERROR(SEARCH("Complete",L15)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="41" priority="1" operator="containsText" text="WIP">
+      <formula>NOT(ISERROR(SEARCH("WIP",L15)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2:N7 J2:J14 L8:M8 L9:N14 N15 K16:M16 J16:J27 K17:N18 L23:N26 O24 K25:K26 O26:O30 K27:N27 J28:N31">
+    <cfRule type="containsText" dxfId="40" priority="186" operator="containsText" text="ROW">
+      <formula>NOT(ISERROR(SEARCH("ROW",J2)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2:N7 L8:M8 L9:N14 N15 K16:M16 K17:N18 L23:N26 O24 K25:K26 O26:O30 K27:N27 J28:N31 J2:J14 J16:J27">
+    <cfRule type="containsText" dxfId="39" priority="185" operator="containsText" text="Complete">
+      <formula>NOT(ISERROR(SEARCH("Complete",J2)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L19:N19">
+    <cfRule type="containsText" dxfId="38" priority="18" operator="containsText" text="ROW">
+      <formula>NOT(ISERROR(SEARCH("ROW",L19)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="37" priority="17" operator="containsText" text="Complete">
+      <formula>NOT(ISERROR(SEARCH("Complete",L19)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L19:O19">
+    <cfRule type="containsText" dxfId="36" priority="19" operator="containsText" text="WIP">
+      <formula>NOT(ISERROR(SEARCH("WIP",L19)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O2:O3">
-    <cfRule type="containsText" dxfId="50" priority="60" operator="containsText" text="WIP">
+    <cfRule type="containsText" dxfId="35" priority="60" operator="containsText" text="WIP">
       <formula>NOT(ISERROR(SEARCH("WIP",O2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="49" priority="61" operator="containsText" text="Complete">
+    <cfRule type="containsText" dxfId="34" priority="61" operator="containsText" text="Complete">
       <formula>NOT(ISERROR(SEARCH("Complete",O2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="48" priority="62" operator="containsText" text="ROW">
+    <cfRule type="containsText" dxfId="33" priority="62" operator="containsText" text="ROW">
       <formula>NOT(ISERROR(SEARCH("ROW",O2)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O3:O7">
-    <cfRule type="containsText" dxfId="47" priority="36" operator="containsText" text="Complete">
+  <conditionalFormatting sqref="O3:O8">
+    <cfRule type="containsText" dxfId="32" priority="37" operator="containsText" text="ROW">
+      <formula>NOT(ISERROR(SEARCH("ROW",O3)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="31" priority="36" operator="containsText" text="Complete">
       <formula>NOT(ISERROR(SEARCH("Complete",O3)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="46" priority="37" operator="containsText" text="ROW">
-      <formula>NOT(ISERROR(SEARCH("ROW",O3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O4">
-    <cfRule type="containsText" dxfId="45" priority="33" operator="containsText" text="Complete">
+    <cfRule type="containsText" dxfId="30" priority="33" operator="containsText" text="Complete">
       <formula>NOT(ISERROR(SEARCH("Complete",O4)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="44" priority="34" operator="containsText" text="ROW">
+    <cfRule type="containsText" dxfId="29" priority="34" operator="containsText" text="ROW">
       <formula>NOT(ISERROR(SEARCH("ROW",O4)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O4:O7">
-    <cfRule type="containsText" dxfId="43" priority="35" operator="containsText" text="WIP">
+  <conditionalFormatting sqref="O4:O8">
+    <cfRule type="containsText" dxfId="28" priority="35" operator="containsText" text="WIP">
       <formula>NOT(ISERROR(SEARCH("WIP",O4)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O6:O7">
-    <cfRule type="containsText" dxfId="42" priority="31" operator="containsText" text="Complete">
+    <cfRule type="containsText" dxfId="27" priority="31" operator="containsText" text="Complete">
       <formula>NOT(ISERROR(SEARCH("Complete",O6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="41" priority="32" operator="containsText" text="ROW">
+    <cfRule type="containsText" dxfId="26" priority="32" operator="containsText" text="ROW">
       <formula>NOT(ISERROR(SEARCH("ROW",O6)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O8 O10">
-    <cfRule type="containsText" dxfId="40" priority="57" operator="containsText" text="WIP">
-      <formula>NOT(ISERROR(SEARCH("WIP",O8)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="39" priority="58" operator="containsText" text="Complete">
-      <formula>NOT(ISERROR(SEARCH("Complete",O8)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="38" priority="59" operator="containsText" text="ROW">
-      <formula>NOT(ISERROR(SEARCH("ROW",O8)))</formula>
+  <conditionalFormatting sqref="O9">
+    <cfRule type="containsText" dxfId="25" priority="28" operator="containsText" text="ROW">
+      <formula>NOT(ISERROR(SEARCH("ROW",O9)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="24" priority="26" operator="containsText" text="WIP">
+      <formula>NOT(ISERROR(SEARCH("WIP",O9)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="23" priority="27" operator="containsText" text="Complete">
+      <formula>NOT(ISERROR(SEARCH("Complete",O9)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O10">
+    <cfRule type="containsText" dxfId="22" priority="59" operator="containsText" text="ROW">
+      <formula>NOT(ISERROR(SEARCH("ROW",O10)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="21" priority="57" operator="containsText" text="WIP">
+      <formula>NOT(ISERROR(SEARCH("WIP",O10)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="20" priority="58" operator="containsText" text="Complete">
+      <formula>NOT(ISERROR(SEARCH("Complete",O10)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O10:O13">
-    <cfRule type="containsText" dxfId="37" priority="55" operator="containsText" text="Complete">
+    <cfRule type="containsText" dxfId="19" priority="55" operator="containsText" text="Complete">
       <formula>NOT(ISERROR(SEARCH("Complete",O10)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="36" priority="56" operator="containsText" text="ROW">
+    <cfRule type="containsText" dxfId="18" priority="56" operator="containsText" text="ROW">
       <formula>NOT(ISERROR(SEARCH("ROW",O10)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O11:O13">
-    <cfRule type="containsText" dxfId="35" priority="54" operator="containsText" text="WIP">
+    <cfRule type="containsText" dxfId="17" priority="54" operator="containsText" text="WIP">
       <formula>NOT(ISERROR(SEARCH("WIP",O11)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O13">
+    <cfRule type="containsText" dxfId="16" priority="25" operator="containsText" text="ROW">
+      <formula>NOT(ISERROR(SEARCH("ROW",O13)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="15" priority="24" operator="containsText" text="Complete">
+      <formula>NOT(ISERROR(SEARCH("Complete",O13)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O13:O14">
-    <cfRule type="containsText" dxfId="34" priority="52" operator="containsText" text="Complete">
+    <cfRule type="containsText" dxfId="14" priority="53" operator="containsText" text="ROW">
+      <formula>NOT(ISERROR(SEARCH("ROW",O13)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="13" priority="52" operator="containsText" text="Complete">
       <formula>NOT(ISERROR(SEARCH("Complete",O13)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="33" priority="53" operator="containsText" text="ROW">
-      <formula>NOT(ISERROR(SEARCH("ROW",O13)))</formula>
-    </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O14">
-    <cfRule type="containsText" dxfId="32" priority="51" operator="containsText" text="WIP">
-      <formula>NOT(ISERROR(SEARCH("WIP",O14)))</formula>
+  <conditionalFormatting sqref="O13:O17">
+    <cfRule type="containsText" dxfId="12" priority="11" operator="containsText" text="WIP">
+      <formula>NOT(ISERROR(SEARCH("WIP",O13)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O20:O21">
-    <cfRule type="containsText" dxfId="31" priority="46" operator="containsText" text="WIP">
+  <conditionalFormatting sqref="O15:O16">
+    <cfRule type="containsText" dxfId="11" priority="9" operator="containsText" text="Complete">
+      <formula>NOT(ISERROR(SEARCH("Complete",O15)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="10" priority="10" operator="containsText" text="ROW">
+      <formula>NOT(ISERROR(SEARCH("ROW",O15)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O15:O17">
+    <cfRule type="containsText" dxfId="9" priority="13" operator="containsText" text="ROW">
+      <formula>NOT(ISERROR(SEARCH("ROW",O15)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="8" priority="12" operator="containsText" text="Complete">
+      <formula>NOT(ISERROR(SEARCH("Complete",O15)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O19:O20">
+    <cfRule type="containsText" dxfId="7" priority="20" operator="containsText" text="Complete">
+      <formula>NOT(ISERROR(SEARCH("Complete",O19)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="6" priority="21" operator="containsText" text="ROW">
+      <formula>NOT(ISERROR(SEARCH("ROW",O19)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O20:O24">
+    <cfRule type="containsText" dxfId="5" priority="41" operator="containsText" text="WIP">
       <formula>NOT(ISERROR(SEARCH("WIP",O20)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="30" priority="47" operator="containsText" text="Complete">
+    <cfRule type="containsText" dxfId="4" priority="42" operator="containsText" text="Complete">
       <formula>NOT(ISERROR(SEARCH("Complete",O20)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="29" priority="48" operator="containsText" text="ROW">
+    <cfRule type="containsText" dxfId="3" priority="43" operator="containsText" text="ROW">
       <formula>NOT(ISERROR(SEARCH("ROW",O20)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O20">
-    <cfRule type="containsText" dxfId="28" priority="44" operator="containsText" text="Complete">
-      <formula>NOT(ISERROR(SEARCH("Complete",O20)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="27" priority="45" operator="containsText" text="ROW">
-      <formula>NOT(ISERROR(SEARCH("ROW",O20)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O22:O24">
-    <cfRule type="containsText" dxfId="26" priority="41" operator="containsText" text="WIP">
-      <formula>NOT(ISERROR(SEARCH("WIP",O22)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="25" priority="42" operator="containsText" text="Complete">
-      <formula>NOT(ISERROR(SEARCH("Complete",O22)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="24" priority="43" operator="containsText" text="ROW">
-      <formula>NOT(ISERROR(SEARCH("ROW",O22)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O26">
-    <cfRule type="containsText" dxfId="23" priority="39" operator="containsText" text="Complete">
+    <cfRule type="containsText" dxfId="2" priority="39" operator="containsText" text="Complete">
       <formula>NOT(ISERROR(SEARCH("Complete",O26)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="22" priority="40" operator="containsText" text="ROW">
+    <cfRule type="containsText" dxfId="1" priority="40" operator="containsText" text="ROW">
       <formula>NOT(ISERROR(SEARCH("ROW",O26)))</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O9">
-    <cfRule type="containsText" dxfId="21" priority="27" operator="containsText" text="Complete">
-      <formula>NOT(ISERROR(SEARCH("Complete",O9)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="20" priority="28" operator="containsText" text="ROW">
-      <formula>NOT(ISERROR(SEARCH("ROW",O9)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O9">
-    <cfRule type="containsText" dxfId="19" priority="26" operator="containsText" text="WIP">
-      <formula>NOT(ISERROR(SEARCH("WIP",O9)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O13">
-    <cfRule type="containsText" dxfId="18" priority="23" operator="containsText" text="WIP">
-      <formula>NOT(ISERROR(SEARCH("WIP",O13)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="17" priority="24" operator="containsText" text="Complete">
-      <formula>NOT(ISERROR(SEARCH("Complete",O13)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="16" priority="25" operator="containsText" text="ROW">
-      <formula>NOT(ISERROR(SEARCH("ROW",O13)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L19:N19">
-    <cfRule type="containsText" dxfId="15" priority="22" operator="containsText" text="WIP">
-      <formula>NOT(ISERROR(SEARCH("WIP",L19)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L19:N19">
-    <cfRule type="containsText" dxfId="14" priority="17" operator="containsText" text="Complete">
-      <formula>NOT(ISERROR(SEARCH("Complete",L19)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="13" priority="18" operator="containsText" text="ROW">
-      <formula>NOT(ISERROR(SEARCH("ROW",L19)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O19">
-    <cfRule type="containsText" dxfId="12" priority="19" operator="containsText" text="WIP">
-      <formula>NOT(ISERROR(SEARCH("WIP",O19)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="11" priority="20" operator="containsText" text="Complete">
-      <formula>NOT(ISERROR(SEARCH("Complete",O19)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="10" priority="21" operator="containsText" text="ROW">
-      <formula>NOT(ISERROR(SEARCH("ROW",O19)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O15:O16">
-    <cfRule type="containsText" dxfId="9" priority="9" operator="containsText" text="Complete">
-      <formula>NOT(ISERROR(SEARCH("Complete",O15)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="8" priority="10" operator="containsText" text="ROW">
-      <formula>NOT(ISERROR(SEARCH("ROW",O15)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O15:O16">
-    <cfRule type="containsText" dxfId="7" priority="12" operator="containsText" text="Complete">
-      <formula>NOT(ISERROR(SEARCH("Complete",O15)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="6" priority="13" operator="containsText" text="ROW">
-      <formula>NOT(ISERROR(SEARCH("ROW",O15)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O15:O16">
-    <cfRule type="containsText" dxfId="5" priority="11" operator="containsText" text="WIP">
-      <formula>NOT(ISERROR(SEARCH("WIP",O15)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L15">
-    <cfRule type="containsText" dxfId="4" priority="2" operator="containsText" text="Complete">
-      <formula>NOT(ISERROR(SEARCH("Complete",L15)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="3" priority="3" operator="containsText" text="ROW">
-      <formula>NOT(ISERROR(SEARCH("ROW",L15)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L15">
-    <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="WIP">
-      <formula>NOT(ISERROR(SEARCH("WIP",L15)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B28:B31 B24:B25">
-    <cfRule type="duplicateValues" dxfId="1" priority="1396"/>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7160,55 +7251,555 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F813407-BB56-4257-97C7-4D69D83F8D4A}">
+  <dimension ref="A1:O11"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="13" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12" style="191" customWidth="1"/>
+    <col min="2" max="2" width="10.81640625" style="191" customWidth="1"/>
+    <col min="3" max="3" width="28.7265625" style="191" customWidth="1"/>
+    <col min="4" max="4" width="21.7265625" style="191" customWidth="1"/>
+    <col min="5" max="5" width="24.26953125" style="191" customWidth="1"/>
+    <col min="6" max="6" width="19.453125" style="191" customWidth="1"/>
+    <col min="7" max="7" width="19.1796875" style="191" customWidth="1"/>
+    <col min="8" max="8" width="19.26953125" style="191" customWidth="1"/>
+    <col min="9" max="9" width="25.7265625" style="191" customWidth="1"/>
+    <col min="10" max="10" width="25.1796875" style="191" customWidth="1"/>
+    <col min="11" max="11" width="17.1796875" style="191" customWidth="1"/>
+    <col min="12" max="12" width="22.54296875" style="191" customWidth="1"/>
+    <col min="13" max="13" width="26.81640625" style="191" customWidth="1"/>
+    <col min="14" max="14" width="41.7265625" style="191" customWidth="1"/>
+    <col min="15" max="15" width="23.1796875" style="191" customWidth="1"/>
+    <col min="16" max="16384" width="9.1796875" style="191"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="1:15" ht="55.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="192" t="s">
+        <v>180</v>
+      </c>
+      <c r="B2" s="193" t="s">
+        <v>181</v>
+      </c>
+      <c r="C2" s="194" t="s">
+        <v>182</v>
+      </c>
+      <c r="D2" s="193" t="s">
+        <v>183</v>
+      </c>
+      <c r="E2" s="193" t="s">
+        <v>184</v>
+      </c>
+      <c r="F2" s="193" t="s">
+        <v>185</v>
+      </c>
+      <c r="G2" s="193" t="s">
+        <v>186</v>
+      </c>
+      <c r="H2" s="193" t="s">
+        <v>187</v>
+      </c>
+      <c r="I2" s="193" t="s">
+        <v>188</v>
+      </c>
+      <c r="J2" s="193" t="s">
+        <v>189</v>
+      </c>
+      <c r="K2" s="195" t="s">
+        <v>190</v>
+      </c>
+      <c r="L2" s="195" t="s">
+        <v>109</v>
+      </c>
+      <c r="M2" s="196" t="s">
+        <v>191</v>
+      </c>
+      <c r="N2" s="197" t="s">
+        <v>105</v>
+      </c>
+      <c r="O2" s="198" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" ht="66.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="199">
+        <v>1</v>
+      </c>
+      <c r="B3" s="200" t="s">
+        <v>192</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="D3" s="8">
+        <v>1.5389999999999999</v>
+      </c>
+      <c r="E3" s="201" t="s">
+        <v>176</v>
+      </c>
+      <c r="F3" s="199">
+        <v>5</v>
+      </c>
+      <c r="G3" s="114">
+        <v>45961</v>
+      </c>
+      <c r="H3" s="114">
+        <v>45971</v>
+      </c>
+      <c r="I3" s="114">
+        <v>45974</v>
+      </c>
+      <c r="J3" s="202">
+        <v>45976</v>
+      </c>
+      <c r="K3" s="203" t="s">
+        <v>194</v>
+      </c>
+      <c r="L3" s="204" t="s">
+        <v>195</v>
+      </c>
+      <c r="M3" s="204">
+        <v>40</v>
+      </c>
+      <c r="N3" s="199" t="s">
+        <v>196</v>
+      </c>
+      <c r="O3" s="199" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" ht="63" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="199">
+        <v>2</v>
+      </c>
+      <c r="B4" s="200" t="s">
+        <v>198</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="D4" s="8">
+        <v>4.7619999999999996</v>
+      </c>
+      <c r="E4" s="201" t="s">
+        <v>199</v>
+      </c>
+      <c r="F4" s="199">
+        <v>12</v>
+      </c>
+      <c r="G4" s="156">
+        <v>45976</v>
+      </c>
+      <c r="H4" s="114">
+        <v>45977</v>
+      </c>
+      <c r="I4" s="114">
+        <v>45981</v>
+      </c>
+      <c r="J4" s="202">
+        <v>45984</v>
+      </c>
+      <c r="K4" s="203" t="s">
+        <v>194</v>
+      </c>
+      <c r="L4" s="204" t="s">
+        <v>195</v>
+      </c>
+      <c r="M4" s="204">
+        <v>40</v>
+      </c>
+      <c r="N4" s="199" t="s">
+        <v>196</v>
+      </c>
+      <c r="O4" s="199" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" ht="63" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="199">
+        <v>3</v>
+      </c>
+      <c r="B5" s="200" t="s">
+        <v>200</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="D5" s="8">
+        <v>1.909</v>
+      </c>
+      <c r="E5" s="201" t="s">
+        <v>176</v>
+      </c>
+      <c r="F5" s="199">
+        <v>5</v>
+      </c>
+      <c r="G5" s="114">
+        <v>45981</v>
+      </c>
+      <c r="H5" s="114">
+        <v>45982</v>
+      </c>
+      <c r="I5" s="114">
+        <v>45985</v>
+      </c>
+      <c r="J5" s="202">
+        <v>45988</v>
+      </c>
+      <c r="K5" s="203" t="s">
+        <v>194</v>
+      </c>
+      <c r="L5" s="204" t="s">
+        <v>195</v>
+      </c>
+      <c r="M5" s="204">
+        <v>40</v>
+      </c>
+      <c r="N5" s="199" t="s">
+        <v>196</v>
+      </c>
+      <c r="O5" s="199" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="199">
+        <v>4</v>
+      </c>
+      <c r="B6" s="200" t="s">
+        <v>201</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="D6" s="8">
+        <v>0.248</v>
+      </c>
+      <c r="E6" s="201" t="s">
+        <v>176</v>
+      </c>
+      <c r="F6" s="199">
+        <v>2</v>
+      </c>
+      <c r="G6" s="114">
+        <v>45986</v>
+      </c>
+      <c r="H6" s="114">
+        <v>45987</v>
+      </c>
+      <c r="I6" s="114">
+        <v>45991</v>
+      </c>
+      <c r="J6" s="202">
+        <v>45991</v>
+      </c>
+      <c r="K6" s="205" t="s">
+        <v>203</v>
+      </c>
+      <c r="L6" s="204" t="s">
+        <v>195</v>
+      </c>
+      <c r="M6" s="204">
+        <v>40</v>
+      </c>
+      <c r="N6" s="199" t="s">
+        <v>196</v>
+      </c>
+      <c r="O6" s="199" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="199">
+        <v>5</v>
+      </c>
+      <c r="B7" s="200" t="s">
+        <v>202</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="D7" s="8">
+        <v>0.43</v>
+      </c>
+      <c r="E7" s="201" t="s">
+        <v>176</v>
+      </c>
+      <c r="F7" s="199">
+        <v>1</v>
+      </c>
+      <c r="G7" s="114">
+        <v>45986</v>
+      </c>
+      <c r="H7" s="114">
+        <v>45987</v>
+      </c>
+      <c r="I7" s="114">
+        <v>45991</v>
+      </c>
+      <c r="J7" s="202">
+        <v>45991</v>
+      </c>
+      <c r="K7" s="205" t="s">
+        <v>203</v>
+      </c>
+      <c r="L7" s="204" t="s">
+        <v>195</v>
+      </c>
+      <c r="M7" s="204">
+        <v>40</v>
+      </c>
+      <c r="N7" s="199" t="s">
+        <v>196</v>
+      </c>
+      <c r="O7" s="199" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="199">
+        <v>6</v>
+      </c>
+      <c r="B8" s="200" t="s">
+        <v>204</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>205</v>
+      </c>
+      <c r="D8" s="8">
+        <v>0.248</v>
+      </c>
+      <c r="E8" s="201" t="s">
+        <v>176</v>
+      </c>
+      <c r="F8" s="199">
+        <v>1</v>
+      </c>
+      <c r="G8" s="114">
+        <v>45986</v>
+      </c>
+      <c r="H8" s="114">
+        <v>45987</v>
+      </c>
+      <c r="I8" s="114">
+        <v>45991</v>
+      </c>
+      <c r="J8" s="202">
+        <v>45991</v>
+      </c>
+      <c r="K8" s="205" t="s">
+        <v>203</v>
+      </c>
+      <c r="L8" s="204" t="s">
+        <v>195</v>
+      </c>
+      <c r="M8" s="204">
+        <v>40</v>
+      </c>
+      <c r="N8" s="199" t="s">
+        <v>196</v>
+      </c>
+      <c r="O8" s="199" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" ht="68.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="199">
+        <v>7</v>
+      </c>
+      <c r="B9" s="200" t="s">
+        <v>206</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="D9" s="8">
+        <v>4.91</v>
+      </c>
+      <c r="E9" s="201" t="s">
+        <v>176</v>
+      </c>
+      <c r="F9" s="199">
+        <v>12</v>
+      </c>
+      <c r="G9" s="114">
+        <v>45961</v>
+      </c>
+      <c r="H9" s="114">
+        <v>45972</v>
+      </c>
+      <c r="I9" s="114">
+        <v>45976</v>
+      </c>
+      <c r="J9" s="202">
+        <v>45979</v>
+      </c>
+      <c r="K9" s="205" t="s">
+        <v>208</v>
+      </c>
+      <c r="L9" s="199" t="s">
+        <v>209</v>
+      </c>
+      <c r="M9" s="199">
+        <v>45</v>
+      </c>
+      <c r="N9" s="199" t="s">
+        <v>210</v>
+      </c>
+      <c r="O9" s="199" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" ht="76.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="199">
+        <v>8</v>
+      </c>
+      <c r="B10" s="200" t="s">
+        <v>207</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="D10" s="8">
+        <v>0.498</v>
+      </c>
+      <c r="E10" s="201" t="s">
+        <v>176</v>
+      </c>
+      <c r="F10" s="199">
+        <v>1</v>
+      </c>
+      <c r="G10" s="114">
+        <v>45976</v>
+      </c>
+      <c r="H10" s="114">
+        <v>45977</v>
+      </c>
+      <c r="I10" s="114">
+        <v>45978</v>
+      </c>
+      <c r="J10" s="202">
+        <v>45981</v>
+      </c>
+      <c r="K10" s="205" t="s">
+        <v>208</v>
+      </c>
+      <c r="L10" s="199" t="s">
+        <v>209</v>
+      </c>
+      <c r="M10" s="199">
+        <v>45</v>
+      </c>
+      <c r="N10" s="199" t="s">
+        <v>210</v>
+      </c>
+      <c r="O10" s="199" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" ht="63" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="199">
+        <v>9</v>
+      </c>
+      <c r="B11" s="200" t="s">
+        <v>212</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>213</v>
+      </c>
+      <c r="D11" s="8">
+        <v>4.7510000000000003</v>
+      </c>
+      <c r="E11" s="206" t="s">
+        <v>214</v>
+      </c>
+      <c r="F11" s="199">
+        <v>11</v>
+      </c>
+      <c r="G11" s="114">
+        <v>45985</v>
+      </c>
+      <c r="H11" s="114">
+        <v>45986</v>
+      </c>
+      <c r="I11" s="114">
+        <v>45991</v>
+      </c>
+      <c r="J11" s="202">
+        <v>45991</v>
+      </c>
+      <c r="K11" s="205" t="s">
+        <v>208</v>
+      </c>
+      <c r="L11" s="199" t="s">
+        <v>209</v>
+      </c>
+      <c r="M11" s="199">
+        <v>45</v>
+      </c>
+      <c r="N11" s="199" t="s">
+        <v>210</v>
+      </c>
+      <c r="O11" s="199" t="s">
+        <v>211</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21CFCD75-33F5-49B3-A4C8-4F19BD2235FD}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AB34"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="3.42578125" style="4" customWidth="1"/>
-    <col min="2" max="2" width="15.28515625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="11.28515625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="12.5703125" style="4" customWidth="1"/>
-    <col min="5" max="5" width="12.7109375" style="4" customWidth="1"/>
-    <col min="6" max="6" width="10.140625" style="4" customWidth="1"/>
-    <col min="7" max="7" width="12.5703125" style="4" customWidth="1"/>
-    <col min="8" max="8" width="11.5703125" style="1" customWidth="1"/>
-    <col min="9" max="10" width="10.7109375" style="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" customWidth="1"/>
-    <col min="12" max="12" width="3.140625" style="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" customWidth="1"/>
-    <col min="14" max="14" width="3.140625" style="1" customWidth="1"/>
-    <col min="15" max="15" width="10.5703125" style="1" customWidth="1"/>
-    <col min="16" max="20" width="8.7109375" style="1" customWidth="1"/>
-    <col min="21" max="21" width="3.140625" style="1" customWidth="1"/>
-    <col min="22" max="22" width="10.7109375" style="1" customWidth="1"/>
-    <col min="23" max="23" width="12.5703125" style="1" customWidth="1"/>
-    <col min="24" max="24" width="12.42578125" style="1" customWidth="1"/>
-    <col min="25" max="26" width="10.7109375" style="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" customWidth="1"/>
-    <col min="28" max="28" width="17.28515625" style="1" customWidth="1"/>
-    <col min="29" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="3.453125" style="4" customWidth="1"/>
+    <col min="2" max="2" width="15.26953125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="11.26953125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="12.54296875" style="4" customWidth="1"/>
+    <col min="5" max="5" width="12.7265625" style="4" customWidth="1"/>
+    <col min="6" max="6" width="10.1796875" style="4" customWidth="1"/>
+    <col min="7" max="7" width="12.54296875" style="4" customWidth="1"/>
+    <col min="8" max="8" width="11.54296875" style="1" customWidth="1"/>
+    <col min="9" max="10" width="10.7265625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="14.81640625" style="1" customWidth="1"/>
+    <col min="12" max="12" width="3.1796875" style="1" customWidth="1"/>
+    <col min="13" max="13" width="14.54296875" style="1" customWidth="1"/>
+    <col min="14" max="14" width="3.1796875" style="1" customWidth="1"/>
+    <col min="15" max="15" width="10.54296875" style="1" customWidth="1"/>
+    <col min="16" max="20" width="8.7265625" style="1" customWidth="1"/>
+    <col min="21" max="21" width="3.1796875" style="1" customWidth="1"/>
+    <col min="22" max="22" width="10.7265625" style="1" customWidth="1"/>
+    <col min="23" max="23" width="12.54296875" style="1" customWidth="1"/>
+    <col min="24" max="24" width="12.453125" style="1" customWidth="1"/>
+    <col min="25" max="26" width="10.7265625" style="1" customWidth="1"/>
+    <col min="27" max="27" width="14.453125" style="1" customWidth="1"/>
+    <col min="28" max="28" width="17.26953125" style="1" customWidth="1"/>
+    <col min="29" max="16384" width="9.1796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="38"/>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A2" s="13" t="s">
         <v>21</v>
       </c>
       <c r="D2" s="1"/>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A3" s="6"/>
       <c r="D3" s="1"/>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A4" s="13" t="s">
         <v>22</v>
       </c>
@@ -7225,7 +7816,7 @@
         <v>905812</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A5" s="6"/>
       <c r="D5" s="2" t="s">
         <v>29</v>
@@ -7235,7 +7826,7 @@
       </c>
       <c r="O5" s="119"/>
     </row>
-    <row r="6" spans="1:15" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" ht="16" x14ac:dyDescent="0.35">
       <c r="A6" s="6"/>
       <c r="D6" s="2" t="s">
         <v>88</v>
@@ -7244,7 +7835,7 @@
         <v>32.6</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A7" s="6"/>
       <c r="D7" s="2" t="s">
         <v>2</v>
@@ -7254,11 +7845,11 @@
         <v>82.4</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="5.0999999999999996" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" ht="5.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A8" s="6"/>
       <c r="D8" s="1"/>
     </row>
-    <row r="9" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A9" s="13" t="s">
         <v>23</v>
       </c>
@@ -7280,13 +7871,13 @@
         <v>32</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" ht="5.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="13"/>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
       <c r="F10" s="13"/>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A11" s="13" t="s">
         <v>33</v>
       </c>
@@ -7310,7 +7901,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A12" s="5"/>
       <c r="D12" s="2" t="s">
         <v>25</v>
@@ -7332,7 +7923,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A13" s="5"/>
       <c r="D13" s="2" t="s">
         <v>26</v>
@@ -7354,7 +7945,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A14" s="5"/>
       <c r="D14" s="2" t="s">
         <v>27</v>
@@ -7376,7 +7967,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" ht="16" x14ac:dyDescent="0.35">
       <c r="A15" s="5"/>
       <c r="D15" s="28" t="s">
         <v>28</v>
@@ -7398,7 +7989,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A16" s="5"/>
       <c r="D16" s="27" t="s">
         <v>29</v>
@@ -7420,125 +8011,125 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A17" s="5"/>
       <c r="D17" s="6"/>
       <c r="E17" s="6"/>
       <c r="F17" s="6"/>
     </row>
-    <row r="18" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="135" t="s">
+    <row r="18" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="179" t="s">
         <v>4</v>
       </c>
-      <c r="B18" s="135" t="s">
+      <c r="B18" s="179" t="s">
         <v>42</v>
       </c>
-      <c r="C18" s="132" t="s">
+      <c r="C18" s="175" t="s">
         <v>47</v>
       </c>
-      <c r="D18" s="132" t="s">
+      <c r="D18" s="175" t="s">
         <v>43</v>
       </c>
-      <c r="E18" s="135" t="s">
+      <c r="E18" s="179" t="s">
         <v>8</v>
       </c>
-      <c r="F18" s="147" t="s">
+      <c r="F18" s="166" t="s">
         <v>18</v>
       </c>
-      <c r="G18" s="147"/>
-      <c r="H18" s="147"/>
-      <c r="I18" s="147"/>
-      <c r="J18" s="147"/>
-      <c r="K18" s="140" t="s">
+      <c r="G18" s="166"/>
+      <c r="H18" s="166"/>
+      <c r="I18" s="166"/>
+      <c r="J18" s="166"/>
+      <c r="K18" s="169" t="s">
         <v>19</v>
       </c>
-      <c r="M18" s="132" t="s">
+      <c r="M18" s="175" t="s">
         <v>36</v>
       </c>
-      <c r="O18" s="141" t="s">
+      <c r="O18" s="170" t="s">
         <v>31</v>
       </c>
-      <c r="P18" s="142"/>
-      <c r="Q18" s="142"/>
-      <c r="R18" s="142"/>
-      <c r="S18" s="142"/>
-      <c r="T18" s="143"/>
-      <c r="V18" s="141" t="s">
+      <c r="P18" s="171"/>
+      <c r="Q18" s="171"/>
+      <c r="R18" s="171"/>
+      <c r="S18" s="171"/>
+      <c r="T18" s="172"/>
+      <c r="V18" s="170" t="s">
         <v>30</v>
       </c>
-      <c r="W18" s="142"/>
-      <c r="X18" s="142"/>
-      <c r="Y18" s="142"/>
-      <c r="Z18" s="142"/>
-      <c r="AA18" s="143"/>
-      <c r="AB18" s="144" t="s">
+      <c r="W18" s="171"/>
+      <c r="X18" s="171"/>
+      <c r="Y18" s="171"/>
+      <c r="Z18" s="171"/>
+      <c r="AA18" s="172"/>
+      <c r="AB18" s="173" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="19" spans="1:28" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="136"/>
-      <c r="B19" s="136"/>
-      <c r="C19" s="133"/>
-      <c r="D19" s="136"/>
-      <c r="E19" s="136"/>
-      <c r="F19" s="159" t="s">
+    <row r="19" spans="1:28" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="180"/>
+      <c r="B19" s="180"/>
+      <c r="C19" s="177"/>
+      <c r="D19" s="180"/>
+      <c r="E19" s="180"/>
+      <c r="F19" s="187" t="s">
         <v>40</v>
       </c>
-      <c r="G19" s="160" t="s">
+      <c r="G19" s="188" t="s">
         <v>44</v>
       </c>
-      <c r="H19" s="161"/>
-      <c r="I19" s="160" t="s">
+      <c r="H19" s="189"/>
+      <c r="I19" s="188" t="s">
         <v>45</v>
       </c>
-      <c r="J19" s="161"/>
-      <c r="K19" s="140"/>
-      <c r="M19" s="146"/>
-      <c r="O19" s="138" t="s">
+      <c r="J19" s="189"/>
+      <c r="K19" s="169"/>
+      <c r="M19" s="176"/>
+      <c r="O19" s="167" t="s">
         <v>24</v>
       </c>
-      <c r="P19" s="138" t="s">
+      <c r="P19" s="167" t="s">
         <v>25</v>
       </c>
-      <c r="Q19" s="138" t="s">
+      <c r="Q19" s="167" t="s">
         <v>26</v>
       </c>
-      <c r="R19" s="138" t="s">
+      <c r="R19" s="167" t="s">
         <v>27</v>
       </c>
-      <c r="S19" s="138" t="s">
+      <c r="S19" s="167" t="s">
         <v>28</v>
       </c>
       <c r="T19" s="43" t="s">
         <v>29</v>
       </c>
-      <c r="V19" s="138" t="s">
+      <c r="V19" s="167" t="s">
         <v>24</v>
       </c>
-      <c r="W19" s="138" t="s">
+      <c r="W19" s="167" t="s">
         <v>25</v>
       </c>
-      <c r="X19" s="138" t="s">
+      <c r="X19" s="167" t="s">
         <v>26</v>
       </c>
-      <c r="Y19" s="138" t="s">
+      <c r="Y19" s="167" t="s">
         <v>27</v>
       </c>
-      <c r="Z19" s="138" t="s">
+      <c r="Z19" s="167" t="s">
         <v>28</v>
       </c>
       <c r="AA19" s="43" t="s">
         <v>29</v>
       </c>
-      <c r="AB19" s="145"/>
-    </row>
-    <row r="20" spans="1:28" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="136"/>
-      <c r="B20" s="136"/>
-      <c r="C20" s="133"/>
-      <c r="D20" s="136"/>
-      <c r="E20" s="136"/>
-      <c r="F20" s="159"/>
+      <c r="AB19" s="174"/>
+    </row>
+    <row r="20" spans="1:28" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="180"/>
+      <c r="B20" s="180"/>
+      <c r="C20" s="177"/>
+      <c r="D20" s="180"/>
+      <c r="E20" s="180"/>
+      <c r="F20" s="187"/>
       <c r="G20" s="94" t="s">
         <v>10</v>
       </c>
@@ -7557,17 +8148,17 @@
       <c r="M20" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="O20" s="139"/>
-      <c r="P20" s="139"/>
-      <c r="Q20" s="139"/>
-      <c r="R20" s="139"/>
-      <c r="S20" s="139"/>
+      <c r="O20" s="168"/>
+      <c r="P20" s="168"/>
+      <c r="Q20" s="168"/>
+      <c r="R20" s="168"/>
+      <c r="S20" s="168"/>
       <c r="T20" s="19"/>
-      <c r="V20" s="139"/>
-      <c r="W20" s="139"/>
-      <c r="X20" s="139"/>
-      <c r="Y20" s="139"/>
-      <c r="Z20" s="139"/>
+      <c r="V20" s="168"/>
+      <c r="W20" s="168"/>
+      <c r="X20" s="168"/>
+      <c r="Y20" s="168"/>
+      <c r="Z20" s="168"/>
       <c r="AA20" s="19" t="s">
         <v>20</v>
       </c>
@@ -7575,7 +8166,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:28" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="8">
         <v>1</v>
       </c>
@@ -7588,7 +8179,7 @@
       <c r="D21" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="E21" s="158" t="s">
+      <c r="E21" s="190" t="s">
         <v>98</v>
       </c>
       <c r="F21" s="114">
@@ -7649,7 +8240,7 @@
         <v>3270887.1320000002</v>
       </c>
     </row>
-    <row r="22" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:28" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="8">
         <v>2</v>
       </c>
@@ -7662,7 +8253,7 @@
       <c r="D22" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="E22" s="158"/>
+      <c r="E22" s="190"/>
       <c r="F22" s="114">
         <v>45913</v>
       </c>
@@ -7721,7 +8312,7 @@
         <v>3550783.04</v>
       </c>
     </row>
-    <row r="23" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:28" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="8">
         <v>3</v>
       </c>
@@ -7734,7 +8325,7 @@
       <c r="D23" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="E23" s="158"/>
+      <c r="E23" s="190"/>
       <c r="F23" s="114">
         <v>45910</v>
       </c>
@@ -7793,7 +8384,7 @@
         <v>253627.36000000002</v>
       </c>
     </row>
-    <row r="24" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:28" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="8">
         <v>4</v>
       </c>
@@ -7806,7 +8397,7 @@
       <c r="D24" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="E24" s="158"/>
+      <c r="E24" s="190"/>
       <c r="F24" s="114">
         <v>45927</v>
       </c>
@@ -7865,7 +8456,7 @@
         <v>283519.15600000002</v>
       </c>
     </row>
-    <row r="25" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:28" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="8">
         <v>5</v>
       </c>
@@ -7878,7 +8469,7 @@
       <c r="D25" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="E25" s="158"/>
+      <c r="E25" s="190"/>
       <c r="F25" s="114">
         <v>45915</v>
       </c>
@@ -7937,7 +8528,7 @@
         <v>288954.02799999999</v>
       </c>
     </row>
-    <row r="26" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:28" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="8">
         <v>6</v>
       </c>
@@ -8011,7 +8602,7 @@
         <v>4491015.8959999997</v>
       </c>
     </row>
-    <row r="27" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:28" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="8">
         <v>7</v>
       </c>
@@ -8083,7 +8674,7 @@
         <v>1454734.0720000002</v>
       </c>
     </row>
-    <row r="28" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:28" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="8">
         <v>8</v>
       </c>
@@ -8155,7 +8746,7 @@
         <v>292577.27600000001</v>
       </c>
     </row>
-    <row r="29" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:28" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="8">
         <v>9</v>
       </c>
@@ -8227,7 +8818,7 @@
         <v>4481051.9639999997</v>
       </c>
     </row>
-    <row r="30" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:28" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="8">
         <v>10</v>
       </c>
@@ -8299,7 +8890,7 @@
         <v>2490983</v>
       </c>
     </row>
-    <row r="31" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:28" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="8">
         <v>11</v>
       </c>
@@ -8371,7 +8962,7 @@
         <v>244569.24000000002</v>
       </c>
     </row>
-    <row r="32" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:28" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="8">
         <v>12</v>
       </c>
@@ -8443,7 +9034,7 @@
         <v>623198.65599999996</v>
       </c>
     </row>
-    <row r="33" spans="1:28" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:28" ht="20.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A33" s="8">
         <v>13</v>
       </c>
@@ -8499,7 +9090,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:28" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="9"/>
       <c r="B34" s="10"/>
       <c r="C34" s="125">
@@ -8573,6 +9164,18 @@
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="E21:E25"/>
+    <mergeCell ref="W19:W20"/>
+    <mergeCell ref="K18:K19"/>
+    <mergeCell ref="M18:M19"/>
+    <mergeCell ref="O18:T18"/>
+    <mergeCell ref="V18:AA18"/>
+    <mergeCell ref="V19:V20"/>
+    <mergeCell ref="A18:A20"/>
+    <mergeCell ref="B18:B20"/>
+    <mergeCell ref="C18:C20"/>
+    <mergeCell ref="D18:D20"/>
+    <mergeCell ref="E18:E20"/>
     <mergeCell ref="AB18:AB19"/>
     <mergeCell ref="F19:F20"/>
     <mergeCell ref="G19:H19"/>
@@ -8586,18 +9189,6 @@
     <mergeCell ref="Q19:Q20"/>
     <mergeCell ref="R19:R20"/>
     <mergeCell ref="S19:S20"/>
-    <mergeCell ref="A18:A20"/>
-    <mergeCell ref="B18:B20"/>
-    <mergeCell ref="C18:C20"/>
-    <mergeCell ref="D18:D20"/>
-    <mergeCell ref="E18:E20"/>
-    <mergeCell ref="E21:E25"/>
-    <mergeCell ref="W19:W20"/>
-    <mergeCell ref="K18:K19"/>
-    <mergeCell ref="M18:M19"/>
-    <mergeCell ref="O18:T18"/>
-    <mergeCell ref="V18:AA18"/>
-    <mergeCell ref="V19:V20"/>
   </mergeCells>
   <conditionalFormatting sqref="C26:C27">
     <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="4DT6">

--- a/Raw Data/Micro Plans/November 2025/Micro Plan - TA-421 Nov'25.xlsx
+++ b/Raw Data/Micro Plans/November 2025/Micro Plan - TA-421 Nov'25.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kaushikb\Documents\Work\Git\Office-work-\Raw Data\Micro Plans\November 2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ABE5E5B-1032-43D4-BF9B-84C78188882A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C965881B-D56B-4EDF-9D96-6A23D224259C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="757" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1777,96 +1777,6 @@
     <xf numFmtId="14" fontId="31" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="33" fillId="2" borderId="15" xfId="27" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1911,6 +1821,96 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2022,6 +2022,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -2042,6 +2052,26 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -2062,6 +2092,26 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C5700"/>
       </font>
       <fill>
@@ -2072,6 +2122,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -2102,6 +2162,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -2112,6 +2182,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C5700"/>
       </font>
       <fill>
@@ -2142,6 +2222,26 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -2152,6 +2252,46 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C5700"/>
       </font>
       <fill>
@@ -2162,6 +2302,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -2182,6 +2332,46 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C5700"/>
       </font>
       <fill>
@@ -2202,6 +2392,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -2252,6 +2452,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -2262,6 +2472,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -2272,6 +2492,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -2292,261 +2522,31 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C5700"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2892,6 +2892,31 @@
     </dxf>
     <dxf>
       <font>
+        <color indexed="20"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor indexed="45"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color indexed="20"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor indexed="45"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color indexed="20"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
         <color indexed="17"/>
       </font>
       <fill>
@@ -2899,31 +2924,6 @@
           <bgColor indexed="42"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color indexed="20"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor indexed="45"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color indexed="20"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor indexed="45"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color indexed="20"/>
-      </font>
     </dxf>
     <dxf>
       <font>
@@ -3745,137 +3745,137 @@
       <c r="F17" s="6"/>
     </row>
     <row r="18" spans="1:33" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="179" t="s">
+      <c r="A18" s="180" t="s">
         <v>4</v>
       </c>
-      <c r="B18" s="179" t="s">
+      <c r="B18" s="180" t="s">
         <v>5</v>
       </c>
-      <c r="C18" s="175" t="s">
+      <c r="C18" s="177" t="s">
         <v>6</v>
       </c>
-      <c r="D18" s="179" t="s">
+      <c r="D18" s="180" t="s">
         <v>7</v>
       </c>
-      <c r="E18" s="175" t="s">
+      <c r="E18" s="177" t="s">
         <v>16</v>
       </c>
-      <c r="F18" s="175" t="s">
+      <c r="F18" s="177" t="s">
         <v>17</v>
       </c>
-      <c r="G18" s="179" t="s">
+      <c r="G18" s="180" t="s">
         <v>8</v>
       </c>
-      <c r="H18" s="166" t="s">
+      <c r="H18" s="192" t="s">
         <v>18</v>
       </c>
-      <c r="I18" s="166"/>
-      <c r="J18" s="166"/>
-      <c r="K18" s="166"/>
-      <c r="L18" s="166"/>
-      <c r="M18" s="166"/>
-      <c r="N18" s="166"/>
-      <c r="O18" s="166"/>
-      <c r="P18" s="169" t="s">
+      <c r="I18" s="192"/>
+      <c r="J18" s="192"/>
+      <c r="K18" s="192"/>
+      <c r="L18" s="192"/>
+      <c r="M18" s="192"/>
+      <c r="N18" s="192"/>
+      <c r="O18" s="192"/>
+      <c r="P18" s="185" t="s">
         <v>19</v>
       </c>
-      <c r="R18" s="175" t="s">
+      <c r="R18" s="177" t="s">
         <v>36</v>
       </c>
-      <c r="T18" s="170" t="s">
+      <c r="T18" s="186" t="s">
         <v>31</v>
       </c>
-      <c r="U18" s="171"/>
-      <c r="V18" s="171"/>
-      <c r="W18" s="171"/>
-      <c r="X18" s="171"/>
-      <c r="Y18" s="172"/>
-      <c r="AA18" s="170" t="s">
+      <c r="U18" s="187"/>
+      <c r="V18" s="187"/>
+      <c r="W18" s="187"/>
+      <c r="X18" s="187"/>
+      <c r="Y18" s="188"/>
+      <c r="AA18" s="186" t="s">
         <v>30</v>
       </c>
-      <c r="AB18" s="171"/>
-      <c r="AC18" s="171"/>
-      <c r="AD18" s="171"/>
-      <c r="AE18" s="171"/>
-      <c r="AF18" s="172"/>
-      <c r="AG18" s="173" t="s">
+      <c r="AB18" s="187"/>
+      <c r="AC18" s="187"/>
+      <c r="AD18" s="187"/>
+      <c r="AE18" s="187"/>
+      <c r="AF18" s="188"/>
+      <c r="AG18" s="189" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="19" spans="1:33" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="180"/>
-      <c r="B19" s="180"/>
-      <c r="C19" s="177"/>
-      <c r="D19" s="180"/>
-      <c r="E19" s="177"/>
-      <c r="F19" s="177"/>
-      <c r="G19" s="180"/>
-      <c r="H19" s="165" t="s">
+      <c r="A19" s="181"/>
+      <c r="B19" s="181"/>
+      <c r="C19" s="178"/>
+      <c r="D19" s="181"/>
+      <c r="E19" s="178"/>
+      <c r="F19" s="178"/>
+      <c r="G19" s="181"/>
+      <c r="H19" s="197" t="s">
         <v>9</v>
       </c>
-      <c r="I19" s="165"/>
-      <c r="J19" s="165" t="s">
+      <c r="I19" s="197"/>
+      <c r="J19" s="197" t="s">
         <v>12</v>
       </c>
-      <c r="K19" s="165"/>
-      <c r="L19" s="165" t="s">
+      <c r="K19" s="197"/>
+      <c r="L19" s="197" t="s">
         <v>13</v>
       </c>
-      <c r="M19" s="165"/>
-      <c r="N19" s="163" t="s">
+      <c r="M19" s="197"/>
+      <c r="N19" s="193" t="s">
         <v>15</v>
       </c>
-      <c r="O19" s="163" t="s">
+      <c r="O19" s="193" t="s">
         <v>14</v>
       </c>
-      <c r="P19" s="169"/>
-      <c r="R19" s="176"/>
-      <c r="T19" s="167" t="s">
+      <c r="P19" s="185"/>
+      <c r="R19" s="191"/>
+      <c r="T19" s="183" t="s">
         <v>24</v>
       </c>
-      <c r="U19" s="167" t="s">
+      <c r="U19" s="183" t="s">
         <v>25</v>
       </c>
-      <c r="V19" s="167" t="s">
+      <c r="V19" s="183" t="s">
         <v>26</v>
       </c>
-      <c r="W19" s="167" t="s">
+      <c r="W19" s="183" t="s">
         <v>27</v>
       </c>
-      <c r="X19" s="167" t="s">
+      <c r="X19" s="183" t="s">
         <v>28</v>
       </c>
       <c r="Y19" s="43" t="s">
         <v>29</v>
       </c>
-      <c r="AA19" s="167" t="s">
+      <c r="AA19" s="183" t="s">
         <v>24</v>
       </c>
-      <c r="AB19" s="167" t="s">
+      <c r="AB19" s="183" t="s">
         <v>25</v>
       </c>
-      <c r="AC19" s="167" t="s">
+      <c r="AC19" s="183" t="s">
         <v>26</v>
       </c>
-      <c r="AD19" s="167" t="s">
+      <c r="AD19" s="183" t="s">
         <v>27</v>
       </c>
-      <c r="AE19" s="167" t="s">
+      <c r="AE19" s="183" t="s">
         <v>28</v>
       </c>
       <c r="AF19" s="43" t="s">
         <v>29</v>
       </c>
-      <c r="AG19" s="174"/>
+      <c r="AG19" s="190"/>
     </row>
     <row r="20" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="181"/>
-      <c r="B20" s="180"/>
-      <c r="C20" s="177"/>
-      <c r="D20" s="180"/>
-      <c r="E20" s="178"/>
-      <c r="F20" s="178"/>
-      <c r="G20" s="180"/>
+      <c r="A20" s="182"/>
+      <c r="B20" s="181"/>
+      <c r="C20" s="178"/>
+      <c r="D20" s="181"/>
+      <c r="E20" s="179"/>
+      <c r="F20" s="179"/>
+      <c r="G20" s="181"/>
       <c r="H20" s="94" t="s">
         <v>10</v>
       </c>
@@ -3894,25 +3894,25 @@
       <c r="M20" s="94" t="s">
         <v>11</v>
       </c>
-      <c r="N20" s="164"/>
-      <c r="O20" s="164"/>
+      <c r="N20" s="194"/>
+      <c r="O20" s="194"/>
       <c r="P20" s="44" t="s">
         <v>50</v>
       </c>
       <c r="R20" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="T20" s="168"/>
-      <c r="U20" s="168"/>
-      <c r="V20" s="168"/>
-      <c r="W20" s="168"/>
-      <c r="X20" s="168"/>
+      <c r="T20" s="184"/>
+      <c r="U20" s="184"/>
+      <c r="V20" s="184"/>
+      <c r="W20" s="184"/>
+      <c r="X20" s="184"/>
       <c r="Y20" s="19"/>
-      <c r="AA20" s="168"/>
-      <c r="AB20" s="168"/>
-      <c r="AC20" s="168"/>
-      <c r="AD20" s="168"/>
-      <c r="AE20" s="168"/>
+      <c r="AA20" s="184"/>
+      <c r="AB20" s="184"/>
+      <c r="AC20" s="184"/>
+      <c r="AD20" s="184"/>
+      <c r="AE20" s="184"/>
       <c r="AF20" s="19" t="s">
         <v>50</v>
       </c>
@@ -4183,7 +4183,7 @@
       <c r="D25" s="86"/>
       <c r="E25" s="101"/>
       <c r="F25" s="8"/>
-      <c r="G25" s="161"/>
+      <c r="G25" s="195"/>
       <c r="H25" s="99"/>
       <c r="I25" s="99"/>
       <c r="J25" s="99"/>
@@ -4241,7 +4241,7 @@
       <c r="D26" s="8"/>
       <c r="E26" s="102"/>
       <c r="F26" s="97"/>
-      <c r="G26" s="162"/>
+      <c r="G26" s="196"/>
       <c r="H26" s="99"/>
       <c r="I26" s="99"/>
       <c r="J26" s="99"/>
@@ -4596,13 +4596,16 @@
     <filterColumn colId="13" showButton="0"/>
   </autoFilter>
   <mergeCells count="29">
-    <mergeCell ref="F18:F20"/>
-    <mergeCell ref="G18:G20"/>
-    <mergeCell ref="A18:A20"/>
-    <mergeCell ref="B18:B20"/>
-    <mergeCell ref="C18:C20"/>
-    <mergeCell ref="D18:D20"/>
-    <mergeCell ref="E18:E20"/>
+    <mergeCell ref="G25:G26"/>
+    <mergeCell ref="O19:O20"/>
+    <mergeCell ref="H19:I19"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="L19:M19"/>
+    <mergeCell ref="H18:O18"/>
+    <mergeCell ref="N19:N20"/>
+    <mergeCell ref="U19:U20"/>
+    <mergeCell ref="V19:V20"/>
+    <mergeCell ref="W19:W20"/>
     <mergeCell ref="X19:X20"/>
     <mergeCell ref="P18:P19"/>
     <mergeCell ref="AA18:AF18"/>
@@ -4615,16 +4618,13 @@
     <mergeCell ref="R18:R19"/>
     <mergeCell ref="T18:Y18"/>
     <mergeCell ref="T19:T20"/>
-    <mergeCell ref="H18:O18"/>
-    <mergeCell ref="N19:N20"/>
-    <mergeCell ref="U19:U20"/>
-    <mergeCell ref="V19:V20"/>
-    <mergeCell ref="W19:W20"/>
-    <mergeCell ref="G25:G26"/>
-    <mergeCell ref="O19:O20"/>
-    <mergeCell ref="H19:I19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="L19:M19"/>
+    <mergeCell ref="F18:F20"/>
+    <mergeCell ref="G18:G20"/>
+    <mergeCell ref="A18:A20"/>
+    <mergeCell ref="B18:B20"/>
+    <mergeCell ref="C18:C20"/>
+    <mergeCell ref="D18:D20"/>
+    <mergeCell ref="E18:E20"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="B21">
@@ -4699,17 +4699,17 @@
     <cfRule type="expression" dxfId="99" priority="1243" stopIfTrue="1">
       <formula>AND(COUNTIF($D$1:$D$123, B26)+COUNTIF($D$142:$D$65380, B26)&gt;1,NOT(ISBLANK(B26)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="98" priority="1245" stopIfTrue="1">
+    <cfRule type="expression" dxfId="98" priority="1244" stopIfTrue="1">
       <formula>AND(COUNTIF($D$1:$D$191, B26)+COUNTIF($D$214:$D$65380, B26)&gt;1,NOT(ISBLANK(B26)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="97" priority="1246" stopIfTrue="1">
+    <cfRule type="expression" dxfId="97" priority="1245" stopIfTrue="1">
       <formula>AND(COUNTIF($D$1:$D$191, B26)+COUNTIF($D$214:$D$65380, B26)&gt;1,NOT(ISBLANK(B26)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="96" priority="1247" stopIfTrue="1">
+    <cfRule type="expression" dxfId="96" priority="1246" stopIfTrue="1">
+      <formula>AND(COUNTIF($D$1:$D$191, B26)+COUNTIF($D$214:$D$65380, B26)&gt;1,NOT(ISBLANK(B26)))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="95" priority="1247" stopIfTrue="1">
       <formula>AND(COUNTIF($D$474:$D$65380, B26)+COUNTIF($D$454:$D$455, B26)+COUNTIF($D$416:$D$417, B26)+COUNTIF($D$374:$D$377, B26)+COUNTIF($D$351:$D$352, B26)+COUNTIF($D$324:$D$325, B26)+COUNTIF($D$303:$D$303, B26)+COUNTIF($D$288:$D$289, B26)+COUNTIF($D$263:$D$263, B26)+COUNTIF($D$252:$D$253, B26)+COUNTIF($D$233:$D$234, B26)+COUNTIF($D$51:$D$218, B26)+COUNTIF($D$219:$D$220, B26)+COUNTIF($D$1:$D$50, B26)&gt;1,NOT(ISBLANK(B26)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="95" priority="1244" stopIfTrue="1">
-      <formula>AND(COUNTIF($D$1:$D$191, B26)+COUNTIF($D$214:$D$65380, B26)&gt;1,NOT(ISBLANK(B26)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B27">
@@ -4726,55 +4726,55 @@
     <cfRule type="duplicateValues" dxfId="88" priority="347"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="L4">
-    <cfRule type="expression" dxfId="87" priority="1221" stopIfTrue="1">
+    <cfRule type="expression" dxfId="87" priority="1220" stopIfTrue="1">
+      <formula>AND(COUNTIF($C$314:$C$65460, L4)+COUNTIF($C$294:$C$295, L4)+COUNTIF($C$256:$C$257, L4)+COUNTIF($C$214:$C$217, L4)+COUNTIF($C$191:$C$192, L4)+COUNTIF($C$164:$C$165, L4)+COUNTIF($C$143:$C$143, L4)+COUNTIF($C$128:$C$129, L4)+COUNTIF($C$103:$C$103, L4)+COUNTIF($C$92:$C$93, L4)+COUNTIF($C$73:$C$74, L4)+COUNTIF($C$29:$C$56, L4)+COUNTIF($C$58:$C$60, L4)+COUNTIF($C$1:$C$27, L4)&gt;1,NOT(ISBLANK(L4)))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="86" priority="1221" stopIfTrue="1">
       <formula>AND(COUNTIF($C$1:$C$65460, L4)+COUNTIF(#REF!, L4)&gt;1,NOT(ISBLANK(L4)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="86" priority="1220" stopIfTrue="1">
-      <formula>AND(COUNTIF($C$314:$C$65460, L4)+COUNTIF($C$294:$C$295, L4)+COUNTIF($C$256:$C$257, L4)+COUNTIF($C$214:$C$217, L4)+COUNTIF($C$191:$C$192, L4)+COUNTIF($C$164:$C$165, L4)+COUNTIF($C$143:$C$143, L4)+COUNTIF($C$128:$C$129, L4)+COUNTIF($C$103:$C$103, L4)+COUNTIF($C$92:$C$93, L4)+COUNTIF($C$73:$C$74, L4)+COUNTIF($C$29:$C$56, L4)+COUNTIF($C$58:$C$60, L4)+COUNTIF($C$1:$C$27, L4)&gt;1,NOT(ISBLANK(L4)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M4">
-    <cfRule type="expression" dxfId="85" priority="1223" stopIfTrue="1">
+    <cfRule type="expression" dxfId="85" priority="1222" stopIfTrue="1">
+      <formula>AND(COUNTIF($D$331:$D$65460, M4)+COUNTIF($D$1:$D$27, M4)+COUNTIF(#REF!, M4)+COUNTIF($D$314:$D$315, M4)+COUNTIF($D$294:$D$295, M4)+COUNTIF($D$256:$D$257, M4)+COUNTIF($D$214:$D$217, M4)+COUNTIF($D$191:$D$192, M4)+COUNTIF($D$164:$D$165, M4)+COUNTIF($D$143:$D$143, M4)+COUNTIF($D$128:$D$129, M4)+COUNTIF($D$103:$D$103, M4)+COUNTIF($D$92:$D$93, M4)+COUNTIF($D$73:$D$74, M4)+COUNTIF($D$58:$D$60, M4)&gt;1,NOT(ISBLANK(M4)))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="84" priority="1223" stopIfTrue="1">
       <formula>AND(COUNTIF($D$314:$D$65460, M4)+COUNTIF(#REF!, M4)+COUNTIF($D$1:$D$27, M4)+COUNTIF($D$294:$D$295, M4)+COUNTIF($D$256:$D$257, M4)+COUNTIF($D$214:$D$217, M4)+COUNTIF($D$191:$D$192, M4)+COUNTIF($D$164:$D$165, M4)+COUNTIF($D$143:$D$143, M4)+COUNTIF($D$128:$D$129, M4)+COUNTIF($D$103:$D$103, M4)+COUNTIF($D$92:$D$93, M4)+COUNTIF($D$73:$D$74, M4)+COUNTIF($D$58:$D$60, M4)&gt;1,NOT(ISBLANK(M4)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="84" priority="1224" stopIfTrue="1">
+    <cfRule type="expression" dxfId="83" priority="1224" stopIfTrue="1">
       <formula>AND(COUNTIF($D$294:$D$65460, M4)+COUNTIF($D$1:$D$27, M4)+COUNTIF($D$256:$D$257, M4)+COUNTIF(#REF!, M4)+COUNTIF($D$214:$D$217, M4)+COUNTIF($D$191:$D$192, M4)+COUNTIF($D$164:$D$165, M4)+COUNTIF($D$143:$D$143, M4)+COUNTIF($D$128:$D$129, M4)+COUNTIF($D$103:$D$103, M4)+COUNTIF($D$92:$D$93, M4)+COUNTIF($D$73:$D$74, M4)+COUNTIF($D$58:$D$60, M4)&gt;1,NOT(ISBLANK(M4)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="83" priority="1225" stopIfTrue="1">
+    <cfRule type="expression" dxfId="82" priority="1225" stopIfTrue="1">
       <formula>AND(COUNTIF($D$256:$D$65460, M4)+COUNTIF($D$1:$D$27, M4)+COUNTIF(#REF!, M4)+COUNTIF($D$214:$D$217, M4)+COUNTIF($D$191:$D$192, M4)+COUNTIF($D$164:$D$165, M4)+COUNTIF($D$143:$D$143, M4)+COUNTIF($D$128:$D$129, M4)+COUNTIF($D$103:$D$103, M4)+COUNTIF($D$92:$D$93, M4)+COUNTIF($D$73:$D$74, M4)+COUNTIF($D$58:$D$60, M4)&gt;1,NOT(ISBLANK(M4)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="82" priority="1226" stopIfTrue="1">
+    <cfRule type="expression" dxfId="81" priority="1226" stopIfTrue="1">
       <formula>AND(COUNTIF($D$214:$D$65460, M4)+COUNTIF(#REF!, M4)+COUNTIF($D$1:$D$27, M4)+COUNTIF($D$191:$D$192, M4)+COUNTIF($D$164:$D$165, M4)+COUNTIF($D$143:$D$143, M4)+COUNTIF($D$128:$D$129, M4)+COUNTIF($D$103:$D$103, M4)+COUNTIF($D$92:$D$93, M4)+COUNTIF($D$73:$D$74, M4)+COUNTIF($D$58:$D$60, M4)&gt;1,NOT(ISBLANK(M4)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="81" priority="1227" stopIfTrue="1">
+    <cfRule type="expression" dxfId="80" priority="1227" stopIfTrue="1">
       <formula>AND(COUNTIF($D$214:$D$65460, M4)+COUNTIF($D$191:$D$192, M4)+COUNTIF($D$164:$D$165, M4)+COUNTIF($D$143:$D$143, M4)+COUNTIF($D$128:$D$129, M4)+COUNTIF($D$1:$D$27, M4)+COUNTIF(#REF!, M4)+COUNTIF($D$103:$D$103, M4)+COUNTIF($D$92:$D$93, M4)+COUNTIF(#REF!, M4)+COUNTIF($D$73:$D$74, M4)+COUNTIF($D$51:$D$51, M4)+COUNTIF($D$53:$D$60, M4)+COUNTIF(#REF!, M4)&gt;1,NOT(ISBLANK(M4)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="80" priority="1228" stopIfTrue="1">
+    <cfRule type="expression" dxfId="79" priority="1228" stopIfTrue="1">
       <formula>AND(COUNTIF($D$191:$D$65460, M4)+COUNTIF($D$164:$D$165, M4)+COUNTIF($D$143:$D$143, M4)+COUNTIF($D$128:$D$129, M4)+COUNTIF($D$1:$D$27, M4)+COUNTIF(#REF!, M4)+COUNTIF($D$103:$D$103, M4)+COUNTIF($D$92:$D$93, M4)+COUNTIF(#REF!, M4)+COUNTIF($D$73:$D$74, M4)+COUNTIF($D$51:$D$51, M4)+COUNTIF($D$53:$D$60, M4)+COUNTIF(#REF!, M4)&gt;1,NOT(ISBLANK(M4)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="79" priority="1229" stopIfTrue="1">
+    <cfRule type="expression" dxfId="78" priority="1229" stopIfTrue="1">
       <formula>AND(COUNTIF($F$369:$F$65454, M4)+COUNTIF($F$1:$F$27, M4)+COUNTIF(#REF!, M4)+COUNTIF($F$352:$F$353, M4)+COUNTIF($F$332:$F$333, M4)+COUNTIF($F$294:$F$295, M4)+COUNTIF($F$252:$F$255, M4)+COUNTIF($F$229:$F$230, M4)+COUNTIF($F$202:$F$203, M4)+COUNTIF($F$181:$F$181, M4)+COUNTIF($F$166:$F$167, M4)+COUNTIF($F$141:$F$141, M4)+COUNTIF($F$130:$F$131, M4)+COUNTIF($F$111:$F$112, M4)+COUNTIF($F$96:$F$98, M4)&gt;1,NOT(ISBLANK(M4)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="78" priority="1230" stopIfTrue="1">
+    <cfRule type="expression" dxfId="77" priority="1230" stopIfTrue="1">
       <formula>AND(COUNTIF($F$352:$F$65454, M4)+COUNTIF(#REF!, M4)+COUNTIF($F$1:$F$27, M4)+COUNTIF($F$332:$F$333, M4)+COUNTIF($F$294:$F$295, M4)+COUNTIF($F$252:$F$255, M4)+COUNTIF($F$229:$F$230, M4)+COUNTIF($F$202:$F$203, M4)+COUNTIF($F$181:$F$181, M4)+COUNTIF($F$166:$F$167, M4)+COUNTIF($F$141:$F$141, M4)+COUNTIF($F$130:$F$131, M4)+COUNTIF($F$111:$F$112, M4)+COUNTIF($F$96:$F$98, M4)&gt;1,NOT(ISBLANK(M4)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="77" priority="1231" stopIfTrue="1">
+    <cfRule type="expression" dxfId="76" priority="1231" stopIfTrue="1">
       <formula>AND(COUNTIF($F$332:$F$65454, M4)+COUNTIF($F$1:$F$27, M4)+COUNTIF($F$294:$F$295, M4)+COUNTIF(#REF!, M4)+COUNTIF($F$252:$F$255, M4)+COUNTIF($F$229:$F$230, M4)+COUNTIF($F$202:$F$203, M4)+COUNTIF($F$181:$F$181, M4)+COUNTIF($F$166:$F$167, M4)+COUNTIF($F$141:$F$141, M4)+COUNTIF($F$130:$F$131, M4)+COUNTIF($F$111:$F$112, M4)+COUNTIF($F$96:$F$98, M4)&gt;1,NOT(ISBLANK(M4)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="76" priority="1232" stopIfTrue="1">
+    <cfRule type="expression" dxfId="75" priority="1232" stopIfTrue="1">
       <formula>AND(COUNTIF($F$294:$F$65454, M4)+COUNTIF($F$1:$F$27, M4)+COUNTIF(#REF!, M4)+COUNTIF($F$252:$F$255, M4)+COUNTIF($F$229:$F$230, M4)+COUNTIF($F$202:$F$203, M4)+COUNTIF($F$181:$F$181, M4)+COUNTIF($F$166:$F$167, M4)+COUNTIF($F$141:$F$141, M4)+COUNTIF($F$130:$F$131, M4)+COUNTIF($F$111:$F$112, M4)+COUNTIF($F$96:$F$98, M4)&gt;1,NOT(ISBLANK(M4)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="75" priority="1233" stopIfTrue="1">
+    <cfRule type="expression" dxfId="74" priority="1233" stopIfTrue="1">
       <formula>AND(COUNTIF($F$252:$F$65454, M4)+COUNTIF(#REF!, M4)+COUNTIF($F$1:$F$27, M4)+COUNTIF($F$229:$F$230, M4)+COUNTIF($F$202:$F$203, M4)+COUNTIF($F$181:$F$181, M4)+COUNTIF($F$166:$F$167, M4)+COUNTIF($F$141:$F$141, M4)+COUNTIF($F$130:$F$131, M4)+COUNTIF($F$111:$F$112, M4)+COUNTIF($F$96:$F$98, M4)&gt;1,NOT(ISBLANK(M4)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="74" priority="1234" stopIfTrue="1">
+    <cfRule type="expression" dxfId="73" priority="1234" stopIfTrue="1">
       <formula>AND(COUNTIF($F$252:$F$65454, M4)+COUNTIF($F$229:$F$230, M4)+COUNTIF($F$202:$F$203, M4)+COUNTIF($F$181:$F$181, M4)+COUNTIF($F$166:$F$167, M4)+COUNTIF($F$1:$F$27, M4)+COUNTIF(#REF!, M4)+COUNTIF($F$141:$F$141, M4)+COUNTIF($F$130:$F$131, M4)+COUNTIF(#REF!, M4)+COUNTIF($F$111:$F$112, M4)+COUNTIF($F$89:$F$89, M4)+COUNTIF($F$91:$F$98, M4)+COUNTIF(#REF!, M4)&gt;1,NOT(ISBLANK(M4)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="73" priority="1235" stopIfTrue="1">
+    <cfRule type="expression" dxfId="72" priority="1235" stopIfTrue="1">
       <formula>AND(COUNTIF($F$229:$F$65454, M4)+COUNTIF($F$202:$F$203, M4)+COUNTIF($F$181:$F$181, M4)+COUNTIF($F$166:$F$167, M4)+COUNTIF($F$1:$F$27, M4)+COUNTIF(#REF!, M4)+COUNTIF($F$141:$F$141, M4)+COUNTIF($F$130:$F$131, M4)+COUNTIF(#REF!, M4)+COUNTIF($F$111:$F$112, M4)+COUNTIF($F$89:$F$89, M4)+COUNTIF($F$91:$F$98, M4)+COUNTIF(#REF!, M4)&gt;1,NOT(ISBLANK(M4)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="72" priority="1222" stopIfTrue="1">
-      <formula>AND(COUNTIF($D$331:$D$65460, M4)+COUNTIF($D$1:$D$27, M4)+COUNTIF(#REF!, M4)+COUNTIF($D$314:$D$315, M4)+COUNTIF($D$294:$D$295, M4)+COUNTIF($D$256:$D$257, M4)+COUNTIF($D$214:$D$217, M4)+COUNTIF($D$191:$D$192, M4)+COUNTIF($D$164:$D$165, M4)+COUNTIF($D$143:$D$143, M4)+COUNTIF($D$128:$D$129, M4)+COUNTIF($D$103:$D$103, M4)+COUNTIF($D$92:$D$93, M4)+COUNTIF($D$73:$D$74, M4)+COUNTIF($D$58:$D$60, M4)&gt;1,NOT(ISBLANK(M4)))</formula>
     </cfRule>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
@@ -4895,7 +4895,7 @@
       <c r="Q4" s="70">
         <v>0</v>
       </c>
-      <c r="R4" s="182" t="s">
+      <c r="R4" s="198" t="s">
         <v>75</v>
       </c>
     </row>
@@ -4938,14 +4938,14 @@
       <c r="Q5" s="70">
         <v>0</v>
       </c>
-      <c r="R5" s="183"/>
+      <c r="R5" s="199"/>
     </row>
     <row r="6" spans="2:18" s="75" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="184" t="s">
+      <c r="B6" s="200" t="s">
         <v>29</v>
       </c>
-      <c r="C6" s="185"/>
-      <c r="D6" s="186"/>
+      <c r="C6" s="201"/>
+      <c r="D6" s="202"/>
       <c r="E6" s="73">
         <v>160</v>
       </c>
@@ -7005,28 +7005,28 @@
     <cfRule type="duplicateValues" dxfId="61" priority="160"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J14 K16 J16:J31">
-    <cfRule type="containsText" dxfId="60" priority="197" operator="containsText" text="Complete">
+    <cfRule type="containsText" dxfId="60" priority="179" operator="containsText" text="WIP">
+      <formula>NOT(ISERROR(SEARCH("WIP",J2)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="59" priority="182" operator="containsText" text="Complete">
       <formula>NOT(ISERROR(SEARCH("Complete",J2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="59" priority="198" operator="containsText" text="ROW">
+    <cfRule type="containsText" dxfId="58" priority="183" operator="containsText" text="ROW">
       <formula>NOT(ISERROR(SEARCH("ROW",J2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="58" priority="179" operator="containsText" text="WIP">
-      <formula>NOT(ISERROR(SEARCH("WIP",J2)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="57" priority="182" operator="containsText" text="Complete">
+    <cfRule type="containsText" dxfId="57" priority="197" operator="containsText" text="Complete">
       <formula>NOT(ISERROR(SEARCH("Complete",J2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="56" priority="183" operator="containsText" text="ROW">
+    <cfRule type="containsText" dxfId="56" priority="198" operator="containsText" text="ROW">
       <formula>NOT(ISERROR(SEARCH("ROW",J2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K3:K7 K9:K13 K20:K22">
-    <cfRule type="containsText" dxfId="55" priority="112" operator="containsText" text="ROW">
+    <cfRule type="containsText" dxfId="55" priority="111" operator="containsText" text="Complete">
+      <formula>NOT(ISERROR(SEARCH("Complete",K3)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="54" priority="112" operator="containsText" text="ROW">
       <formula>NOT(ISERROR(SEARCH("ROW",K3)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="54" priority="111" operator="containsText" text="Complete">
-      <formula>NOT(ISERROR(SEARCH("Complete",K3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K3:K7 K9:K13 K20:N22">
@@ -7072,14 +7072,14 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L15">
-    <cfRule type="containsText" dxfId="43" priority="3" operator="containsText" text="ROW">
-      <formula>NOT(ISERROR(SEARCH("ROW",L15)))</formula>
+    <cfRule type="containsText" dxfId="43" priority="1" operator="containsText" text="WIP">
+      <formula>NOT(ISERROR(SEARCH("WIP",L15)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="42" priority="2" operator="containsText" text="Complete">
       <formula>NOT(ISERROR(SEARCH("Complete",L15)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="41" priority="1" operator="containsText" text="WIP">
-      <formula>NOT(ISERROR(SEARCH("WIP",L15)))</formula>
+    <cfRule type="containsText" dxfId="41" priority="3" operator="containsText" text="ROW">
+      <formula>NOT(ISERROR(SEARCH("ROW",L15)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:N7 J2:J14 L8:M8 L9:N14 N15 K16:M16 J16:J27 K17:N18 L23:N26 O24 K25:K26 O26:O30 K27:N27 J28:N31">
@@ -7093,11 +7093,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L19:N19">
-    <cfRule type="containsText" dxfId="38" priority="18" operator="containsText" text="ROW">
+    <cfRule type="containsText" dxfId="38" priority="17" operator="containsText" text="Complete">
+      <formula>NOT(ISERROR(SEARCH("Complete",L19)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="37" priority="18" operator="containsText" text="ROW">
       <formula>NOT(ISERROR(SEARCH("ROW",L19)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="37" priority="17" operator="containsText" text="Complete">
-      <formula>NOT(ISERROR(SEARCH("Complete",L19)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L19:O19">
@@ -7117,11 +7117,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O3:O8">
-    <cfRule type="containsText" dxfId="32" priority="37" operator="containsText" text="ROW">
+    <cfRule type="containsText" dxfId="32" priority="36" operator="containsText" text="Complete">
+      <formula>NOT(ISERROR(SEARCH("Complete",O3)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="31" priority="37" operator="containsText" text="ROW">
       <formula>NOT(ISERROR(SEARCH("ROW",O3)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="31" priority="36" operator="containsText" text="Complete">
-      <formula>NOT(ISERROR(SEARCH("Complete",O3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O4">
@@ -7146,25 +7146,25 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O9">
-    <cfRule type="containsText" dxfId="25" priority="28" operator="containsText" text="ROW">
+    <cfRule type="containsText" dxfId="25" priority="26" operator="containsText" text="WIP">
+      <formula>NOT(ISERROR(SEARCH("WIP",O9)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="24" priority="27" operator="containsText" text="Complete">
+      <formula>NOT(ISERROR(SEARCH("Complete",O9)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="23" priority="28" operator="containsText" text="ROW">
       <formula>NOT(ISERROR(SEARCH("ROW",O9)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="24" priority="26" operator="containsText" text="WIP">
-      <formula>NOT(ISERROR(SEARCH("WIP",O9)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="23" priority="27" operator="containsText" text="Complete">
-      <formula>NOT(ISERROR(SEARCH("Complete",O9)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O10">
-    <cfRule type="containsText" dxfId="22" priority="59" operator="containsText" text="ROW">
+    <cfRule type="containsText" dxfId="22" priority="57" operator="containsText" text="WIP">
+      <formula>NOT(ISERROR(SEARCH("WIP",O10)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="21" priority="58" operator="containsText" text="Complete">
+      <formula>NOT(ISERROR(SEARCH("Complete",O10)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="20" priority="59" operator="containsText" text="ROW">
       <formula>NOT(ISERROR(SEARCH("ROW",O10)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="21" priority="57" operator="containsText" text="WIP">
-      <formula>NOT(ISERROR(SEARCH("WIP",O10)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="20" priority="58" operator="containsText" text="Complete">
-      <formula>NOT(ISERROR(SEARCH("Complete",O10)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O10:O13">
@@ -7181,19 +7181,19 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O13">
-    <cfRule type="containsText" dxfId="16" priority="25" operator="containsText" text="ROW">
+    <cfRule type="containsText" dxfId="16" priority="24" operator="containsText" text="Complete">
+      <formula>NOT(ISERROR(SEARCH("Complete",O13)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="15" priority="25" operator="containsText" text="ROW">
       <formula>NOT(ISERROR(SEARCH("ROW",O13)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="15" priority="24" operator="containsText" text="Complete">
-      <formula>NOT(ISERROR(SEARCH("Complete",O13)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O13:O14">
-    <cfRule type="containsText" dxfId="14" priority="53" operator="containsText" text="ROW">
+    <cfRule type="containsText" dxfId="14" priority="52" operator="containsText" text="Complete">
+      <formula>NOT(ISERROR(SEARCH("Complete",O13)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="13" priority="53" operator="containsText" text="ROW">
       <formula>NOT(ISERROR(SEARCH("ROW",O13)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="13" priority="52" operator="containsText" text="Complete">
-      <formula>NOT(ISERROR(SEARCH("Complete",O13)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O13:O17">
@@ -7210,11 +7210,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O15:O17">
-    <cfRule type="containsText" dxfId="9" priority="13" operator="containsText" text="ROW">
+    <cfRule type="containsText" dxfId="9" priority="12" operator="containsText" text="Complete">
+      <formula>NOT(ISERROR(SEARCH("Complete",O15)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="8" priority="13" operator="containsText" text="ROW">
       <formula>NOT(ISERROR(SEARCH("ROW",O15)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="8" priority="12" operator="containsText" text="Complete">
-      <formula>NOT(ISERROR(SEARCH("Complete",O15)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O19:O20">
@@ -7255,89 +7255,89 @@
   <dimension ref="A1:O11"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="13" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12" style="191" customWidth="1"/>
-    <col min="2" max="2" width="10.81640625" style="191" customWidth="1"/>
-    <col min="3" max="3" width="28.7265625" style="191" customWidth="1"/>
-    <col min="4" max="4" width="21.7265625" style="191" customWidth="1"/>
-    <col min="5" max="5" width="24.26953125" style="191" customWidth="1"/>
-    <col min="6" max="6" width="19.453125" style="191" customWidth="1"/>
-    <col min="7" max="7" width="19.1796875" style="191" customWidth="1"/>
-    <col min="8" max="8" width="19.26953125" style="191" customWidth="1"/>
-    <col min="9" max="9" width="25.7265625" style="191" customWidth="1"/>
-    <col min="10" max="10" width="25.1796875" style="191" customWidth="1"/>
-    <col min="11" max="11" width="17.1796875" style="191" customWidth="1"/>
-    <col min="12" max="12" width="22.54296875" style="191" customWidth="1"/>
-    <col min="13" max="13" width="26.81640625" style="191" customWidth="1"/>
-    <col min="14" max="14" width="41.7265625" style="191" customWidth="1"/>
-    <col min="15" max="15" width="23.1796875" style="191" customWidth="1"/>
-    <col min="16" max="16384" width="9.1796875" style="191"/>
+    <col min="1" max="1" width="12" style="161" customWidth="1"/>
+    <col min="2" max="2" width="10.81640625" style="161" customWidth="1"/>
+    <col min="3" max="3" width="28.7265625" style="161" customWidth="1"/>
+    <col min="4" max="4" width="21.7265625" style="161" customWidth="1"/>
+    <col min="5" max="5" width="24.26953125" style="161" customWidth="1"/>
+    <col min="6" max="6" width="19.453125" style="161" customWidth="1"/>
+    <col min="7" max="7" width="19.1796875" style="161" customWidth="1"/>
+    <col min="8" max="8" width="19.26953125" style="161" customWidth="1"/>
+    <col min="9" max="9" width="25.7265625" style="161" customWidth="1"/>
+    <col min="10" max="10" width="25.1796875" style="161" customWidth="1"/>
+    <col min="11" max="11" width="17.1796875" style="161" customWidth="1"/>
+    <col min="12" max="12" width="22.54296875" style="161" customWidth="1"/>
+    <col min="13" max="13" width="26.81640625" style="161" customWidth="1"/>
+    <col min="14" max="14" width="41.7265625" style="161" customWidth="1"/>
+    <col min="15" max="15" width="23.1796875" style="161" customWidth="1"/>
+    <col min="16" max="16384" width="9.1796875" style="161"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="1:15" ht="55.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="192" t="s">
+      <c r="A2" s="162" t="s">
         <v>180</v>
       </c>
-      <c r="B2" s="193" t="s">
+      <c r="B2" s="163" t="s">
         <v>181</v>
       </c>
-      <c r="C2" s="194" t="s">
+      <c r="C2" s="164" t="s">
         <v>182</v>
       </c>
-      <c r="D2" s="193" t="s">
+      <c r="D2" s="163" t="s">
         <v>183</v>
       </c>
-      <c r="E2" s="193" t="s">
+      <c r="E2" s="163" t="s">
         <v>184</v>
       </c>
-      <c r="F2" s="193" t="s">
+      <c r="F2" s="163" t="s">
         <v>185</v>
       </c>
-      <c r="G2" s="193" t="s">
+      <c r="G2" s="163" t="s">
         <v>186</v>
       </c>
-      <c r="H2" s="193" t="s">
+      <c r="H2" s="163" t="s">
         <v>187</v>
       </c>
-      <c r="I2" s="193" t="s">
+      <c r="I2" s="163" t="s">
         <v>188</v>
       </c>
-      <c r="J2" s="193" t="s">
+      <c r="J2" s="163" t="s">
         <v>189</v>
       </c>
-      <c r="K2" s="195" t="s">
+      <c r="K2" s="165" t="s">
         <v>190</v>
       </c>
-      <c r="L2" s="195" t="s">
+      <c r="L2" s="165" t="s">
         <v>109</v>
       </c>
-      <c r="M2" s="196" t="s">
+      <c r="M2" s="166" t="s">
         <v>191</v>
       </c>
-      <c r="N2" s="197" t="s">
+      <c r="N2" s="167" t="s">
         <v>105</v>
       </c>
-      <c r="O2" s="198" t="s">
+      <c r="O2" s="168" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="66.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="199">
+      <c r="A3" s="169">
         <v>1</v>
       </c>
-      <c r="B3" s="200" t="s">
+      <c r="B3" s="170" t="s">
         <v>192</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>193</v>
       </c>
       <c r="D3" s="8">
-        <v>1.5389999999999999</v>
-      </c>
-      <c r="E3" s="201" t="s">
+        <v>1539</v>
+      </c>
+      <c r="E3" s="171" t="s">
         <v>176</v>
       </c>
-      <c r="F3" s="199">
+      <c r="F3" s="169">
         <v>5</v>
       </c>
       <c r="G3" s="114">
@@ -7349,42 +7349,42 @@
       <c r="I3" s="114">
         <v>45974</v>
       </c>
-      <c r="J3" s="202">
+      <c r="J3" s="172">
         <v>45976</v>
       </c>
-      <c r="K3" s="203" t="s">
+      <c r="K3" s="173" t="s">
         <v>194</v>
       </c>
-      <c r="L3" s="204" t="s">
+      <c r="L3" s="174" t="s">
         <v>195</v>
       </c>
-      <c r="M3" s="204">
+      <c r="M3" s="174">
         <v>40</v>
       </c>
-      <c r="N3" s="199" t="s">
+      <c r="N3" s="169" t="s">
         <v>196</v>
       </c>
-      <c r="O3" s="199" t="s">
+      <c r="O3" s="169" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="4" spans="1:15" ht="63" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="199">
+      <c r="A4" s="169">
         <v>2</v>
       </c>
-      <c r="B4" s="200" t="s">
+      <c r="B4" s="170" t="s">
         <v>198</v>
       </c>
       <c r="C4" s="8" t="s">
         <v>192</v>
       </c>
       <c r="D4" s="8">
-        <v>4.7619999999999996</v>
-      </c>
-      <c r="E4" s="201" t="s">
+        <v>4762</v>
+      </c>
+      <c r="E4" s="171" t="s">
         <v>199</v>
       </c>
-      <c r="F4" s="199">
+      <c r="F4" s="169">
         <v>12</v>
       </c>
       <c r="G4" s="156">
@@ -7396,42 +7396,42 @@
       <c r="I4" s="114">
         <v>45981</v>
       </c>
-      <c r="J4" s="202">
+      <c r="J4" s="172">
         <v>45984</v>
       </c>
-      <c r="K4" s="203" t="s">
+      <c r="K4" s="173" t="s">
         <v>194</v>
       </c>
-      <c r="L4" s="204" t="s">
+      <c r="L4" s="174" t="s">
         <v>195</v>
       </c>
-      <c r="M4" s="204">
+      <c r="M4" s="174">
         <v>40</v>
       </c>
-      <c r="N4" s="199" t="s">
+      <c r="N4" s="169" t="s">
         <v>196</v>
       </c>
-      <c r="O4" s="199" t="s">
+      <c r="O4" s="169" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="5" spans="1:15" ht="63" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="199">
+      <c r="A5" s="169">
         <v>3</v>
       </c>
-      <c r="B5" s="200" t="s">
+      <c r="B5" s="170" t="s">
         <v>200</v>
       </c>
       <c r="C5" s="8" t="s">
         <v>198</v>
       </c>
       <c r="D5" s="8">
-        <v>1.909</v>
-      </c>
-      <c r="E5" s="201" t="s">
+        <v>1909</v>
+      </c>
+      <c r="E5" s="171" t="s">
         <v>176</v>
       </c>
-      <c r="F5" s="199">
+      <c r="F5" s="169">
         <v>5</v>
       </c>
       <c r="G5" s="114">
@@ -7443,42 +7443,42 @@
       <c r="I5" s="114">
         <v>45985</v>
       </c>
-      <c r="J5" s="202">
+      <c r="J5" s="172">
         <v>45988</v>
       </c>
-      <c r="K5" s="203" t="s">
+      <c r="K5" s="173" t="s">
         <v>194</v>
       </c>
-      <c r="L5" s="204" t="s">
+      <c r="L5" s="174" t="s">
         <v>195</v>
       </c>
-      <c r="M5" s="204">
+      <c r="M5" s="174">
         <v>40</v>
       </c>
-      <c r="N5" s="199" t="s">
+      <c r="N5" s="169" t="s">
         <v>196</v>
       </c>
-      <c r="O5" s="199" t="s">
+      <c r="O5" s="169" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="6" spans="1:15" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="199">
+      <c r="A6" s="169">
         <v>4</v>
       </c>
-      <c r="B6" s="200" t="s">
+      <c r="B6" s="170" t="s">
         <v>201</v>
       </c>
       <c r="C6" s="8" t="s">
         <v>202</v>
       </c>
       <c r="D6" s="8">
-        <v>0.248</v>
-      </c>
-      <c r="E6" s="201" t="s">
+        <v>248</v>
+      </c>
+      <c r="E6" s="171" t="s">
         <v>176</v>
       </c>
-      <c r="F6" s="199">
+      <c r="F6" s="169">
         <v>2</v>
       </c>
       <c r="G6" s="114">
@@ -7490,42 +7490,42 @@
       <c r="I6" s="114">
         <v>45991</v>
       </c>
-      <c r="J6" s="202">
+      <c r="J6" s="172">
         <v>45991</v>
       </c>
-      <c r="K6" s="205" t="s">
+      <c r="K6" s="175" t="s">
         <v>203</v>
       </c>
-      <c r="L6" s="204" t="s">
+      <c r="L6" s="174" t="s">
         <v>195</v>
       </c>
-      <c r="M6" s="204">
+      <c r="M6" s="174">
         <v>40</v>
       </c>
-      <c r="N6" s="199" t="s">
+      <c r="N6" s="169" t="s">
         <v>196</v>
       </c>
-      <c r="O6" s="199" t="s">
+      <c r="O6" s="169" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="7" spans="1:15" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="199">
+      <c r="A7" s="169">
         <v>5</v>
       </c>
-      <c r="B7" s="200" t="s">
+      <c r="B7" s="170" t="s">
         <v>202</v>
       </c>
       <c r="C7" s="8" t="s">
         <v>204</v>
       </c>
       <c r="D7" s="8">
-        <v>0.43</v>
-      </c>
-      <c r="E7" s="201" t="s">
+        <v>430</v>
+      </c>
+      <c r="E7" s="171" t="s">
         <v>176</v>
       </c>
-      <c r="F7" s="199">
+      <c r="F7" s="169">
         <v>1</v>
       </c>
       <c r="G7" s="114">
@@ -7537,42 +7537,42 @@
       <c r="I7" s="114">
         <v>45991</v>
       </c>
-      <c r="J7" s="202">
+      <c r="J7" s="172">
         <v>45991</v>
       </c>
-      <c r="K7" s="205" t="s">
+      <c r="K7" s="175" t="s">
         <v>203</v>
       </c>
-      <c r="L7" s="204" t="s">
+      <c r="L7" s="174" t="s">
         <v>195</v>
       </c>
-      <c r="M7" s="204">
+      <c r="M7" s="174">
         <v>40</v>
       </c>
-      <c r="N7" s="199" t="s">
+      <c r="N7" s="169" t="s">
         <v>196</v>
       </c>
-      <c r="O7" s="199" t="s">
+      <c r="O7" s="169" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="8" spans="1:15" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="199">
+      <c r="A8" s="169">
         <v>6</v>
       </c>
-      <c r="B8" s="200" t="s">
+      <c r="B8" s="170" t="s">
         <v>204</v>
       </c>
       <c r="C8" s="8" t="s">
         <v>205</v>
       </c>
       <c r="D8" s="8">
-        <v>0.248</v>
-      </c>
-      <c r="E8" s="201" t="s">
+        <v>248</v>
+      </c>
+      <c r="E8" s="171" t="s">
         <v>176</v>
       </c>
-      <c r="F8" s="199">
+      <c r="F8" s="169">
         <v>1</v>
       </c>
       <c r="G8" s="114">
@@ -7584,42 +7584,42 @@
       <c r="I8" s="114">
         <v>45991</v>
       </c>
-      <c r="J8" s="202">
+      <c r="J8" s="172">
         <v>45991</v>
       </c>
-      <c r="K8" s="205" t="s">
+      <c r="K8" s="175" t="s">
         <v>203</v>
       </c>
-      <c r="L8" s="204" t="s">
+      <c r="L8" s="174" t="s">
         <v>195</v>
       </c>
-      <c r="M8" s="204">
+      <c r="M8" s="174">
         <v>40</v>
       </c>
-      <c r="N8" s="199" t="s">
+      <c r="N8" s="169" t="s">
         <v>196</v>
       </c>
-      <c r="O8" s="199" t="s">
+      <c r="O8" s="169" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="9" spans="1:15" ht="68.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="199">
+      <c r="A9" s="169">
         <v>7</v>
       </c>
-      <c r="B9" s="200" t="s">
+      <c r="B9" s="170" t="s">
         <v>206</v>
       </c>
       <c r="C9" s="8" t="s">
         <v>207</v>
       </c>
       <c r="D9" s="8">
-        <v>4.91</v>
-      </c>
-      <c r="E9" s="201" t="s">
+        <v>4910</v>
+      </c>
+      <c r="E9" s="171" t="s">
         <v>176</v>
       </c>
-      <c r="F9" s="199">
+      <c r="F9" s="169">
         <v>12</v>
       </c>
       <c r="G9" s="114">
@@ -7631,42 +7631,42 @@
       <c r="I9" s="114">
         <v>45976</v>
       </c>
-      <c r="J9" s="202">
+      <c r="J9" s="172">
         <v>45979</v>
       </c>
-      <c r="K9" s="205" t="s">
+      <c r="K9" s="175" t="s">
         <v>208</v>
       </c>
-      <c r="L9" s="199" t="s">
+      <c r="L9" s="169" t="s">
         <v>209</v>
       </c>
-      <c r="M9" s="199">
+      <c r="M9" s="169">
         <v>45</v>
       </c>
-      <c r="N9" s="199" t="s">
+      <c r="N9" s="169" t="s">
         <v>210</v>
       </c>
-      <c r="O9" s="199" t="s">
+      <c r="O9" s="169" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="10" spans="1:15" ht="76.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="199">
+      <c r="A10" s="169">
         <v>8</v>
       </c>
-      <c r="B10" s="200" t="s">
+      <c r="B10" s="170" t="s">
         <v>207</v>
       </c>
       <c r="C10" s="8" t="s">
         <v>200</v>
       </c>
       <c r="D10" s="8">
-        <v>0.498</v>
-      </c>
-      <c r="E10" s="201" t="s">
+        <v>498</v>
+      </c>
+      <c r="E10" s="171" t="s">
         <v>176</v>
       </c>
-      <c r="F10" s="199">
+      <c r="F10" s="169">
         <v>1</v>
       </c>
       <c r="G10" s="114">
@@ -7678,42 +7678,42 @@
       <c r="I10" s="114">
         <v>45978</v>
       </c>
-      <c r="J10" s="202">
+      <c r="J10" s="172">
         <v>45981</v>
       </c>
-      <c r="K10" s="205" t="s">
+      <c r="K10" s="175" t="s">
         <v>208</v>
       </c>
-      <c r="L10" s="199" t="s">
+      <c r="L10" s="169" t="s">
         <v>209</v>
       </c>
-      <c r="M10" s="199">
+      <c r="M10" s="169">
         <v>45</v>
       </c>
-      <c r="N10" s="199" t="s">
+      <c r="N10" s="169" t="s">
         <v>210</v>
       </c>
-      <c r="O10" s="199" t="s">
+      <c r="O10" s="169" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="11" spans="1:15" ht="63" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="199">
+      <c r="A11" s="169">
         <v>9</v>
       </c>
-      <c r="B11" s="200" t="s">
+      <c r="B11" s="170" t="s">
         <v>212</v>
       </c>
       <c r="C11" s="8" t="s">
         <v>213</v>
       </c>
       <c r="D11" s="8">
-        <v>4.7510000000000003</v>
-      </c>
-      <c r="E11" s="206" t="s">
+        <v>4751</v>
+      </c>
+      <c r="E11" s="176" t="s">
         <v>214</v>
       </c>
-      <c r="F11" s="199">
+      <c r="F11" s="169">
         <v>11</v>
       </c>
       <c r="G11" s="114">
@@ -7725,22 +7725,22 @@
       <c r="I11" s="114">
         <v>45991</v>
       </c>
-      <c r="J11" s="202">
+      <c r="J11" s="172">
         <v>45991</v>
       </c>
-      <c r="K11" s="205" t="s">
+      <c r="K11" s="175" t="s">
         <v>208</v>
       </c>
-      <c r="L11" s="199" t="s">
+      <c r="L11" s="169" t="s">
         <v>209</v>
       </c>
-      <c r="M11" s="199">
+      <c r="M11" s="169">
         <v>45</v>
       </c>
-      <c r="N11" s="199" t="s">
+      <c r="N11" s="169" t="s">
         <v>210</v>
       </c>
-      <c r="O11" s="199" t="s">
+      <c r="O11" s="169" t="s">
         <v>211</v>
       </c>
     </row>
@@ -8018,118 +8018,118 @@
       <c r="F17" s="6"/>
     </row>
     <row r="18" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="179" t="s">
+      <c r="A18" s="180" t="s">
         <v>4</v>
       </c>
-      <c r="B18" s="179" t="s">
+      <c r="B18" s="180" t="s">
         <v>42</v>
       </c>
-      <c r="C18" s="175" t="s">
+      <c r="C18" s="177" t="s">
         <v>47</v>
       </c>
-      <c r="D18" s="175" t="s">
+      <c r="D18" s="177" t="s">
         <v>43</v>
       </c>
-      <c r="E18" s="179" t="s">
+      <c r="E18" s="180" t="s">
         <v>8</v>
       </c>
-      <c r="F18" s="166" t="s">
+      <c r="F18" s="192" t="s">
         <v>18</v>
       </c>
-      <c r="G18" s="166"/>
-      <c r="H18" s="166"/>
-      <c r="I18" s="166"/>
-      <c r="J18" s="166"/>
-      <c r="K18" s="169" t="s">
+      <c r="G18" s="192"/>
+      <c r="H18" s="192"/>
+      <c r="I18" s="192"/>
+      <c r="J18" s="192"/>
+      <c r="K18" s="185" t="s">
         <v>19</v>
       </c>
-      <c r="M18" s="175" t="s">
+      <c r="M18" s="177" t="s">
         <v>36</v>
       </c>
-      <c r="O18" s="170" t="s">
+      <c r="O18" s="186" t="s">
         <v>31</v>
       </c>
-      <c r="P18" s="171"/>
-      <c r="Q18" s="171"/>
-      <c r="R18" s="171"/>
-      <c r="S18" s="171"/>
-      <c r="T18" s="172"/>
-      <c r="V18" s="170" t="s">
+      <c r="P18" s="187"/>
+      <c r="Q18" s="187"/>
+      <c r="R18" s="187"/>
+      <c r="S18" s="187"/>
+      <c r="T18" s="188"/>
+      <c r="V18" s="186" t="s">
         <v>30</v>
       </c>
-      <c r="W18" s="171"/>
-      <c r="X18" s="171"/>
-      <c r="Y18" s="171"/>
-      <c r="Z18" s="171"/>
-      <c r="AA18" s="172"/>
-      <c r="AB18" s="173" t="s">
+      <c r="W18" s="187"/>
+      <c r="X18" s="187"/>
+      <c r="Y18" s="187"/>
+      <c r="Z18" s="187"/>
+      <c r="AA18" s="188"/>
+      <c r="AB18" s="189" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="19" spans="1:28" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="180"/>
-      <c r="B19" s="180"/>
-      <c r="C19" s="177"/>
-      <c r="D19" s="180"/>
-      <c r="E19" s="180"/>
-      <c r="F19" s="187" t="s">
+      <c r="A19" s="181"/>
+      <c r="B19" s="181"/>
+      <c r="C19" s="178"/>
+      <c r="D19" s="181"/>
+      <c r="E19" s="181"/>
+      <c r="F19" s="204" t="s">
         <v>40</v>
       </c>
-      <c r="G19" s="188" t="s">
+      <c r="G19" s="205" t="s">
         <v>44</v>
       </c>
-      <c r="H19" s="189"/>
-      <c r="I19" s="188" t="s">
+      <c r="H19" s="206"/>
+      <c r="I19" s="205" t="s">
         <v>45</v>
       </c>
-      <c r="J19" s="189"/>
-      <c r="K19" s="169"/>
-      <c r="M19" s="176"/>
-      <c r="O19" s="167" t="s">
+      <c r="J19" s="206"/>
+      <c r="K19" s="185"/>
+      <c r="M19" s="191"/>
+      <c r="O19" s="183" t="s">
         <v>24</v>
       </c>
-      <c r="P19" s="167" t="s">
+      <c r="P19" s="183" t="s">
         <v>25</v>
       </c>
-      <c r="Q19" s="167" t="s">
+      <c r="Q19" s="183" t="s">
         <v>26</v>
       </c>
-      <c r="R19" s="167" t="s">
+      <c r="R19" s="183" t="s">
         <v>27</v>
       </c>
-      <c r="S19" s="167" t="s">
+      <c r="S19" s="183" t="s">
         <v>28</v>
       </c>
       <c r="T19" s="43" t="s">
         <v>29</v>
       </c>
-      <c r="V19" s="167" t="s">
+      <c r="V19" s="183" t="s">
         <v>24</v>
       </c>
-      <c r="W19" s="167" t="s">
+      <c r="W19" s="183" t="s">
         <v>25</v>
       </c>
-      <c r="X19" s="167" t="s">
+      <c r="X19" s="183" t="s">
         <v>26</v>
       </c>
-      <c r="Y19" s="167" t="s">
+      <c r="Y19" s="183" t="s">
         <v>27</v>
       </c>
-      <c r="Z19" s="167" t="s">
+      <c r="Z19" s="183" t="s">
         <v>28</v>
       </c>
       <c r="AA19" s="43" t="s">
         <v>29</v>
       </c>
-      <c r="AB19" s="174"/>
+      <c r="AB19" s="190"/>
     </row>
     <row r="20" spans="1:28" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="180"/>
-      <c r="B20" s="180"/>
-      <c r="C20" s="177"/>
-      <c r="D20" s="180"/>
-      <c r="E20" s="180"/>
-      <c r="F20" s="187"/>
+      <c r="A20" s="181"/>
+      <c r="B20" s="181"/>
+      <c r="C20" s="178"/>
+      <c r="D20" s="181"/>
+      <c r="E20" s="181"/>
+      <c r="F20" s="204"/>
       <c r="G20" s="94" t="s">
         <v>10</v>
       </c>
@@ -8148,17 +8148,17 @@
       <c r="M20" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="O20" s="168"/>
-      <c r="P20" s="168"/>
-      <c r="Q20" s="168"/>
-      <c r="R20" s="168"/>
-      <c r="S20" s="168"/>
+      <c r="O20" s="184"/>
+      <c r="P20" s="184"/>
+      <c r="Q20" s="184"/>
+      <c r="R20" s="184"/>
+      <c r="S20" s="184"/>
       <c r="T20" s="19"/>
-      <c r="V20" s="168"/>
-      <c r="W20" s="168"/>
-      <c r="X20" s="168"/>
-      <c r="Y20" s="168"/>
-      <c r="Z20" s="168"/>
+      <c r="V20" s="184"/>
+      <c r="W20" s="184"/>
+      <c r="X20" s="184"/>
+      <c r="Y20" s="184"/>
+      <c r="Z20" s="184"/>
       <c r="AA20" s="19" t="s">
         <v>20</v>
       </c>
@@ -8179,7 +8179,7 @@
       <c r="D21" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="E21" s="190" t="s">
+      <c r="E21" s="203" t="s">
         <v>98</v>
       </c>
       <c r="F21" s="114">
@@ -8253,7 +8253,7 @@
       <c r="D22" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="E22" s="190"/>
+      <c r="E22" s="203"/>
       <c r="F22" s="114">
         <v>45913</v>
       </c>
@@ -8325,7 +8325,7 @@
       <c r="D23" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="E23" s="190"/>
+      <c r="E23" s="203"/>
       <c r="F23" s="114">
         <v>45910</v>
       </c>
@@ -8397,7 +8397,7 @@
       <c r="D24" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="E24" s="190"/>
+      <c r="E24" s="203"/>
       <c r="F24" s="114">
         <v>45927</v>
       </c>
@@ -8469,7 +8469,7 @@
       <c r="D25" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="E25" s="190"/>
+      <c r="E25" s="203"/>
       <c r="F25" s="114">
         <v>45915</v>
       </c>
@@ -9164,18 +9164,6 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="E21:E25"/>
-    <mergeCell ref="W19:W20"/>
-    <mergeCell ref="K18:K19"/>
-    <mergeCell ref="M18:M19"/>
-    <mergeCell ref="O18:T18"/>
-    <mergeCell ref="V18:AA18"/>
-    <mergeCell ref="V19:V20"/>
-    <mergeCell ref="A18:A20"/>
-    <mergeCell ref="B18:B20"/>
-    <mergeCell ref="C18:C20"/>
-    <mergeCell ref="D18:D20"/>
-    <mergeCell ref="E18:E20"/>
     <mergeCell ref="AB18:AB19"/>
     <mergeCell ref="F19:F20"/>
     <mergeCell ref="G19:H19"/>
@@ -9189,6 +9177,18 @@
     <mergeCell ref="Q19:Q20"/>
     <mergeCell ref="R19:R20"/>
     <mergeCell ref="S19:S20"/>
+    <mergeCell ref="A18:A20"/>
+    <mergeCell ref="B18:B20"/>
+    <mergeCell ref="C18:C20"/>
+    <mergeCell ref="D18:D20"/>
+    <mergeCell ref="E18:E20"/>
+    <mergeCell ref="E21:E25"/>
+    <mergeCell ref="W19:W20"/>
+    <mergeCell ref="K18:K19"/>
+    <mergeCell ref="M18:M19"/>
+    <mergeCell ref="O18:T18"/>
+    <mergeCell ref="V18:AA18"/>
+    <mergeCell ref="V19:V20"/>
   </mergeCells>
   <conditionalFormatting sqref="C26:C27">
     <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="4DT6">

--- a/Raw Data/Micro Plans/November 2025/Micro Plan - TA-421 Nov'25.xlsx
+++ b/Raw Data/Micro Plans/November 2025/Micro Plan - TA-421 Nov'25.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kaushikb\Documents\Work\Git\Office-work-\Raw Data\Micro Plans\November 2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C965881B-D56B-4EDF-9D96-6A23D224259C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCEE4415-2D78-481B-8A00-29F4AB8B23A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="757" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="757" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FDN-June25" sheetId="1" state="hidden" r:id="rId1"/>
@@ -1823,9 +1823,54 @@
     <xf numFmtId="0" fontId="25" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1841,51 +1886,6 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1901,9 +1901,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1911,6 +1908,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1972,6 +1972,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -1992,6 +2002,66 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C5700"/>
       </font>
       <fill>
@@ -2002,6 +2072,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -2032,6 +2112,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -2052,6 +2142,26 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -2072,6 +2182,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -2082,6 +2202,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -2092,6 +2222,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -2112,6 +2252,46 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C5700"/>
       </font>
       <fill>
@@ -2122,6 +2302,26 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -2152,6 +2352,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -2172,6 +2382,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -2192,6 +2412,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C5700"/>
       </font>
       <fill>
@@ -2202,6 +2432,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -2222,6 +2462,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C5700"/>
       </font>
       <fill>
@@ -2232,6 +2482,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -2242,6 +2502,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -2277,276 +2547,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2892,6 +2892,16 @@
     </dxf>
     <dxf>
       <font>
+        <color indexed="17"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color indexed="20"/>
       </font>
       <fill>
@@ -2914,16 +2924,6 @@
       <font>
         <color indexed="20"/>
       </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color indexed="17"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor indexed="42"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <font>
@@ -3745,41 +3745,41 @@
       <c r="F17" s="6"/>
     </row>
     <row r="18" spans="1:33" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="180" t="s">
+      <c r="A18" s="195" t="s">
         <v>4</v>
       </c>
-      <c r="B18" s="180" t="s">
+      <c r="B18" s="195" t="s">
         <v>5</v>
       </c>
-      <c r="C18" s="177" t="s">
+      <c r="C18" s="191" t="s">
         <v>6</v>
       </c>
-      <c r="D18" s="180" t="s">
+      <c r="D18" s="195" t="s">
         <v>7</v>
       </c>
-      <c r="E18" s="177" t="s">
+      <c r="E18" s="191" t="s">
         <v>16</v>
       </c>
-      <c r="F18" s="177" t="s">
+      <c r="F18" s="191" t="s">
         <v>17</v>
       </c>
-      <c r="G18" s="180" t="s">
+      <c r="G18" s="195" t="s">
         <v>8</v>
       </c>
-      <c r="H18" s="192" t="s">
+      <c r="H18" s="182" t="s">
         <v>18</v>
       </c>
-      <c r="I18" s="192"/>
-      <c r="J18" s="192"/>
-      <c r="K18" s="192"/>
-      <c r="L18" s="192"/>
-      <c r="M18" s="192"/>
-      <c r="N18" s="192"/>
-      <c r="O18" s="192"/>
+      <c r="I18" s="182"/>
+      <c r="J18" s="182"/>
+      <c r="K18" s="182"/>
+      <c r="L18" s="182"/>
+      <c r="M18" s="182"/>
+      <c r="N18" s="182"/>
+      <c r="O18" s="182"/>
       <c r="P18" s="185" t="s">
         <v>19</v>
       </c>
-      <c r="R18" s="177" t="s">
+      <c r="R18" s="191" t="s">
         <v>36</v>
       </c>
       <c r="T18" s="186" t="s">
@@ -3803,33 +3803,33 @@
       </c>
     </row>
     <row r="19" spans="1:33" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="181"/>
-      <c r="B19" s="181"/>
-      <c r="C19" s="178"/>
-      <c r="D19" s="181"/>
-      <c r="E19" s="178"/>
-      <c r="F19" s="178"/>
-      <c r="G19" s="181"/>
-      <c r="H19" s="197" t="s">
+      <c r="A19" s="196"/>
+      <c r="B19" s="196"/>
+      <c r="C19" s="193"/>
+      <c r="D19" s="196"/>
+      <c r="E19" s="193"/>
+      <c r="F19" s="193"/>
+      <c r="G19" s="196"/>
+      <c r="H19" s="181" t="s">
         <v>9</v>
       </c>
-      <c r="I19" s="197"/>
-      <c r="J19" s="197" t="s">
+      <c r="I19" s="181"/>
+      <c r="J19" s="181" t="s">
         <v>12</v>
       </c>
-      <c r="K19" s="197"/>
-      <c r="L19" s="197" t="s">
+      <c r="K19" s="181"/>
+      <c r="L19" s="181" t="s">
         <v>13</v>
       </c>
-      <c r="M19" s="197"/>
-      <c r="N19" s="193" t="s">
+      <c r="M19" s="181"/>
+      <c r="N19" s="179" t="s">
         <v>15</v>
       </c>
-      <c r="O19" s="193" t="s">
+      <c r="O19" s="179" t="s">
         <v>14</v>
       </c>
       <c r="P19" s="185"/>
-      <c r="R19" s="191"/>
+      <c r="R19" s="192"/>
       <c r="T19" s="183" t="s">
         <v>24</v>
       </c>
@@ -3869,13 +3869,13 @@
       <c r="AG19" s="190"/>
     </row>
     <row r="20" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="182"/>
-      <c r="B20" s="181"/>
-      <c r="C20" s="178"/>
-      <c r="D20" s="181"/>
-      <c r="E20" s="179"/>
-      <c r="F20" s="179"/>
-      <c r="G20" s="181"/>
+      <c r="A20" s="197"/>
+      <c r="B20" s="196"/>
+      <c r="C20" s="193"/>
+      <c r="D20" s="196"/>
+      <c r="E20" s="194"/>
+      <c r="F20" s="194"/>
+      <c r="G20" s="196"/>
       <c r="H20" s="94" t="s">
         <v>10</v>
       </c>
@@ -3894,8 +3894,8 @@
       <c r="M20" s="94" t="s">
         <v>11</v>
       </c>
-      <c r="N20" s="194"/>
-      <c r="O20" s="194"/>
+      <c r="N20" s="180"/>
+      <c r="O20" s="180"/>
       <c r="P20" s="44" t="s">
         <v>50</v>
       </c>
@@ -4183,7 +4183,7 @@
       <c r="D25" s="86"/>
       <c r="E25" s="101"/>
       <c r="F25" s="8"/>
-      <c r="G25" s="195"/>
+      <c r="G25" s="177"/>
       <c r="H25" s="99"/>
       <c r="I25" s="99"/>
       <c r="J25" s="99"/>
@@ -4241,7 +4241,7 @@
       <c r="D26" s="8"/>
       <c r="E26" s="102"/>
       <c r="F26" s="97"/>
-      <c r="G26" s="196"/>
+      <c r="G26" s="178"/>
       <c r="H26" s="99"/>
       <c r="I26" s="99"/>
       <c r="J26" s="99"/>
@@ -4596,16 +4596,13 @@
     <filterColumn colId="13" showButton="0"/>
   </autoFilter>
   <mergeCells count="29">
-    <mergeCell ref="G25:G26"/>
-    <mergeCell ref="O19:O20"/>
-    <mergeCell ref="H19:I19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="L19:M19"/>
-    <mergeCell ref="H18:O18"/>
-    <mergeCell ref="N19:N20"/>
-    <mergeCell ref="U19:U20"/>
-    <mergeCell ref="V19:V20"/>
-    <mergeCell ref="W19:W20"/>
+    <mergeCell ref="F18:F20"/>
+    <mergeCell ref="G18:G20"/>
+    <mergeCell ref="A18:A20"/>
+    <mergeCell ref="B18:B20"/>
+    <mergeCell ref="C18:C20"/>
+    <mergeCell ref="D18:D20"/>
+    <mergeCell ref="E18:E20"/>
     <mergeCell ref="X19:X20"/>
     <mergeCell ref="P18:P19"/>
     <mergeCell ref="AA18:AF18"/>
@@ -4618,13 +4615,16 @@
     <mergeCell ref="R18:R19"/>
     <mergeCell ref="T18:Y18"/>
     <mergeCell ref="T19:T20"/>
-    <mergeCell ref="F18:F20"/>
-    <mergeCell ref="G18:G20"/>
-    <mergeCell ref="A18:A20"/>
-    <mergeCell ref="B18:B20"/>
-    <mergeCell ref="C18:C20"/>
-    <mergeCell ref="D18:D20"/>
-    <mergeCell ref="E18:E20"/>
+    <mergeCell ref="H18:O18"/>
+    <mergeCell ref="N19:N20"/>
+    <mergeCell ref="U19:U20"/>
+    <mergeCell ref="V19:V20"/>
+    <mergeCell ref="W19:W20"/>
+    <mergeCell ref="G25:G26"/>
+    <mergeCell ref="O19:O20"/>
+    <mergeCell ref="H19:I19"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="L19:M19"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="B21">
@@ -4699,17 +4699,17 @@
     <cfRule type="expression" dxfId="99" priority="1243" stopIfTrue="1">
       <formula>AND(COUNTIF($D$1:$D$123, B26)+COUNTIF($D$142:$D$65380, B26)&gt;1,NOT(ISBLANK(B26)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="98" priority="1244" stopIfTrue="1">
+    <cfRule type="expression" dxfId="98" priority="1245" stopIfTrue="1">
       <formula>AND(COUNTIF($D$1:$D$191, B26)+COUNTIF($D$214:$D$65380, B26)&gt;1,NOT(ISBLANK(B26)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="97" priority="1245" stopIfTrue="1">
+    <cfRule type="expression" dxfId="97" priority="1246" stopIfTrue="1">
       <formula>AND(COUNTIF($D$1:$D$191, B26)+COUNTIF($D$214:$D$65380, B26)&gt;1,NOT(ISBLANK(B26)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="96" priority="1246" stopIfTrue="1">
+    <cfRule type="expression" dxfId="96" priority="1247" stopIfTrue="1">
+      <formula>AND(COUNTIF($D$474:$D$65380, B26)+COUNTIF($D$454:$D$455, B26)+COUNTIF($D$416:$D$417, B26)+COUNTIF($D$374:$D$377, B26)+COUNTIF($D$351:$D$352, B26)+COUNTIF($D$324:$D$325, B26)+COUNTIF($D$303:$D$303, B26)+COUNTIF($D$288:$D$289, B26)+COUNTIF($D$263:$D$263, B26)+COUNTIF($D$252:$D$253, B26)+COUNTIF($D$233:$D$234, B26)+COUNTIF($D$51:$D$218, B26)+COUNTIF($D$219:$D$220, B26)+COUNTIF($D$1:$D$50, B26)&gt;1,NOT(ISBLANK(B26)))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="95" priority="1244" stopIfTrue="1">
       <formula>AND(COUNTIF($D$1:$D$191, B26)+COUNTIF($D$214:$D$65380, B26)&gt;1,NOT(ISBLANK(B26)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="95" priority="1247" stopIfTrue="1">
-      <formula>AND(COUNTIF($D$474:$D$65380, B26)+COUNTIF($D$454:$D$455, B26)+COUNTIF($D$416:$D$417, B26)+COUNTIF($D$374:$D$377, B26)+COUNTIF($D$351:$D$352, B26)+COUNTIF($D$324:$D$325, B26)+COUNTIF($D$303:$D$303, B26)+COUNTIF($D$288:$D$289, B26)+COUNTIF($D$263:$D$263, B26)+COUNTIF($D$252:$D$253, B26)+COUNTIF($D$233:$D$234, B26)+COUNTIF($D$51:$D$218, B26)+COUNTIF($D$219:$D$220, B26)+COUNTIF($D$1:$D$50, B26)&gt;1,NOT(ISBLANK(B26)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B27">
@@ -4726,55 +4726,55 @@
     <cfRule type="duplicateValues" dxfId="88" priority="347"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="L4">
-    <cfRule type="expression" dxfId="87" priority="1220" stopIfTrue="1">
+    <cfRule type="expression" dxfId="87" priority="1221" stopIfTrue="1">
+      <formula>AND(COUNTIF($C$1:$C$65460, L4)+COUNTIF(#REF!, L4)&gt;1,NOT(ISBLANK(L4)))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="86" priority="1220" stopIfTrue="1">
       <formula>AND(COUNTIF($C$314:$C$65460, L4)+COUNTIF($C$294:$C$295, L4)+COUNTIF($C$256:$C$257, L4)+COUNTIF($C$214:$C$217, L4)+COUNTIF($C$191:$C$192, L4)+COUNTIF($C$164:$C$165, L4)+COUNTIF($C$143:$C$143, L4)+COUNTIF($C$128:$C$129, L4)+COUNTIF($C$103:$C$103, L4)+COUNTIF($C$92:$C$93, L4)+COUNTIF($C$73:$C$74, L4)+COUNTIF($C$29:$C$56, L4)+COUNTIF($C$58:$C$60, L4)+COUNTIF($C$1:$C$27, L4)&gt;1,NOT(ISBLANK(L4)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="86" priority="1221" stopIfTrue="1">
-      <formula>AND(COUNTIF($C$1:$C$65460, L4)+COUNTIF(#REF!, L4)&gt;1,NOT(ISBLANK(L4)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M4">
-    <cfRule type="expression" dxfId="85" priority="1222" stopIfTrue="1">
+    <cfRule type="expression" dxfId="85" priority="1223" stopIfTrue="1">
+      <formula>AND(COUNTIF($D$314:$D$65460, M4)+COUNTIF(#REF!, M4)+COUNTIF($D$1:$D$27, M4)+COUNTIF($D$294:$D$295, M4)+COUNTIF($D$256:$D$257, M4)+COUNTIF($D$214:$D$217, M4)+COUNTIF($D$191:$D$192, M4)+COUNTIF($D$164:$D$165, M4)+COUNTIF($D$143:$D$143, M4)+COUNTIF($D$128:$D$129, M4)+COUNTIF($D$103:$D$103, M4)+COUNTIF($D$92:$D$93, M4)+COUNTIF($D$73:$D$74, M4)+COUNTIF($D$58:$D$60, M4)&gt;1,NOT(ISBLANK(M4)))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="84" priority="1224" stopIfTrue="1">
+      <formula>AND(COUNTIF($D$294:$D$65460, M4)+COUNTIF($D$1:$D$27, M4)+COUNTIF($D$256:$D$257, M4)+COUNTIF(#REF!, M4)+COUNTIF($D$214:$D$217, M4)+COUNTIF($D$191:$D$192, M4)+COUNTIF($D$164:$D$165, M4)+COUNTIF($D$143:$D$143, M4)+COUNTIF($D$128:$D$129, M4)+COUNTIF($D$103:$D$103, M4)+COUNTIF($D$92:$D$93, M4)+COUNTIF($D$73:$D$74, M4)+COUNTIF($D$58:$D$60, M4)&gt;1,NOT(ISBLANK(M4)))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="83" priority="1225" stopIfTrue="1">
+      <formula>AND(COUNTIF($D$256:$D$65460, M4)+COUNTIF($D$1:$D$27, M4)+COUNTIF(#REF!, M4)+COUNTIF($D$214:$D$217, M4)+COUNTIF($D$191:$D$192, M4)+COUNTIF($D$164:$D$165, M4)+COUNTIF($D$143:$D$143, M4)+COUNTIF($D$128:$D$129, M4)+COUNTIF($D$103:$D$103, M4)+COUNTIF($D$92:$D$93, M4)+COUNTIF($D$73:$D$74, M4)+COUNTIF($D$58:$D$60, M4)&gt;1,NOT(ISBLANK(M4)))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="82" priority="1226" stopIfTrue="1">
+      <formula>AND(COUNTIF($D$214:$D$65460, M4)+COUNTIF(#REF!, M4)+COUNTIF($D$1:$D$27, M4)+COUNTIF($D$191:$D$192, M4)+COUNTIF($D$164:$D$165, M4)+COUNTIF($D$143:$D$143, M4)+COUNTIF($D$128:$D$129, M4)+COUNTIF($D$103:$D$103, M4)+COUNTIF($D$92:$D$93, M4)+COUNTIF($D$73:$D$74, M4)+COUNTIF($D$58:$D$60, M4)&gt;1,NOT(ISBLANK(M4)))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="81" priority="1227" stopIfTrue="1">
+      <formula>AND(COUNTIF($D$214:$D$65460, M4)+COUNTIF($D$191:$D$192, M4)+COUNTIF($D$164:$D$165, M4)+COUNTIF($D$143:$D$143, M4)+COUNTIF($D$128:$D$129, M4)+COUNTIF($D$1:$D$27, M4)+COUNTIF(#REF!, M4)+COUNTIF($D$103:$D$103, M4)+COUNTIF($D$92:$D$93, M4)+COUNTIF(#REF!, M4)+COUNTIF($D$73:$D$74, M4)+COUNTIF($D$51:$D$51, M4)+COUNTIF($D$53:$D$60, M4)+COUNTIF(#REF!, M4)&gt;1,NOT(ISBLANK(M4)))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="80" priority="1228" stopIfTrue="1">
+      <formula>AND(COUNTIF($D$191:$D$65460, M4)+COUNTIF($D$164:$D$165, M4)+COUNTIF($D$143:$D$143, M4)+COUNTIF($D$128:$D$129, M4)+COUNTIF($D$1:$D$27, M4)+COUNTIF(#REF!, M4)+COUNTIF($D$103:$D$103, M4)+COUNTIF($D$92:$D$93, M4)+COUNTIF(#REF!, M4)+COUNTIF($D$73:$D$74, M4)+COUNTIF($D$51:$D$51, M4)+COUNTIF($D$53:$D$60, M4)+COUNTIF(#REF!, M4)&gt;1,NOT(ISBLANK(M4)))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="79" priority="1229" stopIfTrue="1">
+      <formula>AND(COUNTIF($F$369:$F$65454, M4)+COUNTIF($F$1:$F$27, M4)+COUNTIF(#REF!, M4)+COUNTIF($F$352:$F$353, M4)+COUNTIF($F$332:$F$333, M4)+COUNTIF($F$294:$F$295, M4)+COUNTIF($F$252:$F$255, M4)+COUNTIF($F$229:$F$230, M4)+COUNTIF($F$202:$F$203, M4)+COUNTIF($F$181:$F$181, M4)+COUNTIF($F$166:$F$167, M4)+COUNTIF($F$141:$F$141, M4)+COUNTIF($F$130:$F$131, M4)+COUNTIF($F$111:$F$112, M4)+COUNTIF($F$96:$F$98, M4)&gt;1,NOT(ISBLANK(M4)))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="78" priority="1230" stopIfTrue="1">
+      <formula>AND(COUNTIF($F$352:$F$65454, M4)+COUNTIF(#REF!, M4)+COUNTIF($F$1:$F$27, M4)+COUNTIF($F$332:$F$333, M4)+COUNTIF($F$294:$F$295, M4)+COUNTIF($F$252:$F$255, M4)+COUNTIF($F$229:$F$230, M4)+COUNTIF($F$202:$F$203, M4)+COUNTIF($F$181:$F$181, M4)+COUNTIF($F$166:$F$167, M4)+COUNTIF($F$141:$F$141, M4)+COUNTIF($F$130:$F$131, M4)+COUNTIF($F$111:$F$112, M4)+COUNTIF($F$96:$F$98, M4)&gt;1,NOT(ISBLANK(M4)))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="77" priority="1231" stopIfTrue="1">
+      <formula>AND(COUNTIF($F$332:$F$65454, M4)+COUNTIF($F$1:$F$27, M4)+COUNTIF($F$294:$F$295, M4)+COUNTIF(#REF!, M4)+COUNTIF($F$252:$F$255, M4)+COUNTIF($F$229:$F$230, M4)+COUNTIF($F$202:$F$203, M4)+COUNTIF($F$181:$F$181, M4)+COUNTIF($F$166:$F$167, M4)+COUNTIF($F$141:$F$141, M4)+COUNTIF($F$130:$F$131, M4)+COUNTIF($F$111:$F$112, M4)+COUNTIF($F$96:$F$98, M4)&gt;1,NOT(ISBLANK(M4)))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="76" priority="1232" stopIfTrue="1">
+      <formula>AND(COUNTIF($F$294:$F$65454, M4)+COUNTIF($F$1:$F$27, M4)+COUNTIF(#REF!, M4)+COUNTIF($F$252:$F$255, M4)+COUNTIF($F$229:$F$230, M4)+COUNTIF($F$202:$F$203, M4)+COUNTIF($F$181:$F$181, M4)+COUNTIF($F$166:$F$167, M4)+COUNTIF($F$141:$F$141, M4)+COUNTIF($F$130:$F$131, M4)+COUNTIF($F$111:$F$112, M4)+COUNTIF($F$96:$F$98, M4)&gt;1,NOT(ISBLANK(M4)))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="75" priority="1233" stopIfTrue="1">
+      <formula>AND(COUNTIF($F$252:$F$65454, M4)+COUNTIF(#REF!, M4)+COUNTIF($F$1:$F$27, M4)+COUNTIF($F$229:$F$230, M4)+COUNTIF($F$202:$F$203, M4)+COUNTIF($F$181:$F$181, M4)+COUNTIF($F$166:$F$167, M4)+COUNTIF($F$141:$F$141, M4)+COUNTIF($F$130:$F$131, M4)+COUNTIF($F$111:$F$112, M4)+COUNTIF($F$96:$F$98, M4)&gt;1,NOT(ISBLANK(M4)))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="74" priority="1234" stopIfTrue="1">
+      <formula>AND(COUNTIF($F$252:$F$65454, M4)+COUNTIF($F$229:$F$230, M4)+COUNTIF($F$202:$F$203, M4)+COUNTIF($F$181:$F$181, M4)+COUNTIF($F$166:$F$167, M4)+COUNTIF($F$1:$F$27, M4)+COUNTIF(#REF!, M4)+COUNTIF($F$141:$F$141, M4)+COUNTIF($F$130:$F$131, M4)+COUNTIF(#REF!, M4)+COUNTIF($F$111:$F$112, M4)+COUNTIF($F$89:$F$89, M4)+COUNTIF($F$91:$F$98, M4)+COUNTIF(#REF!, M4)&gt;1,NOT(ISBLANK(M4)))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="73" priority="1235" stopIfTrue="1">
+      <formula>AND(COUNTIF($F$229:$F$65454, M4)+COUNTIF($F$202:$F$203, M4)+COUNTIF($F$181:$F$181, M4)+COUNTIF($F$166:$F$167, M4)+COUNTIF($F$1:$F$27, M4)+COUNTIF(#REF!, M4)+COUNTIF($F$141:$F$141, M4)+COUNTIF($F$130:$F$131, M4)+COUNTIF(#REF!, M4)+COUNTIF($F$111:$F$112, M4)+COUNTIF($F$89:$F$89, M4)+COUNTIF($F$91:$F$98, M4)+COUNTIF(#REF!, M4)&gt;1,NOT(ISBLANK(M4)))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="72" priority="1222" stopIfTrue="1">
       <formula>AND(COUNTIF($D$331:$D$65460, M4)+COUNTIF($D$1:$D$27, M4)+COUNTIF(#REF!, M4)+COUNTIF($D$314:$D$315, M4)+COUNTIF($D$294:$D$295, M4)+COUNTIF($D$256:$D$257, M4)+COUNTIF($D$214:$D$217, M4)+COUNTIF($D$191:$D$192, M4)+COUNTIF($D$164:$D$165, M4)+COUNTIF($D$143:$D$143, M4)+COUNTIF($D$128:$D$129, M4)+COUNTIF($D$103:$D$103, M4)+COUNTIF($D$92:$D$93, M4)+COUNTIF($D$73:$D$74, M4)+COUNTIF($D$58:$D$60, M4)&gt;1,NOT(ISBLANK(M4)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="84" priority="1223" stopIfTrue="1">
-      <formula>AND(COUNTIF($D$314:$D$65460, M4)+COUNTIF(#REF!, M4)+COUNTIF($D$1:$D$27, M4)+COUNTIF($D$294:$D$295, M4)+COUNTIF($D$256:$D$257, M4)+COUNTIF($D$214:$D$217, M4)+COUNTIF($D$191:$D$192, M4)+COUNTIF($D$164:$D$165, M4)+COUNTIF($D$143:$D$143, M4)+COUNTIF($D$128:$D$129, M4)+COUNTIF($D$103:$D$103, M4)+COUNTIF($D$92:$D$93, M4)+COUNTIF($D$73:$D$74, M4)+COUNTIF($D$58:$D$60, M4)&gt;1,NOT(ISBLANK(M4)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="83" priority="1224" stopIfTrue="1">
-      <formula>AND(COUNTIF($D$294:$D$65460, M4)+COUNTIF($D$1:$D$27, M4)+COUNTIF($D$256:$D$257, M4)+COUNTIF(#REF!, M4)+COUNTIF($D$214:$D$217, M4)+COUNTIF($D$191:$D$192, M4)+COUNTIF($D$164:$D$165, M4)+COUNTIF($D$143:$D$143, M4)+COUNTIF($D$128:$D$129, M4)+COUNTIF($D$103:$D$103, M4)+COUNTIF($D$92:$D$93, M4)+COUNTIF($D$73:$D$74, M4)+COUNTIF($D$58:$D$60, M4)&gt;1,NOT(ISBLANK(M4)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="82" priority="1225" stopIfTrue="1">
-      <formula>AND(COUNTIF($D$256:$D$65460, M4)+COUNTIF($D$1:$D$27, M4)+COUNTIF(#REF!, M4)+COUNTIF($D$214:$D$217, M4)+COUNTIF($D$191:$D$192, M4)+COUNTIF($D$164:$D$165, M4)+COUNTIF($D$143:$D$143, M4)+COUNTIF($D$128:$D$129, M4)+COUNTIF($D$103:$D$103, M4)+COUNTIF($D$92:$D$93, M4)+COUNTIF($D$73:$D$74, M4)+COUNTIF($D$58:$D$60, M4)&gt;1,NOT(ISBLANK(M4)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="81" priority="1226" stopIfTrue="1">
-      <formula>AND(COUNTIF($D$214:$D$65460, M4)+COUNTIF(#REF!, M4)+COUNTIF($D$1:$D$27, M4)+COUNTIF($D$191:$D$192, M4)+COUNTIF($D$164:$D$165, M4)+COUNTIF($D$143:$D$143, M4)+COUNTIF($D$128:$D$129, M4)+COUNTIF($D$103:$D$103, M4)+COUNTIF($D$92:$D$93, M4)+COUNTIF($D$73:$D$74, M4)+COUNTIF($D$58:$D$60, M4)&gt;1,NOT(ISBLANK(M4)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="80" priority="1227" stopIfTrue="1">
-      <formula>AND(COUNTIF($D$214:$D$65460, M4)+COUNTIF($D$191:$D$192, M4)+COUNTIF($D$164:$D$165, M4)+COUNTIF($D$143:$D$143, M4)+COUNTIF($D$128:$D$129, M4)+COUNTIF($D$1:$D$27, M4)+COUNTIF(#REF!, M4)+COUNTIF($D$103:$D$103, M4)+COUNTIF($D$92:$D$93, M4)+COUNTIF(#REF!, M4)+COUNTIF($D$73:$D$74, M4)+COUNTIF($D$51:$D$51, M4)+COUNTIF($D$53:$D$60, M4)+COUNTIF(#REF!, M4)&gt;1,NOT(ISBLANK(M4)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="79" priority="1228" stopIfTrue="1">
-      <formula>AND(COUNTIF($D$191:$D$65460, M4)+COUNTIF($D$164:$D$165, M4)+COUNTIF($D$143:$D$143, M4)+COUNTIF($D$128:$D$129, M4)+COUNTIF($D$1:$D$27, M4)+COUNTIF(#REF!, M4)+COUNTIF($D$103:$D$103, M4)+COUNTIF($D$92:$D$93, M4)+COUNTIF(#REF!, M4)+COUNTIF($D$73:$D$74, M4)+COUNTIF($D$51:$D$51, M4)+COUNTIF($D$53:$D$60, M4)+COUNTIF(#REF!, M4)&gt;1,NOT(ISBLANK(M4)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="78" priority="1229" stopIfTrue="1">
-      <formula>AND(COUNTIF($F$369:$F$65454, M4)+COUNTIF($F$1:$F$27, M4)+COUNTIF(#REF!, M4)+COUNTIF($F$352:$F$353, M4)+COUNTIF($F$332:$F$333, M4)+COUNTIF($F$294:$F$295, M4)+COUNTIF($F$252:$F$255, M4)+COUNTIF($F$229:$F$230, M4)+COUNTIF($F$202:$F$203, M4)+COUNTIF($F$181:$F$181, M4)+COUNTIF($F$166:$F$167, M4)+COUNTIF($F$141:$F$141, M4)+COUNTIF($F$130:$F$131, M4)+COUNTIF($F$111:$F$112, M4)+COUNTIF($F$96:$F$98, M4)&gt;1,NOT(ISBLANK(M4)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="77" priority="1230" stopIfTrue="1">
-      <formula>AND(COUNTIF($F$352:$F$65454, M4)+COUNTIF(#REF!, M4)+COUNTIF($F$1:$F$27, M4)+COUNTIF($F$332:$F$333, M4)+COUNTIF($F$294:$F$295, M4)+COUNTIF($F$252:$F$255, M4)+COUNTIF($F$229:$F$230, M4)+COUNTIF($F$202:$F$203, M4)+COUNTIF($F$181:$F$181, M4)+COUNTIF($F$166:$F$167, M4)+COUNTIF($F$141:$F$141, M4)+COUNTIF($F$130:$F$131, M4)+COUNTIF($F$111:$F$112, M4)+COUNTIF($F$96:$F$98, M4)&gt;1,NOT(ISBLANK(M4)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="76" priority="1231" stopIfTrue="1">
-      <formula>AND(COUNTIF($F$332:$F$65454, M4)+COUNTIF($F$1:$F$27, M4)+COUNTIF($F$294:$F$295, M4)+COUNTIF(#REF!, M4)+COUNTIF($F$252:$F$255, M4)+COUNTIF($F$229:$F$230, M4)+COUNTIF($F$202:$F$203, M4)+COUNTIF($F$181:$F$181, M4)+COUNTIF($F$166:$F$167, M4)+COUNTIF($F$141:$F$141, M4)+COUNTIF($F$130:$F$131, M4)+COUNTIF($F$111:$F$112, M4)+COUNTIF($F$96:$F$98, M4)&gt;1,NOT(ISBLANK(M4)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="75" priority="1232" stopIfTrue="1">
-      <formula>AND(COUNTIF($F$294:$F$65454, M4)+COUNTIF($F$1:$F$27, M4)+COUNTIF(#REF!, M4)+COUNTIF($F$252:$F$255, M4)+COUNTIF($F$229:$F$230, M4)+COUNTIF($F$202:$F$203, M4)+COUNTIF($F$181:$F$181, M4)+COUNTIF($F$166:$F$167, M4)+COUNTIF($F$141:$F$141, M4)+COUNTIF($F$130:$F$131, M4)+COUNTIF($F$111:$F$112, M4)+COUNTIF($F$96:$F$98, M4)&gt;1,NOT(ISBLANK(M4)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="74" priority="1233" stopIfTrue="1">
-      <formula>AND(COUNTIF($F$252:$F$65454, M4)+COUNTIF(#REF!, M4)+COUNTIF($F$1:$F$27, M4)+COUNTIF($F$229:$F$230, M4)+COUNTIF($F$202:$F$203, M4)+COUNTIF($F$181:$F$181, M4)+COUNTIF($F$166:$F$167, M4)+COUNTIF($F$141:$F$141, M4)+COUNTIF($F$130:$F$131, M4)+COUNTIF($F$111:$F$112, M4)+COUNTIF($F$96:$F$98, M4)&gt;1,NOT(ISBLANK(M4)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="73" priority="1234" stopIfTrue="1">
-      <formula>AND(COUNTIF($F$252:$F$65454, M4)+COUNTIF($F$229:$F$230, M4)+COUNTIF($F$202:$F$203, M4)+COUNTIF($F$181:$F$181, M4)+COUNTIF($F$166:$F$167, M4)+COUNTIF($F$1:$F$27, M4)+COUNTIF(#REF!, M4)+COUNTIF($F$141:$F$141, M4)+COUNTIF($F$130:$F$131, M4)+COUNTIF(#REF!, M4)+COUNTIF($F$111:$F$112, M4)+COUNTIF($F$89:$F$89, M4)+COUNTIF($F$91:$F$98, M4)+COUNTIF(#REF!, M4)&gt;1,NOT(ISBLANK(M4)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="72" priority="1235" stopIfTrue="1">
-      <formula>AND(COUNTIF($F$229:$F$65454, M4)+COUNTIF($F$202:$F$203, M4)+COUNTIF($F$181:$F$181, M4)+COUNTIF($F$166:$F$167, M4)+COUNTIF($F$1:$F$27, M4)+COUNTIF(#REF!, M4)+COUNTIF($F$141:$F$141, M4)+COUNTIF($F$130:$F$131, M4)+COUNTIF(#REF!, M4)+COUNTIF($F$111:$F$112, M4)+COUNTIF($F$89:$F$89, M4)+COUNTIF($F$91:$F$98, M4)+COUNTIF(#REF!, M4)&gt;1,NOT(ISBLANK(M4)))</formula>
     </cfRule>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
@@ -5135,7 +5135,9 @@
       <c r="E3" s="138" t="s">
         <v>179</v>
       </c>
-      <c r="F3" s="141"/>
+      <c r="F3" s="139">
+        <v>27</v>
+      </c>
       <c r="G3" s="138" t="s">
         <v>167</v>
       </c>
@@ -5200,7 +5202,9 @@
       <c r="E4" s="138" t="s">
         <v>179</v>
       </c>
-      <c r="F4" s="138"/>
+      <c r="F4" s="139">
+        <v>27</v>
+      </c>
       <c r="G4" s="138" t="s">
         <v>167</v>
       </c>
@@ -5265,7 +5269,9 @@
       <c r="E5" s="138" t="s">
         <v>179</v>
       </c>
-      <c r="F5" s="141"/>
+      <c r="F5" s="139">
+        <v>27</v>
+      </c>
       <c r="G5" s="138" t="s">
         <v>167</v>
       </c>
@@ -5330,7 +5336,9 @@
       <c r="E6" s="138" t="s">
         <v>179</v>
       </c>
-      <c r="F6" s="138"/>
+      <c r="F6" s="139">
+        <v>27</v>
+      </c>
       <c r="G6" s="138" t="s">
         <v>167</v>
       </c>
@@ -5395,7 +5403,9 @@
       <c r="E7" s="138" t="s">
         <v>179</v>
       </c>
-      <c r="F7" s="141"/>
+      <c r="F7" s="139">
+        <v>27</v>
+      </c>
       <c r="G7" s="138" t="s">
         <v>167</v>
       </c>
@@ -5515,7 +5525,9 @@
       <c r="E9" s="138" t="s">
         <v>161</v>
       </c>
-      <c r="F9" s="141"/>
+      <c r="F9" s="139">
+        <v>35</v>
+      </c>
       <c r="G9" s="138" t="s">
         <v>167</v>
       </c>
@@ -5579,7 +5591,9 @@
       <c r="E10" s="138" t="s">
         <v>161</v>
       </c>
-      <c r="F10" s="141"/>
+      <c r="F10" s="139">
+        <v>35</v>
+      </c>
       <c r="G10" s="138" t="s">
         <v>167</v>
       </c>
@@ -5644,7 +5658,9 @@
       <c r="E11" s="138" t="s">
         <v>161</v>
       </c>
-      <c r="F11" s="141"/>
+      <c r="F11" s="139">
+        <v>35</v>
+      </c>
       <c r="G11" s="138" t="s">
         <v>167</v>
       </c>
@@ -5709,7 +5725,9 @@
       <c r="E12" s="138" t="s">
         <v>161</v>
       </c>
-      <c r="F12" s="135"/>
+      <c r="F12" s="139">
+        <v>35</v>
+      </c>
       <c r="G12" s="138" t="s">
         <v>167</v>
       </c>
@@ -5774,7 +5792,9 @@
       <c r="E13" s="138" t="s">
         <v>161</v>
       </c>
-      <c r="F13" s="135"/>
+      <c r="F13" s="139">
+        <v>35</v>
+      </c>
       <c r="G13" s="138" t="s">
         <v>167</v>
       </c>
@@ -5839,7 +5859,9 @@
       <c r="E14" s="138" t="s">
         <v>161</v>
       </c>
-      <c r="F14" s="141"/>
+      <c r="F14" s="139">
+        <v>35</v>
+      </c>
       <c r="G14" s="138" t="s">
         <v>167</v>
       </c>
@@ -5960,7 +5982,9 @@
       <c r="E16" s="138" t="s">
         <v>162</v>
       </c>
-      <c r="F16" s="135"/>
+      <c r="F16" s="139">
+        <v>30</v>
+      </c>
       <c r="G16" s="138" t="s">
         <v>168</v>
       </c>
@@ -6025,7 +6049,9 @@
       <c r="E17" s="138" t="s">
         <v>162</v>
       </c>
-      <c r="F17" s="135"/>
+      <c r="F17" s="139">
+        <v>30</v>
+      </c>
       <c r="G17" s="138" t="s">
         <v>168</v>
       </c>
@@ -6090,7 +6116,9 @@
       <c r="E18" s="138" t="s">
         <v>162</v>
       </c>
-      <c r="F18" s="141"/>
+      <c r="F18" s="139">
+        <v>30</v>
+      </c>
       <c r="G18" s="138" t="s">
         <v>168</v>
       </c>
@@ -6221,7 +6249,9 @@
       <c r="E20" s="138" t="s">
         <v>163</v>
       </c>
-      <c r="F20" s="138"/>
+      <c r="F20" s="139">
+        <v>20</v>
+      </c>
       <c r="G20" s="138" t="s">
         <v>168</v>
       </c>
@@ -6286,7 +6316,9 @@
       <c r="E21" s="138" t="s">
         <v>163</v>
       </c>
-      <c r="F21" s="138"/>
+      <c r="F21" s="139">
+        <v>20</v>
+      </c>
       <c r="G21" s="138" t="s">
         <v>168</v>
       </c>
@@ -6351,7 +6383,9 @@
       <c r="E22" s="138" t="s">
         <v>163</v>
       </c>
-      <c r="F22" s="141"/>
+      <c r="F22" s="139">
+        <v>20</v>
+      </c>
       <c r="G22" s="138" t="s">
         <v>168</v>
       </c>
@@ -6475,7 +6509,9 @@
       <c r="E24" s="138" t="s">
         <v>164</v>
       </c>
-      <c r="F24" s="141"/>
+      <c r="F24" s="139">
+        <v>20</v>
+      </c>
       <c r="G24" s="138" t="s">
         <v>168</v>
       </c>
@@ -6539,7 +6575,9 @@
       <c r="E25" s="138" t="s">
         <v>164</v>
       </c>
-      <c r="F25" s="141"/>
+      <c r="F25" s="139">
+        <v>20</v>
+      </c>
       <c r="G25" s="138" t="s">
         <v>168</v>
       </c>
@@ -6603,7 +6641,9 @@
       <c r="E26" s="138" t="s">
         <v>164</v>
       </c>
-      <c r="F26" s="141"/>
+      <c r="F26" s="139">
+        <v>20</v>
+      </c>
       <c r="G26" s="138" t="s">
         <v>168</v>
       </c>
@@ -6668,7 +6708,9 @@
       <c r="E27" s="138" t="s">
         <v>164</v>
       </c>
-      <c r="F27" s="141"/>
+      <c r="F27" s="139">
+        <v>20</v>
+      </c>
       <c r="G27" s="138" t="s">
         <v>168</v>
       </c>
@@ -6988,12 +7030,12 @@
     <cfRule type="duplicateValues" dxfId="68" priority="1379"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B17">
-    <cfRule type="duplicateValues" dxfId="67" priority="123"/>
-    <cfRule type="duplicateValues" dxfId="66" priority="124"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="124"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="123"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B18">
-    <cfRule type="duplicateValues" dxfId="65" priority="125"/>
-    <cfRule type="duplicateValues" dxfId="64" priority="126"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="126"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="125"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B26:B27 B2:B3 B21:B23 B5:B19">
     <cfRule type="duplicateValues" dxfId="63" priority="1367"/>
@@ -7005,28 +7047,28 @@
     <cfRule type="duplicateValues" dxfId="61" priority="160"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J14 K16 J16:J31">
-    <cfRule type="containsText" dxfId="60" priority="179" operator="containsText" text="WIP">
-      <formula>NOT(ISERROR(SEARCH("WIP",J2)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="59" priority="182" operator="containsText" text="Complete">
+    <cfRule type="containsText" dxfId="60" priority="198" operator="containsText" text="ROW">
+      <formula>NOT(ISERROR(SEARCH("ROW",J2)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="59" priority="197" operator="containsText" text="Complete">
       <formula>NOT(ISERROR(SEARCH("Complete",J2)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="58" priority="183" operator="containsText" text="ROW">
       <formula>NOT(ISERROR(SEARCH("ROW",J2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="57" priority="197" operator="containsText" text="Complete">
+    <cfRule type="containsText" dxfId="57" priority="182" operator="containsText" text="Complete">
       <formula>NOT(ISERROR(SEARCH("Complete",J2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="56" priority="198" operator="containsText" text="ROW">
-      <formula>NOT(ISERROR(SEARCH("ROW",J2)))</formula>
+    <cfRule type="containsText" dxfId="56" priority="179" operator="containsText" text="WIP">
+      <formula>NOT(ISERROR(SEARCH("WIP",J2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K3:K7 K9:K13 K20:K22">
-    <cfRule type="containsText" dxfId="55" priority="111" operator="containsText" text="Complete">
+    <cfRule type="containsText" dxfId="55" priority="112" operator="containsText" text="ROW">
+      <formula>NOT(ISERROR(SEARCH("ROW",K3)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="54" priority="111" operator="containsText" text="Complete">
       <formula>NOT(ISERROR(SEARCH("Complete",K3)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="54" priority="112" operator="containsText" text="ROW">
-      <formula>NOT(ISERROR(SEARCH("ROW",K3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K3:K7 K9:K13 K20:N22">
@@ -7035,19 +7077,19 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K3:K7 L4:L5 K9:K13">
-    <cfRule type="containsText" dxfId="52" priority="108" operator="containsText" text="Complete">
+    <cfRule type="containsText" dxfId="52" priority="109" operator="containsText" text="ROW">
+      <formula>NOT(ISERROR(SEARCH("ROW",K3)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="51" priority="108" operator="containsText" text="Complete">
       <formula>NOT(ISERROR(SEARCH("Complete",K3)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="51" priority="109" operator="containsText" text="ROW">
-      <formula>NOT(ISERROR(SEARCH("ROW",K3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K3:K7">
-    <cfRule type="containsText" dxfId="50" priority="70" operator="containsText" text="Complete">
+    <cfRule type="containsText" dxfId="50" priority="71" operator="containsText" text="ROW">
+      <formula>NOT(ISERROR(SEARCH("ROW",K3)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="49" priority="70" operator="containsText" text="Complete">
       <formula>NOT(ISERROR(SEARCH("Complete",K3)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="49" priority="71" operator="containsText" text="ROW">
-      <formula>NOT(ISERROR(SEARCH("ROW",K3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K16:M16 L2:N7 L9:N14 O24 O26:O30 L8:M8 N15 K17:N18 L23:N26 K25:K26 K27:N31">
@@ -7056,19 +7098,19 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K20:N22">
-    <cfRule type="containsText" dxfId="47" priority="66" operator="containsText" text="Complete">
+    <cfRule type="containsText" dxfId="47" priority="67" operator="containsText" text="ROW">
+      <formula>NOT(ISERROR(SEARCH("ROW",K20)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="46" priority="66" operator="containsText" text="Complete">
       <formula>NOT(ISERROR(SEARCH("Complete",K20)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="46" priority="67" operator="containsText" text="ROW">
-      <formula>NOT(ISERROR(SEARCH("ROW",K20)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L10:L11">
-    <cfRule type="containsText" dxfId="45" priority="72" operator="containsText" text="Complete">
+    <cfRule type="containsText" dxfId="45" priority="73" operator="containsText" text="ROW">
+      <formula>NOT(ISERROR(SEARCH("ROW",L10)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="44" priority="72" operator="containsText" text="Complete">
       <formula>NOT(ISERROR(SEARCH("Complete",L10)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="44" priority="73" operator="containsText" text="ROW">
-      <formula>NOT(ISERROR(SEARCH("ROW",L10)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L15">
@@ -7093,11 +7135,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L19:N19">
-    <cfRule type="containsText" dxfId="38" priority="17" operator="containsText" text="Complete">
+    <cfRule type="containsText" dxfId="38" priority="18" operator="containsText" text="ROW">
+      <formula>NOT(ISERROR(SEARCH("ROW",L19)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="37" priority="17" operator="containsText" text="Complete">
       <formula>NOT(ISERROR(SEARCH("Complete",L19)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="37" priority="18" operator="containsText" text="ROW">
-      <formula>NOT(ISERROR(SEARCH("ROW",L19)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L19:O19">
@@ -7146,33 +7188,33 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O9">
-    <cfRule type="containsText" dxfId="25" priority="26" operator="containsText" text="WIP">
-      <formula>NOT(ISERROR(SEARCH("WIP",O9)))</formula>
+    <cfRule type="containsText" dxfId="25" priority="28" operator="containsText" text="ROW">
+      <formula>NOT(ISERROR(SEARCH("ROW",O9)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="24" priority="27" operator="containsText" text="Complete">
       <formula>NOT(ISERROR(SEARCH("Complete",O9)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="23" priority="28" operator="containsText" text="ROW">
-      <formula>NOT(ISERROR(SEARCH("ROW",O9)))</formula>
+    <cfRule type="containsText" dxfId="23" priority="26" operator="containsText" text="WIP">
+      <formula>NOT(ISERROR(SEARCH("WIP",O9)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O10">
-    <cfRule type="containsText" dxfId="22" priority="57" operator="containsText" text="WIP">
+    <cfRule type="containsText" dxfId="22" priority="58" operator="containsText" text="Complete">
+      <formula>NOT(ISERROR(SEARCH("Complete",O10)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="21" priority="59" operator="containsText" text="ROW">
+      <formula>NOT(ISERROR(SEARCH("ROW",O10)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="20" priority="57" operator="containsText" text="WIP">
       <formula>NOT(ISERROR(SEARCH("WIP",O10)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="21" priority="58" operator="containsText" text="Complete">
-      <formula>NOT(ISERROR(SEARCH("Complete",O10)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="20" priority="59" operator="containsText" text="ROW">
-      <formula>NOT(ISERROR(SEARCH("ROW",O10)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O10:O13">
-    <cfRule type="containsText" dxfId="19" priority="55" operator="containsText" text="Complete">
+    <cfRule type="containsText" dxfId="19" priority="56" operator="containsText" text="ROW">
+      <formula>NOT(ISERROR(SEARCH("ROW",O10)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="18" priority="55" operator="containsText" text="Complete">
       <formula>NOT(ISERROR(SEARCH("Complete",O10)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="18" priority="56" operator="containsText" text="ROW">
-      <formula>NOT(ISERROR(SEARCH("ROW",O10)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O11:O13">
@@ -7181,19 +7223,19 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O13">
-    <cfRule type="containsText" dxfId="16" priority="24" operator="containsText" text="Complete">
+    <cfRule type="containsText" dxfId="16" priority="25" operator="containsText" text="ROW">
+      <formula>NOT(ISERROR(SEARCH("ROW",O13)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="15" priority="24" operator="containsText" text="Complete">
       <formula>NOT(ISERROR(SEARCH("Complete",O13)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="15" priority="25" operator="containsText" text="ROW">
-      <formula>NOT(ISERROR(SEARCH("ROW",O13)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O13:O14">
-    <cfRule type="containsText" dxfId="14" priority="52" operator="containsText" text="Complete">
+    <cfRule type="containsText" dxfId="14" priority="53" operator="containsText" text="ROW">
+      <formula>NOT(ISERROR(SEARCH("ROW",O13)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="13" priority="52" operator="containsText" text="Complete">
       <formula>NOT(ISERROR(SEARCH("Complete",O13)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="13" priority="53" operator="containsText" text="ROW">
-      <formula>NOT(ISERROR(SEARCH("ROW",O13)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O13:O17">
@@ -7202,38 +7244,38 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O15:O16">
-    <cfRule type="containsText" dxfId="11" priority="9" operator="containsText" text="Complete">
+    <cfRule type="containsText" dxfId="11" priority="10" operator="containsText" text="ROW">
+      <formula>NOT(ISERROR(SEARCH("ROW",O15)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="10" priority="9" operator="containsText" text="Complete">
       <formula>NOT(ISERROR(SEARCH("Complete",O15)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="10" priority="10" operator="containsText" text="ROW">
-      <formula>NOT(ISERROR(SEARCH("ROW",O15)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O15:O17">
-    <cfRule type="containsText" dxfId="9" priority="12" operator="containsText" text="Complete">
+    <cfRule type="containsText" dxfId="9" priority="13" operator="containsText" text="ROW">
+      <formula>NOT(ISERROR(SEARCH("ROW",O15)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="8" priority="12" operator="containsText" text="Complete">
       <formula>NOT(ISERROR(SEARCH("Complete",O15)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="8" priority="13" operator="containsText" text="ROW">
-      <formula>NOT(ISERROR(SEARCH("ROW",O15)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O19:O20">
-    <cfRule type="containsText" dxfId="7" priority="20" operator="containsText" text="Complete">
+    <cfRule type="containsText" dxfId="7" priority="21" operator="containsText" text="ROW">
+      <formula>NOT(ISERROR(SEARCH("ROW",O19)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="6" priority="20" operator="containsText" text="Complete">
       <formula>NOT(ISERROR(SEARCH("Complete",O19)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="6" priority="21" operator="containsText" text="ROW">
-      <formula>NOT(ISERROR(SEARCH("ROW",O19)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O20:O24">
-    <cfRule type="containsText" dxfId="5" priority="41" operator="containsText" text="WIP">
+    <cfRule type="containsText" dxfId="5" priority="42" operator="containsText" text="Complete">
+      <formula>NOT(ISERROR(SEARCH("Complete",O20)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="4" priority="43" operator="containsText" text="ROW">
+      <formula>NOT(ISERROR(SEARCH("ROW",O20)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="3" priority="41" operator="containsText" text="WIP">
       <formula>NOT(ISERROR(SEARCH("WIP",O20)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="4" priority="42" operator="containsText" text="Complete">
-      <formula>NOT(ISERROR(SEARCH("Complete",O20)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="3" priority="43" operator="containsText" text="ROW">
-      <formula>NOT(ISERROR(SEARCH("ROW",O20)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O26">
@@ -8018,32 +8060,32 @@
       <c r="F17" s="6"/>
     </row>
     <row r="18" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="180" t="s">
+      <c r="A18" s="195" t="s">
         <v>4</v>
       </c>
-      <c r="B18" s="180" t="s">
+      <c r="B18" s="195" t="s">
         <v>42</v>
       </c>
-      <c r="C18" s="177" t="s">
+      <c r="C18" s="191" t="s">
         <v>47</v>
       </c>
-      <c r="D18" s="177" t="s">
+      <c r="D18" s="191" t="s">
         <v>43</v>
       </c>
-      <c r="E18" s="180" t="s">
+      <c r="E18" s="195" t="s">
         <v>8</v>
       </c>
-      <c r="F18" s="192" t="s">
+      <c r="F18" s="182" t="s">
         <v>18</v>
       </c>
-      <c r="G18" s="192"/>
-      <c r="H18" s="192"/>
-      <c r="I18" s="192"/>
-      <c r="J18" s="192"/>
+      <c r="G18" s="182"/>
+      <c r="H18" s="182"/>
+      <c r="I18" s="182"/>
+      <c r="J18" s="182"/>
       <c r="K18" s="185" t="s">
         <v>19</v>
       </c>
-      <c r="M18" s="177" t="s">
+      <c r="M18" s="191" t="s">
         <v>36</v>
       </c>
       <c r="O18" s="186" t="s">
@@ -8067,24 +8109,24 @@
       </c>
     </row>
     <row r="19" spans="1:28" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="181"/>
-      <c r="B19" s="181"/>
-      <c r="C19" s="178"/>
-      <c r="D19" s="181"/>
-      <c r="E19" s="181"/>
-      <c r="F19" s="204" t="s">
+      <c r="A19" s="196"/>
+      <c r="B19" s="196"/>
+      <c r="C19" s="193"/>
+      <c r="D19" s="196"/>
+      <c r="E19" s="196"/>
+      <c r="F19" s="203" t="s">
         <v>40</v>
       </c>
-      <c r="G19" s="205" t="s">
+      <c r="G19" s="204" t="s">
         <v>44</v>
       </c>
-      <c r="H19" s="206"/>
-      <c r="I19" s="205" t="s">
+      <c r="H19" s="205"/>
+      <c r="I19" s="204" t="s">
         <v>45</v>
       </c>
-      <c r="J19" s="206"/>
+      <c r="J19" s="205"/>
       <c r="K19" s="185"/>
-      <c r="M19" s="191"/>
+      <c r="M19" s="192"/>
       <c r="O19" s="183" t="s">
         <v>24</v>
       </c>
@@ -8124,12 +8166,12 @@
       <c r="AB19" s="190"/>
     </row>
     <row r="20" spans="1:28" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="181"/>
-      <c r="B20" s="181"/>
-      <c r="C20" s="178"/>
-      <c r="D20" s="181"/>
-      <c r="E20" s="181"/>
-      <c r="F20" s="204"/>
+      <c r="A20" s="196"/>
+      <c r="B20" s="196"/>
+      <c r="C20" s="193"/>
+      <c r="D20" s="196"/>
+      <c r="E20" s="196"/>
+      <c r="F20" s="203"/>
       <c r="G20" s="94" t="s">
         <v>10</v>
       </c>
@@ -8179,7 +8221,7 @@
       <c r="D21" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="E21" s="203" t="s">
+      <c r="E21" s="206" t="s">
         <v>98</v>
       </c>
       <c r="F21" s="114">
@@ -8253,7 +8295,7 @@
       <c r="D22" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="E22" s="203"/>
+      <c r="E22" s="206"/>
       <c r="F22" s="114">
         <v>45913</v>
       </c>
@@ -8325,7 +8367,7 @@
       <c r="D23" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="E23" s="203"/>
+      <c r="E23" s="206"/>
       <c r="F23" s="114">
         <v>45910</v>
       </c>
@@ -8397,7 +8439,7 @@
       <c r="D24" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="E24" s="203"/>
+      <c r="E24" s="206"/>
       <c r="F24" s="114">
         <v>45927</v>
       </c>
@@ -8469,7 +8511,7 @@
       <c r="D25" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="E25" s="203"/>
+      <c r="E25" s="206"/>
       <c r="F25" s="114">
         <v>45915</v>
       </c>
@@ -9164,6 +9206,18 @@
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="E21:E25"/>
+    <mergeCell ref="W19:W20"/>
+    <mergeCell ref="K18:K19"/>
+    <mergeCell ref="M18:M19"/>
+    <mergeCell ref="O18:T18"/>
+    <mergeCell ref="V18:AA18"/>
+    <mergeCell ref="V19:V20"/>
+    <mergeCell ref="A18:A20"/>
+    <mergeCell ref="B18:B20"/>
+    <mergeCell ref="C18:C20"/>
+    <mergeCell ref="D18:D20"/>
+    <mergeCell ref="E18:E20"/>
     <mergeCell ref="AB18:AB19"/>
     <mergeCell ref="F19:F20"/>
     <mergeCell ref="G19:H19"/>
@@ -9177,18 +9231,6 @@
     <mergeCell ref="Q19:Q20"/>
     <mergeCell ref="R19:R20"/>
     <mergeCell ref="S19:S20"/>
-    <mergeCell ref="A18:A20"/>
-    <mergeCell ref="B18:B20"/>
-    <mergeCell ref="C18:C20"/>
-    <mergeCell ref="D18:D20"/>
-    <mergeCell ref="E18:E20"/>
-    <mergeCell ref="E21:E25"/>
-    <mergeCell ref="W19:W20"/>
-    <mergeCell ref="K18:K19"/>
-    <mergeCell ref="M18:M19"/>
-    <mergeCell ref="O18:T18"/>
-    <mergeCell ref="V18:AA18"/>
-    <mergeCell ref="V19:V20"/>
   </mergeCells>
   <conditionalFormatting sqref="C26:C27">
     <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="4DT6">
